--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5824,10 +5824,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120039375</v>
+        <v>120035542</v>
       </c>
       <c r="B47" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5864,13 +5864,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503988</v>
+        <v>504175</v>
       </c>
       <c r="R47" t="n">
-        <v>7134466</v>
+        <v>7134410</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035542</v>
+        <v>120039375</v>
       </c>
       <c r="B48" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504175</v>
+        <v>503988</v>
       </c>
       <c r="R48" t="n">
-        <v>7134410</v>
+        <v>7134466</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120060142</v>
+        <v>120076676</v>
       </c>
       <c r="B67" t="n">
         <v>91840</v>
@@ -7905,17 +7905,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503497</v>
+        <v>503536</v>
       </c>
       <c r="R67" t="n">
-        <v>7134657</v>
+        <v>7134619</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076676</v>
+        <v>120076639</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>79643</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503536</v>
+        <v>503430</v>
       </c>
       <c r="R68" t="n">
-        <v>7134619</v>
+        <v>7134677</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076639</v>
+        <v>120076644</v>
       </c>
       <c r="B69" t="n">
-        <v>79643</v>
+        <v>78262</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503430</v>
+        <v>503748</v>
       </c>
       <c r="R69" t="n">
-        <v>7134677</v>
+        <v>7134611</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076644</v>
+        <v>120076652</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,21 +8191,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503748</v>
+        <v>503526</v>
       </c>
       <c r="R70" t="n">
-        <v>7134611</v>
+        <v>7134815</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076652</v>
+        <v>120076650</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8293,21 +8293,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503526</v>
+        <v>503633</v>
       </c>
       <c r="R71" t="n">
-        <v>7134815</v>
+        <v>7134566</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076650</v>
+        <v>120076685</v>
       </c>
       <c r="B72" t="n">
-        <v>90576</v>
+        <v>79642</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503633</v>
+        <v>503819</v>
       </c>
       <c r="R72" t="n">
-        <v>7134566</v>
+        <v>7134668</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076685</v>
+        <v>120076631</v>
       </c>
       <c r="B73" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503819</v>
+        <v>503624</v>
       </c>
       <c r="R73" t="n">
-        <v>7134668</v>
+        <v>7134757</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076631</v>
+        <v>120076618</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>96868</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503624</v>
+        <v>503850</v>
       </c>
       <c r="R74" t="n">
-        <v>7134757</v>
+        <v>7134617</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076618</v>
+        <v>120076620</v>
       </c>
       <c r="B75" t="n">
-        <v>96868</v>
+        <v>92030</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,25 +8697,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503850</v>
+        <v>503618</v>
       </c>
       <c r="R75" t="n">
-        <v>7134617</v>
+        <v>7134495</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076620</v>
+        <v>120076660</v>
       </c>
       <c r="B76" t="n">
-        <v>92030</v>
+        <v>78171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8803,21 +8803,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503618</v>
+        <v>503616</v>
       </c>
       <c r="R76" t="n">
-        <v>7134495</v>
+        <v>7134591</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076660</v>
+        <v>120065097</v>
       </c>
       <c r="B77" t="n">
-        <v>78171</v>
+        <v>91886</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,41 +8901,44 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>232140</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503616</v>
+        <v>503748</v>
       </c>
       <c r="R77" t="n">
-        <v>7134591</v>
+        <v>7134611</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8967,12 +8970,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8991,10 +9000,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120065097</v>
+        <v>120060142</v>
       </c>
       <c r="B78" t="n">
-        <v>91886</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9003,41 +9012,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503748</v>
+        <v>503497</v>
       </c>
       <c r="R78" t="n">
-        <v>7134611</v>
+        <v>7134657</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9072,18 +9078,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076662</v>
+        <v>120076647</v>
       </c>
       <c r="B121" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503535</v>
+        <v>503790</v>
       </c>
       <c r="R121" t="n">
-        <v>7134599</v>
+        <v>7134698</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076670</v>
+        <v>120076662</v>
       </c>
       <c r="B122" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503626</v>
+        <v>503535</v>
       </c>
       <c r="R122" t="n">
-        <v>7134549</v>
+        <v>7134599</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076605</v>
+        <v>120076670</v>
       </c>
       <c r="B123" t="n">
-        <v>79636</v>
+        <v>91840</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503568</v>
+        <v>503626</v>
       </c>
       <c r="R123" t="n">
-        <v>7134774</v>
+        <v>7134549</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076647</v>
+        <v>120076605</v>
       </c>
       <c r="B124" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13709,25 +13709,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503790</v>
+        <v>503568</v>
       </c>
       <c r="R124" t="n">
-        <v>7134698</v>
+        <v>7134774</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120036399</v>
+        <v>120040383</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>90807</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5627,41 +5627,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504083</v>
+        <v>503879</v>
       </c>
       <c r="R45" t="n">
-        <v>7134453</v>
+        <v>7134575</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,11 +5691,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5722,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120034574</v>
+        <v>120035474</v>
       </c>
       <c r="B46" t="n">
-        <v>78262</v>
+        <v>79636</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5734,25 +5729,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5762,13 +5757,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504224</v>
+        <v>504166</v>
       </c>
       <c r="R46" t="n">
-        <v>7134352</v>
+        <v>7134391</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5824,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120035542</v>
+        <v>120039375</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5840,21 +5835,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5864,13 +5859,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504175</v>
+        <v>503988</v>
       </c>
       <c r="R47" t="n">
-        <v>7134410</v>
+        <v>7134466</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5926,7 +5921,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120039375</v>
+        <v>120034574</v>
       </c>
       <c r="B48" t="n">
         <v>78262</v>
@@ -5966,13 +5961,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503988</v>
+        <v>504224</v>
       </c>
       <c r="R48" t="n">
-        <v>7134466</v>
+        <v>7134352</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6028,10 +6023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035460</v>
+        <v>120034826</v>
       </c>
       <c r="B49" t="n">
-        <v>79608</v>
+        <v>91844</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6040,25 +6035,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>4365</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6068,13 +6063,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504169</v>
+        <v>504226</v>
       </c>
       <c r="R49" t="n">
-        <v>7134407</v>
+        <v>7134339</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6130,10 +6125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120034826</v>
+        <v>120035622</v>
       </c>
       <c r="B50" t="n">
-        <v>91844</v>
+        <v>79607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6142,25 +6137,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4365</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,13 +6165,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504226</v>
+        <v>504165</v>
       </c>
       <c r="R50" t="n">
-        <v>7134339</v>
+        <v>7134407</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6232,10 +6227,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120035474</v>
+        <v>120035542</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6244,25 +6239,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6272,13 +6267,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504166</v>
+        <v>504175</v>
       </c>
       <c r="R51" t="n">
-        <v>7134391</v>
+        <v>7134410</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6334,10 +6329,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120035768</v>
+        <v>120034383</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6350,21 +6345,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6374,13 +6369,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504187</v>
+        <v>504257</v>
       </c>
       <c r="R52" t="n">
-        <v>7134438</v>
+        <v>7134334</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6436,10 +6431,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120035622</v>
+        <v>120034479</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6452,21 +6447,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504165</v>
+        <v>504252</v>
       </c>
       <c r="R53" t="n">
-        <v>7134407</v>
+        <v>7134346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6538,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120040383</v>
+        <v>120036022</v>
       </c>
       <c r="B54" t="n">
-        <v>90807</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,38 +6545,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503879</v>
+        <v>504145</v>
       </c>
       <c r="R54" t="n">
-        <v>7134575</v>
+        <v>7134441</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6640,7 +6635,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120036022</v>
+        <v>120035768</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6680,13 +6675,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504145</v>
+        <v>504187</v>
       </c>
       <c r="R55" t="n">
-        <v>7134441</v>
+        <v>7134438</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6849,7 +6844,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120034479</v>
+        <v>120035015</v>
       </c>
       <c r="B57" t="n">
         <v>78262</v>
@@ -6889,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504252</v>
+        <v>504196</v>
       </c>
       <c r="R57" t="n">
-        <v>7134346</v>
+        <v>7134350</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,10 +6946,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120034383</v>
+        <v>120036399</v>
       </c>
       <c r="B58" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6962,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,13 +6986,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504257</v>
+        <v>504083</v>
       </c>
       <c r="R58" t="n">
-        <v>7134334</v>
+        <v>7134453</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7027,6 +7022,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120035868</v>
+        <v>120035460</v>
       </c>
       <c r="B59" t="n">
-        <v>78263</v>
+        <v>79608</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7093,13 +7093,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504193</v>
+        <v>504169</v>
       </c>
       <c r="R59" t="n">
-        <v>7134477</v>
+        <v>7134407</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120035015</v>
+        <v>120035871</v>
       </c>
       <c r="B60" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,21 +7171,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,13 +7195,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504196</v>
+        <v>504192</v>
       </c>
       <c r="R60" t="n">
-        <v>7134350</v>
+        <v>7134481</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120035871</v>
+        <v>120035868</v>
       </c>
       <c r="B61" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504192</v>
+        <v>504193</v>
       </c>
       <c r="R61" t="n">
-        <v>7134481</v>
+        <v>7134477</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120038261</v>
+        <v>120046464</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,41 +7371,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503997</v>
+        <v>503874</v>
       </c>
       <c r="R62" t="n">
-        <v>7134441</v>
+        <v>7134566</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7461,10 +7461,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120046465</v>
+        <v>120046468</v>
       </c>
       <c r="B63" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7473,25 +7473,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504001</v>
+        <v>503899</v>
       </c>
       <c r="R63" t="n">
-        <v>7134466</v>
+        <v>7134531</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120046468</v>
+        <v>120038261</v>
       </c>
       <c r="B64" t="n">
         <v>97907</v>
@@ -7599,17 +7599,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503899</v>
+        <v>503997</v>
       </c>
       <c r="R64" t="n">
-        <v>7134531</v>
+        <v>7134441</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120039963</v>
+        <v>120046465</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,41 +7677,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503904</v>
+        <v>504001</v>
       </c>
       <c r="R65" t="n">
-        <v>7134523</v>
+        <v>7134466</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120046464</v>
+        <v>120039963</v>
       </c>
       <c r="B66" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7779,41 +7779,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503874</v>
+        <v>503904</v>
       </c>
       <c r="R66" t="n">
-        <v>7134566</v>
+        <v>7134523</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076676</v>
+        <v>120064794</v>
       </c>
       <c r="B67" t="n">
         <v>91840</v>
@@ -7905,17 +7905,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503536</v>
+        <v>503729</v>
       </c>
       <c r="R67" t="n">
-        <v>7134619</v>
+        <v>7134606</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076639</v>
+        <v>120076641</v>
       </c>
       <c r="B68" t="n">
-        <v>79643</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,25 +7983,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503430</v>
+        <v>503745</v>
       </c>
       <c r="R68" t="n">
-        <v>7134677</v>
+        <v>7134697</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076644</v>
+        <v>120076646</v>
       </c>
       <c r="B69" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503748</v>
+        <v>503675</v>
       </c>
       <c r="R69" t="n">
-        <v>7134611</v>
+        <v>7134737</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076652</v>
+        <v>120076664</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,21 +8191,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503526</v>
+        <v>503543</v>
       </c>
       <c r="R70" t="n">
-        <v>7134815</v>
+        <v>7134608</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076650</v>
+        <v>120076653</v>
       </c>
       <c r="B71" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8293,21 +8293,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503633</v>
+        <v>503608</v>
       </c>
       <c r="R71" t="n">
-        <v>7134566</v>
+        <v>7134763</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076685</v>
+        <v>120076633</v>
       </c>
       <c r="B72" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503819</v>
+        <v>503430</v>
       </c>
       <c r="R72" t="n">
-        <v>7134668</v>
+        <v>7134677</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076631</v>
+        <v>120076645</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503624</v>
+        <v>503601</v>
       </c>
       <c r="R73" t="n">
-        <v>7134757</v>
+        <v>7134773</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076618</v>
+        <v>120076608</v>
       </c>
       <c r="B74" t="n">
-        <v>96868</v>
+        <v>79608</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503850</v>
+        <v>503530</v>
       </c>
       <c r="R74" t="n">
-        <v>7134617</v>
+        <v>7134813</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076620</v>
+        <v>120076628</v>
       </c>
       <c r="B75" t="n">
-        <v>92030</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8701,21 +8701,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503618</v>
+        <v>503570</v>
       </c>
       <c r="R75" t="n">
-        <v>7134495</v>
+        <v>7134765</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076660</v>
+        <v>120076643</v>
       </c>
       <c r="B76" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8803,21 +8803,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503616</v>
+        <v>503820</v>
       </c>
       <c r="R76" t="n">
-        <v>7134591</v>
+        <v>7134705</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120065097</v>
+        <v>120076652</v>
       </c>
       <c r="B77" t="n">
-        <v>91886</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,44 +8901,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503748</v>
+        <v>503526</v>
       </c>
       <c r="R77" t="n">
-        <v>7134611</v>
+        <v>7134815</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8970,18 +8967,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9000,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120060142</v>
+        <v>120076685</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>79642</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9016,37 +9007,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503497</v>
+        <v>503819</v>
       </c>
       <c r="R78" t="n">
-        <v>7134657</v>
+        <v>7134668</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9102,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076625</v>
+        <v>120076637</v>
       </c>
       <c r="B79" t="n">
-        <v>78263</v>
+        <v>79643</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9114,25 +9105,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9142,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503539</v>
+        <v>503530</v>
       </c>
       <c r="R79" t="n">
-        <v>7134558</v>
+        <v>7134806</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9204,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076614</v>
+        <v>120076636</v>
       </c>
       <c r="B80" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9216,25 +9207,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9244,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503427</v>
+        <v>503530</v>
       </c>
       <c r="R80" t="n">
-        <v>7134675</v>
+        <v>7134813</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9306,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076654</v>
+        <v>120076670</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9318,25 +9309,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9346,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503821</v>
+        <v>503626</v>
       </c>
       <c r="R81" t="n">
-        <v>7134659</v>
+        <v>7134549</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9408,7 +9399,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076675</v>
+        <v>120076674</v>
       </c>
       <c r="B82" t="n">
         <v>91840</v>
@@ -9448,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503542</v>
+        <v>503558</v>
       </c>
       <c r="R82" t="n">
-        <v>7134610</v>
+        <v>7134614</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9510,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076665</v>
+        <v>120060142</v>
       </c>
       <c r="B83" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9522,41 +9513,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503480</v>
+        <v>503497</v>
       </c>
       <c r="R83" t="n">
-        <v>7134647</v>
+        <v>7134657</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9612,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076608</v>
+        <v>120076677</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9624,25 +9615,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9652,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503530</v>
+        <v>503481</v>
       </c>
       <c r="R84" t="n">
-        <v>7134813</v>
+        <v>7134655</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9714,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076633</v>
+        <v>120076672</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9726,25 +9717,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9754,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503430</v>
+        <v>503543</v>
       </c>
       <c r="R85" t="n">
-        <v>7134677</v>
+        <v>7134573</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9816,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076599</v>
+        <v>120076648</v>
       </c>
       <c r="B86" t="n">
-        <v>90527</v>
+        <v>89230</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9828,25 +9819,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>1596</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9856,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503657</v>
+        <v>503495</v>
       </c>
       <c r="R86" t="n">
-        <v>7134513</v>
+        <v>7134638</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9918,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076613</v>
+        <v>120076631</v>
       </c>
       <c r="B87" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9934,21 +9925,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9958,10 +9949,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503646</v>
+        <v>503624</v>
       </c>
       <c r="R87" t="n">
-        <v>7134570</v>
+        <v>7134757</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10020,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076610</v>
+        <v>120076638</v>
       </c>
       <c r="B88" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10032,25 +10023,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10060,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503592</v>
+        <v>503819</v>
       </c>
       <c r="R88" t="n">
-        <v>7134781</v>
+        <v>7134668</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10122,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076632</v>
+        <v>120076613</v>
       </c>
       <c r="B89" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10138,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503434</v>
+        <v>503646</v>
       </c>
       <c r="R89" t="n">
-        <v>7134673</v>
+        <v>7134570</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10224,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076630</v>
+        <v>120076609</v>
       </c>
       <c r="B90" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10240,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10264,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503592</v>
+        <v>503567</v>
       </c>
       <c r="R90" t="n">
-        <v>7134781</v>
+        <v>7134773</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10326,7 +10317,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076664</v>
+        <v>120076660</v>
       </c>
       <c r="B91" t="n">
         <v>78171</v>
@@ -10366,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503543</v>
+        <v>503616</v>
       </c>
       <c r="R91" t="n">
-        <v>7134608</v>
+        <v>7134591</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10428,10 +10419,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076687</v>
+        <v>120076675</v>
       </c>
       <c r="B92" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,25 +10431,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10468,10 +10459,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503491</v>
+        <v>503542</v>
       </c>
       <c r="R92" t="n">
-        <v>7134636</v>
+        <v>7134610</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10530,10 +10521,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076648</v>
+        <v>120076647</v>
       </c>
       <c r="B93" t="n">
-        <v>89230</v>
+        <v>97907</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10546,21 +10537,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1596</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10570,10 +10561,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503495</v>
+        <v>503790</v>
       </c>
       <c r="R93" t="n">
-        <v>7134638</v>
+        <v>7134698</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10632,10 +10623,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076600</v>
+        <v>120076661</v>
       </c>
       <c r="B94" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10648,21 +10639,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10663,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503603</v>
+        <v>503604</v>
       </c>
       <c r="R94" t="n">
-        <v>7134592</v>
+        <v>7134590</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10734,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076624</v>
+        <v>120076654</v>
       </c>
       <c r="B95" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10750,21 +10741,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10774,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503630</v>
+        <v>503821</v>
       </c>
       <c r="R95" t="n">
-        <v>7134529</v>
+        <v>7134659</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10836,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076609</v>
+        <v>120076640</v>
       </c>
       <c r="B96" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10852,21 +10843,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10876,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503567</v>
+        <v>503654</v>
       </c>
       <c r="R96" t="n">
-        <v>7134773</v>
+        <v>7134725</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11040,10 +11031,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076627</v>
+        <v>120076611</v>
       </c>
       <c r="B98" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11056,21 +11047,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11080,10 +11071,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503531</v>
+        <v>503691</v>
       </c>
       <c r="R98" t="n">
-        <v>7134812</v>
+        <v>7134749</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11142,10 +11133,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076646</v>
+        <v>120076630</v>
       </c>
       <c r="B99" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11154,25 +11145,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11182,10 +11173,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503675</v>
+        <v>503592</v>
       </c>
       <c r="R99" t="n">
-        <v>7134737</v>
+        <v>7134781</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11244,10 +11235,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120064794</v>
+        <v>120076684</v>
       </c>
       <c r="B100" t="n">
-        <v>91840</v>
+        <v>79642</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11260,37 +11251,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503729</v>
+        <v>503568</v>
       </c>
       <c r="R100" t="n">
-        <v>7134606</v>
+        <v>7134774</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11346,10 +11337,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076606</v>
+        <v>120076662</v>
       </c>
       <c r="B101" t="n">
-        <v>79636</v>
+        <v>78171</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11358,25 +11349,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11386,10 +11377,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503427</v>
+        <v>503535</v>
       </c>
       <c r="R101" t="n">
-        <v>7134680</v>
+        <v>7134599</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11448,7 +11439,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076626</v>
+        <v>120076629</v>
       </c>
       <c r="B102" t="n">
         <v>79607</v>
@@ -11488,10 +11479,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503534</v>
+        <v>503568</v>
       </c>
       <c r="R102" t="n">
-        <v>7134804</v>
+        <v>7134773</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11550,7 +11541,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076634</v>
+        <v>120076632</v>
       </c>
       <c r="B103" t="n">
         <v>79607</v>
@@ -11590,10 +11581,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503432</v>
+        <v>503434</v>
       </c>
       <c r="R103" t="n">
-        <v>7134696</v>
+        <v>7134673</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11652,10 +11643,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076602</v>
+        <v>120076606</v>
       </c>
       <c r="B104" t="n">
-        <v>89633</v>
+        <v>79636</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11664,25 +11655,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11692,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503489</v>
+        <v>503427</v>
       </c>
       <c r="R104" t="n">
-        <v>7134637</v>
+        <v>7134680</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11754,10 +11745,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076643</v>
+        <v>120076618</v>
       </c>
       <c r="B105" t="n">
-        <v>78262</v>
+        <v>96868</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11766,25 +11757,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11794,10 +11785,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503820</v>
+        <v>503850</v>
       </c>
       <c r="R105" t="n">
-        <v>7134705</v>
+        <v>7134617</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11856,10 +11847,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076640</v>
+        <v>120076605</v>
       </c>
       <c r="B106" t="n">
-        <v>78262</v>
+        <v>79636</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11868,25 +11859,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11896,10 +11887,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503654</v>
+        <v>503568</v>
       </c>
       <c r="R106" t="n">
-        <v>7134725</v>
+        <v>7134774</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11958,10 +11949,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076645</v>
+        <v>120076671</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11970,25 +11961,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11998,10 +11989,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503601</v>
+        <v>503546</v>
       </c>
       <c r="R107" t="n">
-        <v>7134773</v>
+        <v>7134587</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12060,10 +12051,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076651</v>
+        <v>120076665</v>
       </c>
       <c r="B108" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12072,25 +12063,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12100,10 +12091,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503516</v>
+        <v>503480</v>
       </c>
       <c r="R108" t="n">
-        <v>7134622</v>
+        <v>7134647</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12162,10 +12153,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076617</v>
+        <v>120076619</v>
       </c>
       <c r="B109" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12174,25 +12165,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12202,10 +12193,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503847</v>
+        <v>503460</v>
       </c>
       <c r="R109" t="n">
-        <v>7134693</v>
+        <v>7134749</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12264,7 +12255,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076612</v>
+        <v>120076615</v>
       </c>
       <c r="B110" t="n">
         <v>79608</v>
@@ -12304,10 +12295,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503818</v>
+        <v>503430</v>
       </c>
       <c r="R110" t="n">
-        <v>7134671</v>
+        <v>7134677</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12366,10 +12357,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076681</v>
+        <v>120076624</v>
       </c>
       <c r="B111" t="n">
-        <v>12337</v>
+        <v>78263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12378,25 +12369,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>101283</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12406,10 +12397,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503867</v>
+        <v>503630</v>
       </c>
       <c r="R111" t="n">
-        <v>7134650</v>
+        <v>7134529</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12442,11 +12433,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,10 +12459,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076661</v>
+        <v>120076625</v>
       </c>
       <c r="B112" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12489,21 +12475,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12499,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503604</v>
+        <v>503539</v>
       </c>
       <c r="R112" t="n">
-        <v>7134590</v>
+        <v>7134558</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,10 +12561,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076671</v>
+        <v>120076639</v>
       </c>
       <c r="B113" t="n">
-        <v>91840</v>
+        <v>79643</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12591,21 +12577,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12615,10 +12601,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503546</v>
+        <v>503430</v>
       </c>
       <c r="R113" t="n">
-        <v>7134587</v>
+        <v>7134677</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12663,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076649</v>
+        <v>120076676</v>
       </c>
       <c r="B114" t="n">
-        <v>90558</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12689,25 +12675,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12703,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503835</v>
+        <v>503536</v>
       </c>
       <c r="R114" t="n">
-        <v>7134640</v>
+        <v>7134619</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12765,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076686</v>
+        <v>120076673</v>
       </c>
       <c r="B115" t="n">
-        <v>79642</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12795,21 +12781,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12805,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503428</v>
+        <v>503532</v>
       </c>
       <c r="R115" t="n">
-        <v>7134677</v>
+        <v>7134595</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,7 +12867,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076616</v>
+        <v>120076610</v>
       </c>
       <c r="B116" t="n">
         <v>79608</v>
@@ -12921,10 +12907,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503430</v>
+        <v>503592</v>
       </c>
       <c r="R116" t="n">
-        <v>7134700</v>
+        <v>7134781</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12969,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076684</v>
+        <v>120076623</v>
       </c>
       <c r="B117" t="n">
-        <v>79642</v>
+        <v>78263</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12981,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13009,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503568</v>
+        <v>503665</v>
       </c>
       <c r="R117" t="n">
-        <v>7134774</v>
+        <v>7134523</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13071,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076653</v>
+        <v>120076644</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13101,21 +13087,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13111,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503608</v>
+        <v>503748</v>
       </c>
       <c r="R118" t="n">
-        <v>7134763</v>
+        <v>7134611</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13173,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076674</v>
+        <v>120076602</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13185,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13213,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503558</v>
+        <v>503489</v>
       </c>
       <c r="R119" t="n">
-        <v>7134614</v>
+        <v>7134637</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13275,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076628</v>
+        <v>120076617</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>96868</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13301,25 +13287,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13315,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503570</v>
+        <v>503847</v>
       </c>
       <c r="R120" t="n">
-        <v>7134765</v>
+        <v>7134693</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13377,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076647</v>
+        <v>120076687</v>
       </c>
       <c r="B121" t="n">
-        <v>97907</v>
+        <v>91834</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13389,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13417,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503790</v>
+        <v>503491</v>
       </c>
       <c r="R121" t="n">
-        <v>7134698</v>
+        <v>7134636</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13479,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076662</v>
+        <v>120076626</v>
       </c>
       <c r="B122" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13509,21 +13495,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13519,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503535</v>
+        <v>503534</v>
       </c>
       <c r="R122" t="n">
-        <v>7134599</v>
+        <v>7134804</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13581,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076670</v>
+        <v>120076627</v>
       </c>
       <c r="B123" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13607,25 +13593,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13621,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503626</v>
+        <v>503531</v>
       </c>
       <c r="R123" t="n">
-        <v>7134549</v>
+        <v>7134812</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13683,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076605</v>
+        <v>120076620</v>
       </c>
       <c r="B124" t="n">
-        <v>79636</v>
+        <v>92030</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13709,25 +13695,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13723,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503568</v>
+        <v>503618</v>
       </c>
       <c r="R124" t="n">
-        <v>7134774</v>
+        <v>7134495</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13785,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076623</v>
+        <v>120076612</v>
       </c>
       <c r="B125" t="n">
-        <v>78263</v>
+        <v>79608</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13815,21 +13801,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13825,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503665</v>
+        <v>503818</v>
       </c>
       <c r="R125" t="n">
-        <v>7134523</v>
+        <v>7134671</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13901,10 +13887,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076629</v>
+        <v>120076649</v>
       </c>
       <c r="B126" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13903,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13927,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503568</v>
+        <v>503835</v>
       </c>
       <c r="R126" t="n">
-        <v>7134773</v>
+        <v>7134640</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +13989,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076615</v>
+        <v>120076635</v>
       </c>
       <c r="B127" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14019,21 +14005,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14029,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503430</v>
+        <v>503426</v>
       </c>
       <c r="R127" t="n">
-        <v>7134677</v>
+        <v>7134704</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14091,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076636</v>
+        <v>120065097</v>
       </c>
       <c r="B128" t="n">
-        <v>79643</v>
+        <v>91886</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14117,41 +14103,44 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6464</v>
+        <v>232140</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503530</v>
+        <v>503748</v>
       </c>
       <c r="R128" t="n">
-        <v>7134813</v>
+        <v>7134611</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14183,12 +14172,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14207,10 +14202,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076673</v>
+        <v>120076616</v>
       </c>
       <c r="B129" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14219,25 +14214,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14242,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503532</v>
+        <v>503430</v>
       </c>
       <c r="R129" t="n">
-        <v>7134595</v>
+        <v>7134700</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14304,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076672</v>
+        <v>120076651</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14316,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14344,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503543</v>
+        <v>503516</v>
       </c>
       <c r="R130" t="n">
-        <v>7134573</v>
+        <v>7134622</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14406,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076635</v>
+        <v>120076650</v>
       </c>
       <c r="B131" t="n">
-        <v>79607</v>
+        <v>90576</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14427,21 +14422,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14446,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503426</v>
+        <v>503633</v>
       </c>
       <c r="R131" t="n">
-        <v>7134704</v>
+        <v>7134566</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14508,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076638</v>
+        <v>120076614</v>
       </c>
       <c r="B132" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14525,25 +14520,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14553,10 +14548,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503819</v>
+        <v>503427</v>
       </c>
       <c r="R132" t="n">
-        <v>7134668</v>
+        <v>7134675</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14615,10 +14610,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076611</v>
+        <v>120076634</v>
       </c>
       <c r="B133" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14631,21 +14626,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14650,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503691</v>
+        <v>503432</v>
       </c>
       <c r="R133" t="n">
-        <v>7134749</v>
+        <v>7134696</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14712,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076641</v>
+        <v>120076686</v>
       </c>
       <c r="B134" t="n">
-        <v>78262</v>
+        <v>79642</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14729,25 +14724,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14752,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503745</v>
+        <v>503428</v>
       </c>
       <c r="R134" t="n">
-        <v>7134697</v>
+        <v>7134677</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14814,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076637</v>
+        <v>120076599</v>
       </c>
       <c r="B135" t="n">
-        <v>79643</v>
+        <v>90527</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14835,21 +14830,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14854,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503530</v>
+        <v>503657</v>
       </c>
       <c r="R135" t="n">
-        <v>7134806</v>
+        <v>7134513</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14916,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076677</v>
+        <v>120076681</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>12337</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,25 +14928,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14956,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503481</v>
+        <v>503867</v>
       </c>
       <c r="R136" t="n">
-        <v>7134655</v>
+        <v>7134650</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14997,6 +14992,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076619</v>
+        <v>120076600</v>
       </c>
       <c r="B137" t="n">
-        <v>91832</v>
+        <v>79115</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15039,21 +15039,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503460</v>
+        <v>503603</v>
       </c>
       <c r="R137" t="n">
-        <v>7134749</v>
+        <v>7134592</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -6329,10 +6329,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120034383</v>
+        <v>120034479</v>
       </c>
       <c r="B52" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,21 +6345,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6369,13 +6369,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504257</v>
+        <v>504252</v>
       </c>
       <c r="R52" t="n">
-        <v>7134334</v>
+        <v>7134346</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6431,10 +6431,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120034479</v>
+        <v>120036022</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6447,21 +6447,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504252</v>
+        <v>504145</v>
       </c>
       <c r="R53" t="n">
-        <v>7134346</v>
+        <v>7134441</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120036022</v>
+        <v>120034383</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504145</v>
+        <v>504257</v>
       </c>
       <c r="R54" t="n">
-        <v>7134441</v>
+        <v>7134334</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120035768</v>
+        <v>120035015</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6651,21 +6651,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504187</v>
+        <v>504196</v>
       </c>
       <c r="R55" t="n">
-        <v>7134438</v>
+        <v>7134350</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120035291</v>
+        <v>120035768</v>
       </c>
       <c r="B56" t="n">
-        <v>4863</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6749,25 +6749,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101675</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504179</v>
+        <v>504187</v>
       </c>
       <c r="R56" t="n">
-        <v>7134372</v>
+        <v>7134438</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6813,11 +6813,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6844,10 +6839,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035015</v>
+        <v>120035291</v>
       </c>
       <c r="B57" t="n">
-        <v>78262</v>
+        <v>4863</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6856,25 +6851,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>101675</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6879,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504196</v>
+        <v>504179</v>
       </c>
       <c r="R57" t="n">
-        <v>7134350</v>
+        <v>7134372</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6920,6 +6915,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120035871</v>
+        <v>120035868</v>
       </c>
       <c r="B60" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,21 +7171,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504192</v>
+        <v>504193</v>
       </c>
       <c r="R60" t="n">
-        <v>7134481</v>
+        <v>7134477</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120035868</v>
+        <v>120035871</v>
       </c>
       <c r="B61" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504193</v>
+        <v>504192</v>
       </c>
       <c r="R61" t="n">
-        <v>7134477</v>
+        <v>7134481</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120064794</v>
+        <v>120076664</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7881,41 +7881,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503729</v>
+        <v>503543</v>
       </c>
       <c r="R67" t="n">
-        <v>7134606</v>
+        <v>7134608</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076641</v>
+        <v>120064794</v>
       </c>
       <c r="B68" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,41 +7983,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503745</v>
+        <v>503729</v>
       </c>
       <c r="R68" t="n">
-        <v>7134697</v>
+        <v>7134606</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076646</v>
+        <v>120076653</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503675</v>
+        <v>503608</v>
       </c>
       <c r="R69" t="n">
-        <v>7134737</v>
+        <v>7134763</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076664</v>
+        <v>120076641</v>
       </c>
       <c r="B70" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,21 +8191,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503543</v>
+        <v>503745</v>
       </c>
       <c r="R70" t="n">
-        <v>7134608</v>
+        <v>7134697</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076653</v>
+        <v>120076646</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503608</v>
+        <v>503675</v>
       </c>
       <c r="R71" t="n">
-        <v>7134763</v>
+        <v>7134737</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -11337,10 +11337,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076662</v>
+        <v>120076618</v>
       </c>
       <c r="B101" t="n">
-        <v>78171</v>
+        <v>96868</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11349,25 +11349,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503535</v>
+        <v>503850</v>
       </c>
       <c r="R101" t="n">
-        <v>7134599</v>
+        <v>7134617</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11439,10 +11439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076629</v>
+        <v>120076662</v>
       </c>
       <c r="B102" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11455,21 +11455,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503568</v>
+        <v>503535</v>
       </c>
       <c r="R102" t="n">
-        <v>7134773</v>
+        <v>7134599</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11541,10 +11541,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076632</v>
+        <v>120076606</v>
       </c>
       <c r="B103" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11553,25 +11553,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11581,10 +11581,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503434</v>
+        <v>503427</v>
       </c>
       <c r="R103" t="n">
-        <v>7134673</v>
+        <v>7134680</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11643,10 +11643,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076606</v>
+        <v>120076629</v>
       </c>
       <c r="B104" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11655,25 +11655,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503427</v>
+        <v>503568</v>
       </c>
       <c r="R104" t="n">
-        <v>7134680</v>
+        <v>7134773</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11745,10 +11745,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076618</v>
+        <v>120076632</v>
       </c>
       <c r="B105" t="n">
-        <v>96868</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11757,25 +11757,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503850</v>
+        <v>503434</v>
       </c>
       <c r="R105" t="n">
-        <v>7134617</v>
+        <v>7134673</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12561,10 +12561,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076639</v>
+        <v>120076610</v>
       </c>
       <c r="B113" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12573,25 +12573,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503430</v>
+        <v>503592</v>
       </c>
       <c r="R113" t="n">
-        <v>7134677</v>
+        <v>7134781</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12867,10 +12867,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076610</v>
+        <v>120076639</v>
       </c>
       <c r="B116" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12879,25 +12879,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503592</v>
+        <v>503430</v>
       </c>
       <c r="R116" t="n">
-        <v>7134781</v>
+        <v>7134677</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13479,10 +13479,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076626</v>
+        <v>120076649</v>
       </c>
       <c r="B122" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13495,21 +13495,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503534</v>
+        <v>503835</v>
       </c>
       <c r="R122" t="n">
-        <v>7134804</v>
+        <v>7134640</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076627</v>
+        <v>120076620</v>
       </c>
       <c r="B123" t="n">
-        <v>79607</v>
+        <v>92030</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13597,21 +13597,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503531</v>
+        <v>503618</v>
       </c>
       <c r="R123" t="n">
-        <v>7134812</v>
+        <v>7134495</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076620</v>
+        <v>120076612</v>
       </c>
       <c r="B124" t="n">
-        <v>92030</v>
+        <v>79608</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13699,21 +13699,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503618</v>
+        <v>503818</v>
       </c>
       <c r="R124" t="n">
-        <v>7134495</v>
+        <v>7134671</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13785,10 +13785,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076612</v>
+        <v>120076626</v>
       </c>
       <c r="B125" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13801,21 +13801,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503818</v>
+        <v>503534</v>
       </c>
       <c r="R125" t="n">
-        <v>7134671</v>
+        <v>7134804</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13887,10 +13887,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076649</v>
+        <v>120076627</v>
       </c>
       <c r="B126" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13903,21 +13903,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503835</v>
+        <v>503531</v>
       </c>
       <c r="R126" t="n">
-        <v>7134640</v>
+        <v>7134812</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13989,10 +13989,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076635</v>
+        <v>120076616</v>
       </c>
       <c r="B127" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14005,21 +14005,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14029,10 +14029,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503426</v>
+        <v>503430</v>
       </c>
       <c r="R127" t="n">
-        <v>7134704</v>
+        <v>7134700</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14091,10 +14091,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120065097</v>
+        <v>120076635</v>
       </c>
       <c r="B128" t="n">
-        <v>91886</v>
+        <v>79607</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14103,44 +14103,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503748</v>
+        <v>503426</v>
       </c>
       <c r="R128" t="n">
-        <v>7134611</v>
+        <v>7134704</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14172,18 +14169,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14202,10 +14193,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076616</v>
+        <v>120065097</v>
       </c>
       <c r="B129" t="n">
-        <v>79608</v>
+        <v>91886</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14214,41 +14205,44 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>232140</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503430</v>
+        <v>503748</v>
       </c>
       <c r="R129" t="n">
-        <v>7134700</v>
+        <v>7134611</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14280,12 +14274,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14610,10 +14610,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076634</v>
+        <v>120076599</v>
       </c>
       <c r="B133" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14622,25 +14622,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14650,10 +14650,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503432</v>
+        <v>503657</v>
       </c>
       <c r="R133" t="n">
-        <v>7134696</v>
+        <v>7134513</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14814,10 +14814,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076599</v>
+        <v>120076681</v>
       </c>
       <c r="B135" t="n">
-        <v>90527</v>
+        <v>12337</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14826,25 +14826,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5447</v>
+        <v>101283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14854,10 +14854,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503657</v>
+        <v>503867</v>
       </c>
       <c r="R135" t="n">
-        <v>7134513</v>
+        <v>7134650</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14890,6 +14890,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14916,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076681</v>
+        <v>120076634</v>
       </c>
       <c r="B136" t="n">
-        <v>12337</v>
+        <v>79607</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14928,25 +14933,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14956,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503867</v>
+        <v>503432</v>
       </c>
       <c r="R136" t="n">
-        <v>7134650</v>
+        <v>7134696</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14992,11 +14997,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120038086</v>
+        <v>120036022</v>
       </c>
       <c r="B44" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5529,21 +5529,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503980</v>
+        <v>504145</v>
       </c>
       <c r="R44" t="n">
-        <v>7134422</v>
+        <v>7134441</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5717,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120035474</v>
+        <v>120038086</v>
       </c>
       <c r="B46" t="n">
-        <v>79636</v>
+        <v>78263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5729,25 +5729,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,13 +5757,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504166</v>
+        <v>503980</v>
       </c>
       <c r="R46" t="n">
-        <v>7134391</v>
+        <v>7134422</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120039375</v>
+        <v>120035871</v>
       </c>
       <c r="B47" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503988</v>
+        <v>504192</v>
       </c>
       <c r="R47" t="n">
-        <v>7134466</v>
+        <v>7134481</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120034574</v>
+        <v>120035291</v>
       </c>
       <c r="B48" t="n">
-        <v>78262</v>
+        <v>4863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5933,25 +5933,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>101675</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504224</v>
+        <v>504179</v>
       </c>
       <c r="R48" t="n">
-        <v>7134352</v>
+        <v>7134372</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5997,6 +5997,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6023,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120034826</v>
+        <v>120035622</v>
       </c>
       <c r="B49" t="n">
-        <v>91844</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6035,25 +6040,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4365</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6063,13 +6068,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504226</v>
+        <v>504165</v>
       </c>
       <c r="R49" t="n">
-        <v>7134339</v>
+        <v>7134407</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6125,10 +6130,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035622</v>
+        <v>120035768</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6141,21 +6146,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6165,10 +6170,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504165</v>
+        <v>504187</v>
       </c>
       <c r="R50" t="n">
-        <v>7134407</v>
+        <v>7134438</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6329,10 +6334,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120034479</v>
+        <v>120035868</v>
       </c>
       <c r="B52" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,21 +6350,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6369,13 +6374,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504252</v>
+        <v>504193</v>
       </c>
       <c r="R52" t="n">
-        <v>7134346</v>
+        <v>7134477</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6431,10 +6436,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120036022</v>
+        <v>120034574</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6447,21 +6452,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6471,13 +6476,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504145</v>
+        <v>504224</v>
       </c>
       <c r="R53" t="n">
-        <v>7134441</v>
+        <v>7134352</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,10 +6538,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120034383</v>
+        <v>120039375</v>
       </c>
       <c r="B54" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6549,21 +6554,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6573,10 +6578,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504257</v>
+        <v>503988</v>
       </c>
       <c r="R54" t="n">
-        <v>7134334</v>
+        <v>7134466</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6737,10 +6742,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120035768</v>
+        <v>120035460</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6753,21 +6758,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504187</v>
+        <v>504169</v>
       </c>
       <c r="R56" t="n">
-        <v>7134438</v>
+        <v>7134407</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6839,10 +6844,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035291</v>
+        <v>120034826</v>
       </c>
       <c r="B57" t="n">
-        <v>4863</v>
+        <v>91844</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6851,25 +6856,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101675</v>
+        <v>4365</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6879,13 +6884,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504179</v>
+        <v>504226</v>
       </c>
       <c r="R57" t="n">
-        <v>7134372</v>
+        <v>7134339</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6915,11 +6920,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6946,10 +6946,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120036399</v>
+        <v>120035474</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6958,25 +6958,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6986,13 +6986,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504083</v>
+        <v>504166</v>
       </c>
       <c r="R58" t="n">
-        <v>7134453</v>
+        <v>7134391</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7022,11 +7022,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7053,10 +7048,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120035460</v>
+        <v>120034479</v>
       </c>
       <c r="B59" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,21 +7064,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7093,10 +7088,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504169</v>
+        <v>504252</v>
       </c>
       <c r="R59" t="n">
-        <v>7134407</v>
+        <v>7134346</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7155,10 +7150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120035868</v>
+        <v>120036399</v>
       </c>
       <c r="B60" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,21 +7166,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,13 +7190,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504193</v>
+        <v>504083</v>
       </c>
       <c r="R60" t="n">
-        <v>7134477</v>
+        <v>7134453</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7231,6 +7226,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120035871</v>
+        <v>120034383</v>
       </c>
       <c r="B61" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504192</v>
+        <v>504257</v>
       </c>
       <c r="R61" t="n">
-        <v>7134481</v>
+        <v>7134334</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120046464</v>
+        <v>120046468</v>
       </c>
       <c r="B62" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,25 +7371,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503874</v>
+        <v>503899</v>
       </c>
       <c r="R62" t="n">
-        <v>7134566</v>
+        <v>7134531</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120046468</v>
+        <v>120039963</v>
       </c>
       <c r="B63" t="n">
         <v>97907</v>
@@ -7497,17 +7497,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503899</v>
+        <v>503904</v>
       </c>
       <c r="R63" t="n">
-        <v>7134531</v>
+        <v>7134523</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120038261</v>
+        <v>120046465</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,41 +7575,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503997</v>
+        <v>504001</v>
       </c>
       <c r="R64" t="n">
-        <v>7134441</v>
+        <v>7134466</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120046465</v>
+        <v>120046464</v>
       </c>
       <c r="B65" t="n">
         <v>78262</v>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504001</v>
+        <v>503874</v>
       </c>
       <c r="R65" t="n">
-        <v>7134466</v>
+        <v>7134566</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120039963</v>
+        <v>120038261</v>
       </c>
       <c r="B66" t="n">
         <v>97907</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503904</v>
+        <v>503997</v>
       </c>
       <c r="R66" t="n">
-        <v>7134523</v>
+        <v>7134441</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076664</v>
+        <v>120076660</v>
       </c>
       <c r="B67" t="n">
         <v>78171</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503543</v>
+        <v>503616</v>
       </c>
       <c r="R67" t="n">
-        <v>7134608</v>
+        <v>7134591</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120064794</v>
+        <v>120076629</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,41 +7983,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503729</v>
+        <v>503568</v>
       </c>
       <c r="R68" t="n">
-        <v>7134606</v>
+        <v>7134773</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076653</v>
+        <v>120076647</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503608</v>
+        <v>503790</v>
       </c>
       <c r="R69" t="n">
-        <v>7134763</v>
+        <v>7134698</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076641</v>
+        <v>120065097</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>91886</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,41 +8187,44 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503745</v>
+        <v>503748</v>
       </c>
       <c r="R70" t="n">
-        <v>7134697</v>
+        <v>7134611</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8253,12 +8256,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8277,10 +8286,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076646</v>
+        <v>120076625</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8298,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8326,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503675</v>
+        <v>503539</v>
       </c>
       <c r="R71" t="n">
-        <v>7134737</v>
+        <v>7134558</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8388,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076633</v>
+        <v>120076601</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>79115</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,21 +8404,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8428,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503430</v>
+        <v>503546</v>
       </c>
       <c r="R72" t="n">
-        <v>7134677</v>
+        <v>7134565</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8490,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076645</v>
+        <v>120076612</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8502,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8530,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503601</v>
+        <v>503818</v>
       </c>
       <c r="R73" t="n">
-        <v>7134773</v>
+        <v>7134671</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8592,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076608</v>
+        <v>120076681</v>
       </c>
       <c r="B74" t="n">
-        <v>79608</v>
+        <v>12337</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8604,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>101283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8632,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503530</v>
+        <v>503867</v>
       </c>
       <c r="R74" t="n">
-        <v>7134813</v>
+        <v>7134650</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8659,6 +8668,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8685,10 +8699,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076628</v>
+        <v>120076644</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8701,21 +8715,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8739,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503570</v>
+        <v>503748</v>
       </c>
       <c r="R75" t="n">
-        <v>7134765</v>
+        <v>7134611</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8801,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076643</v>
+        <v>120076685</v>
       </c>
       <c r="B76" t="n">
-        <v>78262</v>
+        <v>79642</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8813,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8841,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503820</v>
+        <v>503819</v>
       </c>
       <c r="R76" t="n">
-        <v>7134705</v>
+        <v>7134668</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8903,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076652</v>
+        <v>120076634</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8905,21 +8919,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8943,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503526</v>
+        <v>503432</v>
       </c>
       <c r="R77" t="n">
-        <v>7134815</v>
+        <v>7134696</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +9005,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076685</v>
+        <v>120076609</v>
       </c>
       <c r="B78" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9003,25 +9017,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9045,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503819</v>
+        <v>503567</v>
       </c>
       <c r="R78" t="n">
-        <v>7134668</v>
+        <v>7134773</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9107,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076637</v>
+        <v>120076645</v>
       </c>
       <c r="B79" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9105,25 +9119,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503530</v>
+        <v>503601</v>
       </c>
       <c r="R79" t="n">
-        <v>7134806</v>
+        <v>7134773</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,10 +9209,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076636</v>
+        <v>120076676</v>
       </c>
       <c r="B80" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9211,21 +9225,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503530</v>
+        <v>503536</v>
       </c>
       <c r="R80" t="n">
-        <v>7134813</v>
+        <v>7134619</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,7 +9311,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076670</v>
+        <v>120076673</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9337,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503626</v>
+        <v>503532</v>
       </c>
       <c r="R81" t="n">
-        <v>7134549</v>
+        <v>7134595</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9413,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076674</v>
+        <v>120076630</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9411,25 +9425,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503558</v>
+        <v>503592</v>
       </c>
       <c r="R82" t="n">
-        <v>7134614</v>
+        <v>7134781</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9515,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120060142</v>
+        <v>120076686</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>79642</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9517,37 +9531,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503497</v>
+        <v>503428</v>
       </c>
       <c r="R83" t="n">
-        <v>7134657</v>
+        <v>7134677</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9603,10 +9617,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076677</v>
+        <v>120076665</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9615,25 +9629,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503481</v>
+        <v>503480</v>
       </c>
       <c r="R84" t="n">
-        <v>7134655</v>
+        <v>7134647</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9719,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076672</v>
+        <v>120076649</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>90558</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9717,25 +9731,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503543</v>
+        <v>503835</v>
       </c>
       <c r="R85" t="n">
-        <v>7134573</v>
+        <v>7134640</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9821,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076648</v>
+        <v>120076619</v>
       </c>
       <c r="B86" t="n">
-        <v>89230</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9819,25 +9833,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1596</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9861,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503495</v>
+        <v>503460</v>
       </c>
       <c r="R86" t="n">
-        <v>7134638</v>
+        <v>7134749</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9909,10 +9923,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076631</v>
+        <v>120060142</v>
       </c>
       <c r="B87" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9921,41 +9935,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503624</v>
+        <v>503497</v>
       </c>
       <c r="R87" t="n">
-        <v>7134757</v>
+        <v>7134657</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10011,7 +10025,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076638</v>
+        <v>120076639</v>
       </c>
       <c r="B88" t="n">
         <v>79643</v>
@@ -10051,10 +10065,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503819</v>
+        <v>503430</v>
       </c>
       <c r="R88" t="n">
-        <v>7134668</v>
+        <v>7134677</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10127,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076613</v>
+        <v>120076624</v>
       </c>
       <c r="B89" t="n">
-        <v>79608</v>
+        <v>78263</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10143,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503646</v>
+        <v>503630</v>
       </c>
       <c r="R89" t="n">
-        <v>7134570</v>
+        <v>7134529</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10229,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076609</v>
+        <v>120076602</v>
       </c>
       <c r="B90" t="n">
-        <v>79608</v>
+        <v>89633</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10231,21 +10245,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10269,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503567</v>
+        <v>503489</v>
       </c>
       <c r="R90" t="n">
-        <v>7134773</v>
+        <v>7134637</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10331,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076660</v>
+        <v>120076617</v>
       </c>
       <c r="B91" t="n">
-        <v>78171</v>
+        <v>96868</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10329,25 +10343,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503616</v>
+        <v>503847</v>
       </c>
       <c r="R91" t="n">
-        <v>7134591</v>
+        <v>7134693</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10419,10 +10433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076675</v>
+        <v>120076626</v>
       </c>
       <c r="B92" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10431,25 +10445,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10459,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503542</v>
+        <v>503534</v>
       </c>
       <c r="R92" t="n">
-        <v>7134610</v>
+        <v>7134804</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10521,10 +10535,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076647</v>
+        <v>120076675</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10533,25 +10547,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10561,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503790</v>
+        <v>503542</v>
       </c>
       <c r="R93" t="n">
-        <v>7134698</v>
+        <v>7134610</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10623,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076661</v>
+        <v>120076641</v>
       </c>
       <c r="B94" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10639,21 +10653,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10663,10 +10677,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503604</v>
+        <v>503745</v>
       </c>
       <c r="R94" t="n">
-        <v>7134590</v>
+        <v>7134697</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10725,10 +10739,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076654</v>
+        <v>120076620</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10741,21 +10755,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10779,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503821</v>
+        <v>503618</v>
       </c>
       <c r="R95" t="n">
-        <v>7134659</v>
+        <v>7134495</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10827,10 +10841,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076640</v>
+        <v>120076606</v>
       </c>
       <c r="B96" t="n">
-        <v>78262</v>
+        <v>79636</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10839,25 +10853,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10867,10 +10881,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503654</v>
+        <v>503427</v>
       </c>
       <c r="R96" t="n">
-        <v>7134725</v>
+        <v>7134680</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10943,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076601</v>
+        <v>120076648</v>
       </c>
       <c r="B97" t="n">
-        <v>79115</v>
+        <v>89230</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10941,25 +10955,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>1596</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10983,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503546</v>
+        <v>503495</v>
       </c>
       <c r="R97" t="n">
-        <v>7134565</v>
+        <v>7134638</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11031,10 +11045,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076611</v>
+        <v>120076684</v>
       </c>
       <c r="B98" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11043,25 +11057,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11071,10 +11085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503691</v>
+        <v>503568</v>
       </c>
       <c r="R98" t="n">
-        <v>7134749</v>
+        <v>7134774</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11133,10 +11147,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076630</v>
+        <v>120076614</v>
       </c>
       <c r="B99" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11149,21 +11163,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11173,10 +11187,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503592</v>
+        <v>503427</v>
       </c>
       <c r="R99" t="n">
-        <v>7134781</v>
+        <v>7134675</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11235,10 +11249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076684</v>
+        <v>120076611</v>
       </c>
       <c r="B100" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11247,25 +11261,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11275,10 +11289,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503568</v>
+        <v>503691</v>
       </c>
       <c r="R100" t="n">
-        <v>7134774</v>
+        <v>7134749</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11337,10 +11351,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076618</v>
+        <v>120076674</v>
       </c>
       <c r="B101" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11353,21 +11367,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11377,10 +11391,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503850</v>
+        <v>503558</v>
       </c>
       <c r="R101" t="n">
-        <v>7134617</v>
+        <v>7134614</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11439,10 +11453,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076662</v>
+        <v>120076652</v>
       </c>
       <c r="B102" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11455,21 +11469,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11479,10 +11493,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503535</v>
+        <v>503526</v>
       </c>
       <c r="R102" t="n">
-        <v>7134599</v>
+        <v>7134815</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11541,7 +11555,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076606</v>
+        <v>120076605</v>
       </c>
       <c r="B103" t="n">
         <v>79636</v>
@@ -11581,10 +11595,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503427</v>
+        <v>503568</v>
       </c>
       <c r="R103" t="n">
-        <v>7134680</v>
+        <v>7134774</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11643,7 +11657,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076629</v>
+        <v>120076633</v>
       </c>
       <c r="B104" t="n">
         <v>79607</v>
@@ -11683,10 +11697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503568</v>
+        <v>503430</v>
       </c>
       <c r="R104" t="n">
-        <v>7134773</v>
+        <v>7134677</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11745,10 +11759,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076632</v>
+        <v>120076687</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>91834</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11761,21 +11775,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11785,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503434</v>
+        <v>503491</v>
       </c>
       <c r="R105" t="n">
-        <v>7134673</v>
+        <v>7134636</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11847,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076605</v>
+        <v>120076638</v>
       </c>
       <c r="B106" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11863,21 +11877,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11887,10 +11901,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503568</v>
+        <v>503819</v>
       </c>
       <c r="R106" t="n">
-        <v>7134774</v>
+        <v>7134668</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11949,10 +11963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076671</v>
+        <v>120076623</v>
       </c>
       <c r="B107" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11961,25 +11975,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11989,10 +12003,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503546</v>
+        <v>503665</v>
       </c>
       <c r="R107" t="n">
-        <v>7134587</v>
+        <v>7134523</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12051,10 +12065,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076665</v>
+        <v>120076627</v>
       </c>
       <c r="B108" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12067,21 +12081,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12091,10 +12105,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503480</v>
+        <v>503531</v>
       </c>
       <c r="R108" t="n">
-        <v>7134647</v>
+        <v>7134812</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,10 +12167,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076619</v>
+        <v>120076615</v>
       </c>
       <c r="B109" t="n">
-        <v>91832</v>
+        <v>79608</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12169,21 +12183,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4361</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12193,10 +12207,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503460</v>
+        <v>503430</v>
       </c>
       <c r="R109" t="n">
-        <v>7134749</v>
+        <v>7134677</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12255,10 +12269,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076615</v>
+        <v>120076670</v>
       </c>
       <c r="B110" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12267,25 +12281,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12295,10 +12309,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503430</v>
+        <v>503626</v>
       </c>
       <c r="R110" t="n">
-        <v>7134677</v>
+        <v>7134549</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12357,10 +12371,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076624</v>
+        <v>120076599</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>90527</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12369,25 +12383,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12397,10 +12411,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503630</v>
+        <v>503657</v>
       </c>
       <c r="R111" t="n">
-        <v>7134529</v>
+        <v>7134513</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12459,10 +12473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076625</v>
+        <v>120076635</v>
       </c>
       <c r="B112" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12475,21 +12489,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12499,10 +12513,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503539</v>
+        <v>503426</v>
       </c>
       <c r="R112" t="n">
-        <v>7134558</v>
+        <v>7134704</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12561,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076610</v>
+        <v>120076637</v>
       </c>
       <c r="B113" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12573,25 +12587,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12601,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503592</v>
+        <v>503530</v>
       </c>
       <c r="R113" t="n">
-        <v>7134781</v>
+        <v>7134806</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12663,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076676</v>
+        <v>120076613</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12675,25 +12689,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12703,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503536</v>
+        <v>503646</v>
       </c>
       <c r="R114" t="n">
-        <v>7134619</v>
+        <v>7134570</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12765,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076673</v>
+        <v>120076616</v>
       </c>
       <c r="B115" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12777,25 +12791,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12805,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503532</v>
+        <v>503430</v>
       </c>
       <c r="R115" t="n">
-        <v>7134595</v>
+        <v>7134700</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12867,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076639</v>
+        <v>120076677</v>
       </c>
       <c r="B116" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12883,21 +12897,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12907,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503430</v>
+        <v>503481</v>
       </c>
       <c r="R116" t="n">
-        <v>7134677</v>
+        <v>7134655</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12969,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076623</v>
+        <v>120076653</v>
       </c>
       <c r="B117" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12985,21 +12999,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13009,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503665</v>
+        <v>503608</v>
       </c>
       <c r="R117" t="n">
-        <v>7134523</v>
+        <v>7134763</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13071,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076644</v>
+        <v>120076618</v>
       </c>
       <c r="B118" t="n">
-        <v>78262</v>
+        <v>96868</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13083,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13111,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503748</v>
+        <v>503850</v>
       </c>
       <c r="R118" t="n">
-        <v>7134611</v>
+        <v>7134617</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13173,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076602</v>
+        <v>120076661</v>
       </c>
       <c r="B119" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13189,21 +13203,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13213,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503489</v>
+        <v>503604</v>
       </c>
       <c r="R119" t="n">
-        <v>7134637</v>
+        <v>7134590</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13275,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076617</v>
+        <v>120076608</v>
       </c>
       <c r="B120" t="n">
-        <v>96868</v>
+        <v>79608</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13287,25 +13301,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13315,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503847</v>
+        <v>503530</v>
       </c>
       <c r="R120" t="n">
-        <v>7134693</v>
+        <v>7134813</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13377,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076687</v>
+        <v>120076651</v>
       </c>
       <c r="B121" t="n">
-        <v>91834</v>
+        <v>90712</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13389,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13417,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503491</v>
+        <v>503516</v>
       </c>
       <c r="R121" t="n">
-        <v>7134636</v>
+        <v>7134622</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13479,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076649</v>
+        <v>120076610</v>
       </c>
       <c r="B122" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13495,21 +13509,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13519,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503835</v>
+        <v>503592</v>
       </c>
       <c r="R122" t="n">
-        <v>7134640</v>
+        <v>7134781</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13581,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076620</v>
+        <v>120076654</v>
       </c>
       <c r="B123" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13597,21 +13611,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13621,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503618</v>
+        <v>503821</v>
       </c>
       <c r="R123" t="n">
-        <v>7134495</v>
+        <v>7134659</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13683,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076612</v>
+        <v>120076631</v>
       </c>
       <c r="B124" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13699,21 +13713,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13723,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503818</v>
+        <v>503624</v>
       </c>
       <c r="R124" t="n">
-        <v>7134671</v>
+        <v>7134757</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13785,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076626</v>
+        <v>120076600</v>
       </c>
       <c r="B125" t="n">
-        <v>79607</v>
+        <v>79115</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13801,21 +13815,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13825,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503534</v>
+        <v>503603</v>
       </c>
       <c r="R125" t="n">
-        <v>7134804</v>
+        <v>7134592</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13887,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076627</v>
+        <v>120076662</v>
       </c>
       <c r="B126" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13903,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13927,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503531</v>
+        <v>503535</v>
       </c>
       <c r="R126" t="n">
-        <v>7134812</v>
+        <v>7134599</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13989,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076616</v>
+        <v>120076646</v>
       </c>
       <c r="B127" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14001,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14029,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503430</v>
+        <v>503675</v>
       </c>
       <c r="R127" t="n">
-        <v>7134700</v>
+        <v>7134737</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14091,7 +14105,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076635</v>
+        <v>120076632</v>
       </c>
       <c r="B128" t="n">
         <v>79607</v>
@@ -14131,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503426</v>
+        <v>503434</v>
       </c>
       <c r="R128" t="n">
-        <v>7134704</v>
+        <v>7134673</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14193,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120065097</v>
+        <v>120076664</v>
       </c>
       <c r="B129" t="n">
-        <v>91886</v>
+        <v>78171</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14205,44 +14219,41 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>232140</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503748</v>
+        <v>503543</v>
       </c>
       <c r="R129" t="n">
-        <v>7134611</v>
+        <v>7134608</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14274,18 +14285,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14304,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076651</v>
+        <v>120076628</v>
       </c>
       <c r="B130" t="n">
-        <v>90712</v>
+        <v>79607</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14316,25 +14321,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14344,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503516</v>
+        <v>503570</v>
       </c>
       <c r="R130" t="n">
-        <v>7134622</v>
+        <v>7134765</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14406,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076650</v>
+        <v>120076640</v>
       </c>
       <c r="B131" t="n">
-        <v>90576</v>
+        <v>78262</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14422,21 +14427,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14446,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503633</v>
+        <v>503654</v>
       </c>
       <c r="R131" t="n">
-        <v>7134566</v>
+        <v>7134725</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14508,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076614</v>
+        <v>120076650</v>
       </c>
       <c r="B132" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14524,21 +14529,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14548,10 +14553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503427</v>
+        <v>503633</v>
       </c>
       <c r="R132" t="n">
-        <v>7134675</v>
+        <v>7134566</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14610,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076599</v>
+        <v>120064794</v>
       </c>
       <c r="B133" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14626,37 +14631,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503657</v>
+        <v>503729</v>
       </c>
       <c r="R133" t="n">
-        <v>7134513</v>
+        <v>7134606</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14712,10 +14717,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076686</v>
+        <v>120076643</v>
       </c>
       <c r="B134" t="n">
-        <v>79642</v>
+        <v>78262</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14724,25 +14729,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14752,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503428</v>
+        <v>503820</v>
       </c>
       <c r="R134" t="n">
-        <v>7134677</v>
+        <v>7134705</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14814,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076681</v>
+        <v>120076636</v>
       </c>
       <c r="B135" t="n">
-        <v>12337</v>
+        <v>79643</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14826,25 +14831,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>101283</v>
+        <v>6464</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14854,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503867</v>
+        <v>503530</v>
       </c>
       <c r="R135" t="n">
-        <v>7134650</v>
+        <v>7134813</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14890,11 +14895,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076634</v>
+        <v>120076671</v>
       </c>
       <c r="B136" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,25 +14933,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503432</v>
+        <v>503546</v>
       </c>
       <c r="R136" t="n">
-        <v>7134696</v>
+        <v>7134587</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076600</v>
+        <v>120076672</v>
       </c>
       <c r="B137" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15035,25 +15035,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503603</v>
+        <v>503543</v>
       </c>
       <c r="R137" t="n">
-        <v>7134592</v>
+        <v>7134573</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -7461,10 +7461,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120039963</v>
+        <v>120046465</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7473,41 +7473,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503904</v>
+        <v>504001</v>
       </c>
       <c r="R63" t="n">
-        <v>7134523</v>
+        <v>7134466</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120046465</v>
+        <v>120039963</v>
       </c>
       <c r="B64" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,41 +7575,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>504001</v>
+        <v>503904</v>
       </c>
       <c r="R64" t="n">
-        <v>7134466</v>
+        <v>7134523</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8490,10 +8490,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076612</v>
+        <v>120076685</v>
       </c>
       <c r="B73" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8502,25 +8502,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503818</v>
+        <v>503819</v>
       </c>
       <c r="R73" t="n">
-        <v>7134671</v>
+        <v>7134668</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8592,10 +8592,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076681</v>
+        <v>120076634</v>
       </c>
       <c r="B74" t="n">
-        <v>12337</v>
+        <v>79607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8604,25 +8604,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503867</v>
+        <v>503432</v>
       </c>
       <c r="R74" t="n">
-        <v>7134650</v>
+        <v>7134696</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8668,11 +8668,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8699,10 +8694,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076644</v>
+        <v>120076681</v>
       </c>
       <c r="B75" t="n">
-        <v>78262</v>
+        <v>12337</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8711,25 +8706,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>101283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8739,10 +8734,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503748</v>
+        <v>503867</v>
       </c>
       <c r="R75" t="n">
-        <v>7134611</v>
+        <v>7134650</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8775,6 +8770,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8801,10 +8801,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076685</v>
+        <v>120076612</v>
       </c>
       <c r="B76" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8813,25 +8813,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503819</v>
+        <v>503818</v>
       </c>
       <c r="R76" t="n">
-        <v>7134668</v>
+        <v>7134671</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076634</v>
+        <v>120076644</v>
       </c>
       <c r="B77" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8919,21 +8919,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503432</v>
+        <v>503748</v>
       </c>
       <c r="R77" t="n">
-        <v>7134696</v>
+        <v>7134611</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076609</v>
+        <v>120076645</v>
       </c>
       <c r="B78" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9017,25 +9017,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503567</v>
+        <v>503601</v>
       </c>
       <c r="R78" t="n">
         <v>7134773</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076645</v>
+        <v>120076609</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9119,25 +9119,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503601</v>
+        <v>503567</v>
       </c>
       <c r="R79" t="n">
         <v>7134773</v>
@@ -11759,10 +11759,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076687</v>
+        <v>120076638</v>
       </c>
       <c r="B105" t="n">
-        <v>91834</v>
+        <v>79643</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11771,25 +11771,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503491</v>
+        <v>503819</v>
       </c>
       <c r="R105" t="n">
-        <v>7134636</v>
+        <v>7134668</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11861,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076638</v>
+        <v>120076687</v>
       </c>
       <c r="B106" t="n">
-        <v>79643</v>
+        <v>91834</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11873,25 +11873,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503819</v>
+        <v>503491</v>
       </c>
       <c r="R106" t="n">
-        <v>7134668</v>
+        <v>7134636</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076661</v>
+        <v>120076654</v>
       </c>
       <c r="B119" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13203,21 +13203,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503604</v>
+        <v>503821</v>
       </c>
       <c r="R119" t="n">
-        <v>7134590</v>
+        <v>7134659</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076608</v>
+        <v>120076631</v>
       </c>
       <c r="B120" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13305,21 +13305,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503530</v>
+        <v>503624</v>
       </c>
       <c r="R120" t="n">
-        <v>7134813</v>
+        <v>7134757</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076651</v>
+        <v>120076661</v>
       </c>
       <c r="B121" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503516</v>
+        <v>503604</v>
       </c>
       <c r="R121" t="n">
-        <v>7134622</v>
+        <v>7134590</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,7 +13493,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076610</v>
+        <v>120076608</v>
       </c>
       <c r="B122" t="n">
         <v>79608</v>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503592</v>
+        <v>503530</v>
       </c>
       <c r="R122" t="n">
-        <v>7134781</v>
+        <v>7134813</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076654</v>
+        <v>120076651</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13607,25 +13607,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503821</v>
+        <v>503516</v>
       </c>
       <c r="R123" t="n">
-        <v>7134659</v>
+        <v>7134622</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076631</v>
+        <v>120076610</v>
       </c>
       <c r="B124" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13713,21 +13713,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503624</v>
+        <v>503592</v>
       </c>
       <c r="R124" t="n">
-        <v>7134757</v>
+        <v>7134781</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076600</v>
+        <v>120076646</v>
       </c>
       <c r="B125" t="n">
-        <v>79115</v>
+        <v>97907</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,25 +13811,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503603</v>
+        <v>503675</v>
       </c>
       <c r="R125" t="n">
-        <v>7134592</v>
+        <v>7134737</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076646</v>
+        <v>120076600</v>
       </c>
       <c r="B127" t="n">
-        <v>97907</v>
+        <v>79115</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503675</v>
+        <v>503603</v>
       </c>
       <c r="R127" t="n">
-        <v>7134737</v>
+        <v>7134592</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,7 +5513,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120036022</v>
+        <v>120035768</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504145</v>
+        <v>504187</v>
       </c>
       <c r="R44" t="n">
-        <v>7134441</v>
+        <v>7134438</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040383</v>
+        <v>120036022</v>
       </c>
       <c r="B45" t="n">
-        <v>90807</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5627,38 +5627,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503879</v>
+        <v>504145</v>
       </c>
       <c r="R45" t="n">
-        <v>7134575</v>
+        <v>7134441</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5717,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120038086</v>
+        <v>120035474</v>
       </c>
       <c r="B46" t="n">
-        <v>78263</v>
+        <v>79636</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5729,25 +5729,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,13 +5757,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503980</v>
+        <v>504166</v>
       </c>
       <c r="R46" t="n">
-        <v>7134422</v>
+        <v>7134391</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120035871</v>
+        <v>120034826</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504192</v>
+        <v>504226</v>
       </c>
       <c r="R47" t="n">
-        <v>7134481</v>
+        <v>7134339</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035291</v>
+        <v>120039375</v>
       </c>
       <c r="B48" t="n">
-        <v>4863</v>
+        <v>78262</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5933,25 +5933,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101675</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,13 +5961,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504179</v>
+        <v>503988</v>
       </c>
       <c r="R48" t="n">
-        <v>7134372</v>
+        <v>7134466</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5997,11 +5997,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6028,10 +6023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035622</v>
+        <v>120035291</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>4863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6040,25 +6035,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>101675</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504165</v>
+        <v>504179</v>
       </c>
       <c r="R49" t="n">
-        <v>7134407</v>
+        <v>7134372</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6104,6 +6099,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6130,10 +6130,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035768</v>
+        <v>120038086</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6146,21 +6146,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,13 +6170,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504187</v>
+        <v>503980</v>
       </c>
       <c r="R50" t="n">
-        <v>7134438</v>
+        <v>7134422</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6334,10 +6334,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120035868</v>
+        <v>120036399</v>
       </c>
       <c r="B52" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6350,21 +6350,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6374,13 +6374,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504193</v>
+        <v>504083</v>
       </c>
       <c r="R52" t="n">
-        <v>7134477</v>
+        <v>7134453</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6410,6 +6410,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6538,10 +6543,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120039375</v>
+        <v>120035871</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6554,21 +6559,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6578,10 +6583,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503988</v>
+        <v>504192</v>
       </c>
       <c r="R54" t="n">
-        <v>7134466</v>
+        <v>7134481</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6640,10 +6645,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120035015</v>
+        <v>120040383</v>
       </c>
       <c r="B55" t="n">
-        <v>78262</v>
+        <v>90807</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6652,41 +6657,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504196</v>
+        <v>503879</v>
       </c>
       <c r="R55" t="n">
-        <v>7134350</v>
+        <v>7134575</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6742,10 +6747,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120035460</v>
+        <v>120034383</v>
       </c>
       <c r="B56" t="n">
-        <v>79608</v>
+        <v>78263</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6758,21 +6763,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6782,13 +6787,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504169</v>
+        <v>504257</v>
       </c>
       <c r="R56" t="n">
-        <v>7134407</v>
+        <v>7134334</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6844,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120034826</v>
+        <v>120035868</v>
       </c>
       <c r="B57" t="n">
-        <v>91844</v>
+        <v>78263</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6856,25 +6861,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4365</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504226</v>
+        <v>504193</v>
       </c>
       <c r="R57" t="n">
-        <v>7134339</v>
+        <v>7134477</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6946,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120035474</v>
+        <v>120034479</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>78262</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6958,25 +6963,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6986,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504166</v>
+        <v>504252</v>
       </c>
       <c r="R58" t="n">
-        <v>7134391</v>
+        <v>7134346</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7048,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120034479</v>
+        <v>120035460</v>
       </c>
       <c r="B59" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7064,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7088,10 +7093,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504252</v>
+        <v>504169</v>
       </c>
       <c r="R59" t="n">
-        <v>7134346</v>
+        <v>7134407</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7150,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120036399</v>
+        <v>120035015</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7166,21 +7171,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504083</v>
+        <v>504196</v>
       </c>
       <c r="R60" t="n">
-        <v>7134453</v>
+        <v>7134350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7226,11 +7231,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120034383</v>
+        <v>120035622</v>
       </c>
       <c r="B61" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504257</v>
+        <v>504165</v>
       </c>
       <c r="R61" t="n">
-        <v>7134334</v>
+        <v>7134407</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120046468</v>
+        <v>120039963</v>
       </c>
       <c r="B62" t="n">
         <v>97907</v>
@@ -7395,17 +7395,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503899</v>
+        <v>503904</v>
       </c>
       <c r="R62" t="n">
-        <v>7134531</v>
+        <v>7134523</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120046465</v>
+        <v>120046464</v>
       </c>
       <c r="B63" t="n">
         <v>78262</v>
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504001</v>
+        <v>503874</v>
       </c>
       <c r="R63" t="n">
-        <v>7134466</v>
+        <v>7134566</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120039963</v>
+        <v>120038261</v>
       </c>
       <c r="B64" t="n">
         <v>97907</v>
@@ -7603,13 +7603,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503904</v>
+        <v>503997</v>
       </c>
       <c r="R64" t="n">
-        <v>7134523</v>
+        <v>7134441</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120046464</v>
+        <v>120046465</v>
       </c>
       <c r="B65" t="n">
         <v>78262</v>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503874</v>
+        <v>504001</v>
       </c>
       <c r="R65" t="n">
-        <v>7134566</v>
+        <v>7134466</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120038261</v>
+        <v>120046468</v>
       </c>
       <c r="B66" t="n">
         <v>97907</v>
@@ -7803,17 +7803,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503997</v>
+        <v>503899</v>
       </c>
       <c r="R66" t="n">
-        <v>7134441</v>
+        <v>7134531</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076660</v>
+        <v>120076677</v>
       </c>
       <c r="B67" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503616</v>
+        <v>503481</v>
       </c>
       <c r="R67" t="n">
-        <v>7134591</v>
+        <v>7134655</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076629</v>
+        <v>120076660</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503568</v>
+        <v>503616</v>
       </c>
       <c r="R68" t="n">
-        <v>7134773</v>
+        <v>7134591</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076647</v>
+        <v>120076614</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503790</v>
+        <v>503427</v>
       </c>
       <c r="R69" t="n">
-        <v>7134698</v>
+        <v>7134675</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120065097</v>
+        <v>120076602</v>
       </c>
       <c r="B70" t="n">
-        <v>91886</v>
+        <v>89633</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,44 +8187,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503748</v>
+        <v>503489</v>
       </c>
       <c r="R70" t="n">
-        <v>7134611</v>
+        <v>7134637</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8256,18 +8253,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8286,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076625</v>
+        <v>120076617</v>
       </c>
       <c r="B71" t="n">
-        <v>78263</v>
+        <v>96868</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8298,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8326,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503539</v>
+        <v>503847</v>
       </c>
       <c r="R71" t="n">
-        <v>7134558</v>
+        <v>7134693</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8388,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076601</v>
+        <v>120076618</v>
       </c>
       <c r="B72" t="n">
-        <v>79115</v>
+        <v>96868</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8400,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8428,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503546</v>
+        <v>503850</v>
       </c>
       <c r="R72" t="n">
-        <v>7134565</v>
+        <v>7134617</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8490,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076685</v>
+        <v>120076675</v>
       </c>
       <c r="B73" t="n">
-        <v>79642</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8506,21 +8497,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8530,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503819</v>
+        <v>503542</v>
       </c>
       <c r="R73" t="n">
-        <v>7134668</v>
+        <v>7134610</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8592,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076634</v>
+        <v>120076625</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8608,21 +8599,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8632,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503432</v>
+        <v>503539</v>
       </c>
       <c r="R74" t="n">
-        <v>7134696</v>
+        <v>7134558</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8694,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076681</v>
+        <v>120076637</v>
       </c>
       <c r="B75" t="n">
-        <v>12337</v>
+        <v>79643</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8706,25 +8697,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>101283</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8734,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503867</v>
+        <v>503530</v>
       </c>
       <c r="R75" t="n">
-        <v>7134650</v>
+        <v>7134806</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8770,11 +8761,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8801,7 +8787,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076612</v>
+        <v>120076609</v>
       </c>
       <c r="B76" t="n">
         <v>79608</v>
@@ -8841,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503818</v>
+        <v>503567</v>
       </c>
       <c r="R76" t="n">
-        <v>7134671</v>
+        <v>7134773</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8903,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076644</v>
+        <v>120076611</v>
       </c>
       <c r="B77" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8919,21 +8905,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8943,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503748</v>
+        <v>503691</v>
       </c>
       <c r="R77" t="n">
-        <v>7134611</v>
+        <v>7134749</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9005,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076645</v>
+        <v>120076673</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9017,25 +9003,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9045,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503601</v>
+        <v>503532</v>
       </c>
       <c r="R78" t="n">
-        <v>7134773</v>
+        <v>7134595</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9107,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076609</v>
+        <v>120076605</v>
       </c>
       <c r="B79" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9119,25 +9105,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9147,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503567</v>
+        <v>503568</v>
       </c>
       <c r="R79" t="n">
-        <v>7134773</v>
+        <v>7134774</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9209,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076676</v>
+        <v>120076624</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9221,25 +9207,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503536</v>
+        <v>503630</v>
       </c>
       <c r="R80" t="n">
-        <v>7134619</v>
+        <v>7134529</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9311,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076673</v>
+        <v>120076664</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9323,25 +9309,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503532</v>
+        <v>503543</v>
       </c>
       <c r="R81" t="n">
-        <v>7134595</v>
+        <v>7134608</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9413,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076630</v>
+        <v>120076662</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9429,21 +9415,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9453,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503592</v>
+        <v>503535</v>
       </c>
       <c r="R82" t="n">
-        <v>7134781</v>
+        <v>7134599</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9515,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076686</v>
+        <v>120076631</v>
       </c>
       <c r="B83" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9527,25 +9513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9555,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503428</v>
+        <v>503624</v>
       </c>
       <c r="R83" t="n">
-        <v>7134677</v>
+        <v>7134757</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9617,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076665</v>
+        <v>120076612</v>
       </c>
       <c r="B84" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9633,21 +9619,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9657,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503480</v>
+        <v>503818</v>
       </c>
       <c r="R84" t="n">
-        <v>7134647</v>
+        <v>7134671</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9719,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076649</v>
+        <v>120076606</v>
       </c>
       <c r="B85" t="n">
-        <v>90558</v>
+        <v>79636</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9731,25 +9717,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9759,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503835</v>
+        <v>503427</v>
       </c>
       <c r="R85" t="n">
-        <v>7134640</v>
+        <v>7134680</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9821,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076619</v>
+        <v>120076687</v>
       </c>
       <c r="B86" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9837,21 +9823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9861,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503460</v>
+        <v>503491</v>
       </c>
       <c r="R86" t="n">
-        <v>7134749</v>
+        <v>7134636</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9923,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120060142</v>
+        <v>120076641</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9935,41 +9921,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503497</v>
+        <v>503745</v>
       </c>
       <c r="R87" t="n">
-        <v>7134657</v>
+        <v>7134697</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10025,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076639</v>
+        <v>120076613</v>
       </c>
       <c r="B88" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10037,25 +10023,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10065,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503430</v>
+        <v>503646</v>
       </c>
       <c r="R88" t="n">
-        <v>7134677</v>
+        <v>7134570</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10127,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076624</v>
+        <v>120076619</v>
       </c>
       <c r="B89" t="n">
-        <v>78263</v>
+        <v>91832</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10143,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10167,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503630</v>
+        <v>503460</v>
       </c>
       <c r="R89" t="n">
-        <v>7134529</v>
+        <v>7134749</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10229,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076602</v>
+        <v>120076601</v>
       </c>
       <c r="B90" t="n">
-        <v>89633</v>
+        <v>79115</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10245,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10269,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503489</v>
+        <v>503546</v>
       </c>
       <c r="R90" t="n">
-        <v>7134637</v>
+        <v>7134565</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10331,10 +10317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076617</v>
+        <v>120076626</v>
       </c>
       <c r="B91" t="n">
-        <v>96868</v>
+        <v>79607</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10343,25 +10329,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503847</v>
+        <v>503534</v>
       </c>
       <c r="R91" t="n">
-        <v>7134693</v>
+        <v>7134804</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10433,7 +10419,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076626</v>
+        <v>120076635</v>
       </c>
       <c r="B92" t="n">
         <v>79607</v>
@@ -10473,10 +10459,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503534</v>
+        <v>503426</v>
       </c>
       <c r="R92" t="n">
-        <v>7134804</v>
+        <v>7134704</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10535,10 +10521,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076675</v>
+        <v>120076630</v>
       </c>
       <c r="B93" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10547,25 +10533,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10561,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503542</v>
+        <v>503592</v>
       </c>
       <c r="R93" t="n">
-        <v>7134610</v>
+        <v>7134781</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10637,10 +10623,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076641</v>
+        <v>120076646</v>
       </c>
       <c r="B94" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10649,25 +10635,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10677,10 +10663,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503745</v>
+        <v>503675</v>
       </c>
       <c r="R94" t="n">
-        <v>7134697</v>
+        <v>7134737</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10739,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076620</v>
+        <v>120076676</v>
       </c>
       <c r="B95" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10751,25 +10737,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10779,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503618</v>
+        <v>503536</v>
       </c>
       <c r="R95" t="n">
-        <v>7134495</v>
+        <v>7134619</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10841,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076606</v>
+        <v>120076608</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10853,25 +10839,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10881,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503427</v>
+        <v>503530</v>
       </c>
       <c r="R96" t="n">
-        <v>7134680</v>
+        <v>7134813</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10943,10 +10929,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076648</v>
+        <v>120076599</v>
       </c>
       <c r="B97" t="n">
-        <v>89230</v>
+        <v>90527</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10955,25 +10941,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1596</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10983,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503495</v>
+        <v>503657</v>
       </c>
       <c r="R97" t="n">
-        <v>7134638</v>
+        <v>7134513</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11045,10 +11031,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076684</v>
+        <v>120076638</v>
       </c>
       <c r="B98" t="n">
-        <v>79642</v>
+        <v>79643</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11061,21 +11047,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11085,10 +11071,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503568</v>
+        <v>503819</v>
       </c>
       <c r="R98" t="n">
-        <v>7134774</v>
+        <v>7134668</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11147,10 +11133,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076614</v>
+        <v>120076647</v>
       </c>
       <c r="B99" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11159,25 +11145,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11187,10 +11173,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503427</v>
+        <v>503790</v>
       </c>
       <c r="R99" t="n">
-        <v>7134675</v>
+        <v>7134698</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11249,10 +11235,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076611</v>
+        <v>120076627</v>
       </c>
       <c r="B100" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11265,21 +11251,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11289,10 +11275,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503691</v>
+        <v>503531</v>
       </c>
       <c r="R100" t="n">
-        <v>7134749</v>
+        <v>7134812</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11351,10 +11337,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076674</v>
+        <v>120076623</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11363,25 +11349,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11391,10 +11377,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503558</v>
+        <v>503665</v>
       </c>
       <c r="R101" t="n">
-        <v>7134614</v>
+        <v>7134523</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11453,10 +11439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076652</v>
+        <v>120076628</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11469,21 +11455,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11493,10 +11479,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503526</v>
+        <v>503570</v>
       </c>
       <c r="R102" t="n">
-        <v>7134815</v>
+        <v>7134765</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11555,10 +11541,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076605</v>
+        <v>120076684</v>
       </c>
       <c r="B103" t="n">
-        <v>79636</v>
+        <v>79642</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11571,21 +11557,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11657,10 +11643,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076633</v>
+        <v>120076636</v>
       </c>
       <c r="B104" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11669,25 +11655,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11697,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503430</v>
+        <v>503530</v>
       </c>
       <c r="R104" t="n">
-        <v>7134677</v>
+        <v>7134813</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11759,10 +11745,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076638</v>
+        <v>120076616</v>
       </c>
       <c r="B105" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11771,25 +11757,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11799,10 +11785,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503819</v>
+        <v>503430</v>
       </c>
       <c r="R105" t="n">
-        <v>7134668</v>
+        <v>7134700</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11861,10 +11847,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076687</v>
+        <v>120064794</v>
       </c>
       <c r="B106" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11873,41 +11859,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503491</v>
+        <v>503729</v>
       </c>
       <c r="R106" t="n">
-        <v>7134636</v>
+        <v>7134606</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11963,10 +11949,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076623</v>
+        <v>120076644</v>
       </c>
       <c r="B107" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11979,21 +11965,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12003,10 +11989,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503665</v>
+        <v>503748</v>
       </c>
       <c r="R107" t="n">
-        <v>7134523</v>
+        <v>7134611</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12065,10 +12051,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076627</v>
+        <v>120076681</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>12337</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12077,25 +12063,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>101283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12105,10 +12091,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503531</v>
+        <v>503867</v>
       </c>
       <c r="R108" t="n">
-        <v>7134812</v>
+        <v>7134650</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12141,6 +12127,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12167,10 +12158,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076615</v>
+        <v>120076620</v>
       </c>
       <c r="B109" t="n">
-        <v>79608</v>
+        <v>92030</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12183,21 +12174,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12207,10 +12198,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503430</v>
+        <v>503618</v>
       </c>
       <c r="R109" t="n">
-        <v>7134677</v>
+        <v>7134495</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12269,10 +12260,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076670</v>
+        <v>120076661</v>
       </c>
       <c r="B110" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12281,25 +12272,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12309,10 +12300,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503626</v>
+        <v>503604</v>
       </c>
       <c r="R110" t="n">
-        <v>7134549</v>
+        <v>7134590</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12371,10 +12362,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076599</v>
+        <v>120076634</v>
       </c>
       <c r="B111" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12383,25 +12374,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12411,10 +12402,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503657</v>
+        <v>503432</v>
       </c>
       <c r="R111" t="n">
-        <v>7134513</v>
+        <v>7134696</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12473,10 +12464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076635</v>
+        <v>120076643</v>
       </c>
       <c r="B112" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12489,21 +12480,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12504,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503426</v>
+        <v>503820</v>
       </c>
       <c r="R112" t="n">
-        <v>7134704</v>
+        <v>7134705</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,7 +12566,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076637</v>
+        <v>120076639</v>
       </c>
       <c r="B113" t="n">
         <v>79643</v>
@@ -12615,10 +12606,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503530</v>
+        <v>503430</v>
       </c>
       <c r="R113" t="n">
-        <v>7134806</v>
+        <v>7134677</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12668,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076613</v>
+        <v>120076649</v>
       </c>
       <c r="B114" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12693,21 +12684,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12708,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503646</v>
+        <v>503835</v>
       </c>
       <c r="R114" t="n">
-        <v>7134570</v>
+        <v>7134640</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12770,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076616</v>
+        <v>120065097</v>
       </c>
       <c r="B115" t="n">
-        <v>79608</v>
+        <v>91886</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12791,41 +12782,44 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>232140</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503430</v>
+        <v>503748</v>
       </c>
       <c r="R115" t="n">
-        <v>7134700</v>
+        <v>7134611</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12857,12 +12851,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076677</v>
+        <v>120076632</v>
       </c>
       <c r="B116" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12893,25 +12893,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503481</v>
+        <v>503434</v>
       </c>
       <c r="R116" t="n">
-        <v>7134655</v>
+        <v>7134673</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076653</v>
+        <v>120076648</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>89230</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12995,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503608</v>
+        <v>503495</v>
       </c>
       <c r="R117" t="n">
-        <v>7134763</v>
+        <v>7134638</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076618</v>
+        <v>120076654</v>
       </c>
       <c r="B118" t="n">
-        <v>96868</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503850</v>
+        <v>503821</v>
       </c>
       <c r="R118" t="n">
-        <v>7134617</v>
+        <v>7134659</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,7 +13187,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076654</v>
+        <v>120076653</v>
       </c>
       <c r="B119" t="n">
         <v>78526</v>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503821</v>
+        <v>503608</v>
       </c>
       <c r="R119" t="n">
-        <v>7134659</v>
+        <v>7134763</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076631</v>
+        <v>120076670</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13301,25 +13301,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503624</v>
+        <v>503626</v>
       </c>
       <c r="R120" t="n">
-        <v>7134757</v>
+        <v>7134549</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076661</v>
+        <v>120076674</v>
       </c>
       <c r="B121" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503604</v>
+        <v>503558</v>
       </c>
       <c r="R121" t="n">
-        <v>7134590</v>
+        <v>7134614</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076608</v>
+        <v>120076672</v>
       </c>
       <c r="B122" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503530</v>
+        <v>503543</v>
       </c>
       <c r="R122" t="n">
-        <v>7134813</v>
+        <v>7134573</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076651</v>
+        <v>120076685</v>
       </c>
       <c r="B123" t="n">
-        <v>90712</v>
+        <v>79642</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13607,25 +13607,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503516</v>
+        <v>503819</v>
       </c>
       <c r="R123" t="n">
-        <v>7134622</v>
+        <v>7134668</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076610</v>
+        <v>120076629</v>
       </c>
       <c r="B124" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13713,21 +13713,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503592</v>
+        <v>503568</v>
       </c>
       <c r="R124" t="n">
-        <v>7134781</v>
+        <v>7134773</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076646</v>
+        <v>120076686</v>
       </c>
       <c r="B125" t="n">
-        <v>97907</v>
+        <v>79642</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,25 +13811,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503675</v>
+        <v>503428</v>
       </c>
       <c r="R125" t="n">
-        <v>7134737</v>
+        <v>7134677</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076662</v>
+        <v>120076600</v>
       </c>
       <c r="B126" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503535</v>
+        <v>503603</v>
       </c>
       <c r="R126" t="n">
-        <v>7134599</v>
+        <v>7134592</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076600</v>
+        <v>120076615</v>
       </c>
       <c r="B127" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14019,21 +14019,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503603</v>
+        <v>503430</v>
       </c>
       <c r="R127" t="n">
-        <v>7134592</v>
+        <v>7134677</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076632</v>
+        <v>120076651</v>
       </c>
       <c r="B128" t="n">
-        <v>79607</v>
+        <v>90712</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14117,25 +14117,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503434</v>
+        <v>503516</v>
       </c>
       <c r="R128" t="n">
-        <v>7134673</v>
+        <v>7134622</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076664</v>
+        <v>120076610</v>
       </c>
       <c r="B129" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503543</v>
+        <v>503592</v>
       </c>
       <c r="R129" t="n">
-        <v>7134608</v>
+        <v>7134781</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076628</v>
+        <v>120076665</v>
       </c>
       <c r="B130" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14325,21 +14325,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503570</v>
+        <v>503480</v>
       </c>
       <c r="R130" t="n">
-        <v>7134765</v>
+        <v>7134647</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076640</v>
+        <v>120076671</v>
       </c>
       <c r="B131" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14423,25 +14423,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503654</v>
+        <v>503546</v>
       </c>
       <c r="R131" t="n">
-        <v>7134725</v>
+        <v>7134587</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076650</v>
+        <v>120060142</v>
       </c>
       <c r="B132" t="n">
-        <v>90576</v>
+        <v>91840</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14525,41 +14525,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503633</v>
+        <v>503497</v>
       </c>
       <c r="R132" t="n">
-        <v>7134566</v>
+        <v>7134657</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14615,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120064794</v>
+        <v>120076652</v>
       </c>
       <c r="B133" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14627,41 +14627,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503729</v>
+        <v>503526</v>
       </c>
       <c r="R133" t="n">
-        <v>7134606</v>
+        <v>7134815</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076643</v>
+        <v>120076640</v>
       </c>
       <c r="B134" t="n">
         <v>78262</v>
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503820</v>
+        <v>503654</v>
       </c>
       <c r="R134" t="n">
-        <v>7134705</v>
+        <v>7134725</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076636</v>
+        <v>120076633</v>
       </c>
       <c r="B135" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503530</v>
+        <v>503430</v>
       </c>
       <c r="R135" t="n">
-        <v>7134813</v>
+        <v>7134677</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076671</v>
+        <v>120076650</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>90576</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,25 +14933,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503546</v>
+        <v>503633</v>
       </c>
       <c r="R136" t="n">
-        <v>7134587</v>
+        <v>7134566</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076672</v>
+        <v>120076645</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15035,25 +15035,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503543</v>
+        <v>503601</v>
       </c>
       <c r="R137" t="n">
-        <v>7134573</v>
+        <v>7134773</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -6023,10 +6023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035291</v>
+        <v>120038086</v>
       </c>
       <c r="B49" t="n">
-        <v>4863</v>
+        <v>78263</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6035,25 +6035,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101675</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504179</v>
+        <v>503980</v>
       </c>
       <c r="R49" t="n">
-        <v>7134372</v>
+        <v>7134422</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6099,11 +6099,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6130,10 +6125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120038086</v>
+        <v>120035291</v>
       </c>
       <c r="B50" t="n">
-        <v>78263</v>
+        <v>4863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6142,25 +6137,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>101675</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,13 +6165,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503980</v>
+        <v>504179</v>
       </c>
       <c r="R50" t="n">
-        <v>7134422</v>
+        <v>7134372</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6206,6 +6201,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035868</v>
+        <v>120034479</v>
       </c>
       <c r="B57" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504193</v>
+        <v>504252</v>
       </c>
       <c r="R57" t="n">
-        <v>7134477</v>
+        <v>7134346</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120034479</v>
+        <v>120035868</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504252</v>
+        <v>504193</v>
       </c>
       <c r="R58" t="n">
-        <v>7134346</v>
+        <v>7134477</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076660</v>
+        <v>120076614</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503616</v>
+        <v>503427</v>
       </c>
       <c r="R68" t="n">
-        <v>7134591</v>
+        <v>7134675</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076614</v>
+        <v>120076602</v>
       </c>
       <c r="B69" t="n">
-        <v>79608</v>
+        <v>89633</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503427</v>
+        <v>503489</v>
       </c>
       <c r="R69" t="n">
-        <v>7134675</v>
+        <v>7134637</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076602</v>
+        <v>120076617</v>
       </c>
       <c r="B70" t="n">
-        <v>89633</v>
+        <v>96868</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503489</v>
+        <v>503847</v>
       </c>
       <c r="R70" t="n">
-        <v>7134637</v>
+        <v>7134693</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076617</v>
+        <v>120076618</v>
       </c>
       <c r="B71" t="n">
         <v>96868</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503847</v>
+        <v>503850</v>
       </c>
       <c r="R71" t="n">
-        <v>7134693</v>
+        <v>7134617</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076618</v>
+        <v>120076660</v>
       </c>
       <c r="B72" t="n">
-        <v>96868</v>
+        <v>78171</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503850</v>
+        <v>503616</v>
       </c>
       <c r="R72" t="n">
-        <v>7134617</v>
+        <v>7134591</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076675</v>
+        <v>120076625</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503542</v>
+        <v>503539</v>
       </c>
       <c r="R73" t="n">
-        <v>7134610</v>
+        <v>7134558</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076625</v>
+        <v>120076675</v>
       </c>
       <c r="B74" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503539</v>
+        <v>503542</v>
       </c>
       <c r="R74" t="n">
-        <v>7134558</v>
+        <v>7134610</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -10725,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076676</v>
+        <v>120076608</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,25 +10737,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503536</v>
+        <v>503530</v>
       </c>
       <c r="R95" t="n">
-        <v>7134619</v>
+        <v>7134813</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10827,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076608</v>
+        <v>120076599</v>
       </c>
       <c r="B96" t="n">
-        <v>79608</v>
+        <v>90527</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10839,25 +10839,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503530</v>
+        <v>503657</v>
       </c>
       <c r="R96" t="n">
-        <v>7134813</v>
+        <v>7134513</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10929,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076599</v>
+        <v>120076676</v>
       </c>
       <c r="B97" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10945,21 +10945,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503657</v>
+        <v>503536</v>
       </c>
       <c r="R97" t="n">
-        <v>7134513</v>
+        <v>7134619</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076600</v>
+        <v>120076615</v>
       </c>
       <c r="B126" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503603</v>
+        <v>503430</v>
       </c>
       <c r="R126" t="n">
-        <v>7134592</v>
+        <v>7134677</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076615</v>
+        <v>120076651</v>
       </c>
       <c r="B127" t="n">
-        <v>79608</v>
+        <v>90712</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503430</v>
+        <v>503516</v>
       </c>
       <c r="R127" t="n">
-        <v>7134677</v>
+        <v>7134622</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076651</v>
+        <v>120076610</v>
       </c>
       <c r="B128" t="n">
-        <v>90712</v>
+        <v>79608</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14117,25 +14117,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503516</v>
+        <v>503592</v>
       </c>
       <c r="R128" t="n">
-        <v>7134622</v>
+        <v>7134781</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076610</v>
+        <v>120076600</v>
       </c>
       <c r="B129" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503592</v>
+        <v>503603</v>
       </c>
       <c r="R129" t="n">
-        <v>7134781</v>
+        <v>7134592</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120034479</v>
+        <v>120035868</v>
       </c>
       <c r="B57" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504252</v>
+        <v>504193</v>
       </c>
       <c r="R57" t="n">
-        <v>7134346</v>
+        <v>7134477</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120035868</v>
+        <v>120034479</v>
       </c>
       <c r="B58" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504193</v>
+        <v>504252</v>
       </c>
       <c r="R58" t="n">
-        <v>7134477</v>
+        <v>7134346</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076614</v>
+        <v>120076660</v>
       </c>
       <c r="B68" t="n">
-        <v>79608</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503427</v>
+        <v>503616</v>
       </c>
       <c r="R68" t="n">
-        <v>7134675</v>
+        <v>7134591</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076602</v>
+        <v>120076614</v>
       </c>
       <c r="B69" t="n">
-        <v>89633</v>
+        <v>79608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503489</v>
+        <v>503427</v>
       </c>
       <c r="R69" t="n">
-        <v>7134637</v>
+        <v>7134675</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076617</v>
+        <v>120076602</v>
       </c>
       <c r="B70" t="n">
-        <v>96868</v>
+        <v>89633</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503847</v>
+        <v>503489</v>
       </c>
       <c r="R70" t="n">
-        <v>7134693</v>
+        <v>7134637</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076618</v>
+        <v>120076617</v>
       </c>
       <c r="B71" t="n">
         <v>96868</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503850</v>
+        <v>503847</v>
       </c>
       <c r="R71" t="n">
-        <v>7134617</v>
+        <v>7134693</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076660</v>
+        <v>120076618</v>
       </c>
       <c r="B72" t="n">
-        <v>78171</v>
+        <v>96868</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503616</v>
+        <v>503850</v>
       </c>
       <c r="R72" t="n">
-        <v>7134591</v>
+        <v>7134617</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076625</v>
+        <v>120076675</v>
       </c>
       <c r="B73" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503539</v>
+        <v>503542</v>
       </c>
       <c r="R73" t="n">
-        <v>7134558</v>
+        <v>7134610</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076675</v>
+        <v>120076625</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503542</v>
+        <v>503539</v>
       </c>
       <c r="R74" t="n">
-        <v>7134610</v>
+        <v>7134558</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076641</v>
+        <v>120076601</v>
       </c>
       <c r="B87" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9925,21 +9925,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503745</v>
+        <v>503546</v>
       </c>
       <c r="R87" t="n">
-        <v>7134697</v>
+        <v>7134565</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076613</v>
+        <v>120076641</v>
       </c>
       <c r="B88" t="n">
-        <v>79608</v>
+        <v>78262</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503646</v>
+        <v>503745</v>
       </c>
       <c r="R88" t="n">
-        <v>7134570</v>
+        <v>7134697</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076619</v>
+        <v>120076613</v>
       </c>
       <c r="B89" t="n">
-        <v>91832</v>
+        <v>79608</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503460</v>
+        <v>503646</v>
       </c>
       <c r="R89" t="n">
-        <v>7134749</v>
+        <v>7134570</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076601</v>
+        <v>120076619</v>
       </c>
       <c r="B90" t="n">
-        <v>79115</v>
+        <v>91832</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503546</v>
+        <v>503460</v>
       </c>
       <c r="R90" t="n">
-        <v>7134565</v>
+        <v>7134749</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10725,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076608</v>
+        <v>120076676</v>
       </c>
       <c r="B95" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,25 +10737,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503530</v>
+        <v>503536</v>
       </c>
       <c r="R95" t="n">
-        <v>7134813</v>
+        <v>7134619</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10827,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076599</v>
+        <v>120076608</v>
       </c>
       <c r="B96" t="n">
-        <v>90527</v>
+        <v>79608</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10839,25 +10839,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503657</v>
+        <v>503530</v>
       </c>
       <c r="R96" t="n">
-        <v>7134513</v>
+        <v>7134813</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10929,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076676</v>
+        <v>120076599</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10945,21 +10945,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503536</v>
+        <v>503657</v>
       </c>
       <c r="R97" t="n">
-        <v>7134619</v>
+        <v>7134513</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -11643,10 +11643,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076636</v>
+        <v>120076616</v>
       </c>
       <c r="B104" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11655,25 +11655,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503530</v>
+        <v>503430</v>
       </c>
       <c r="R104" t="n">
-        <v>7134813</v>
+        <v>7134700</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11745,10 +11745,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076616</v>
+        <v>120076636</v>
       </c>
       <c r="B105" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11757,25 +11757,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503430</v>
+        <v>503530</v>
       </c>
       <c r="R105" t="n">
-        <v>7134700</v>
+        <v>7134813</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12362,10 +12362,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076634</v>
+        <v>120065097</v>
       </c>
       <c r="B111" t="n">
-        <v>79607</v>
+        <v>91886</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12374,41 +12374,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503432</v>
+        <v>503748</v>
       </c>
       <c r="R111" t="n">
-        <v>7134696</v>
+        <v>7134611</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12440,12 +12443,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12464,10 +12473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076643</v>
+        <v>120076649</v>
       </c>
       <c r="B112" t="n">
-        <v>78262</v>
+        <v>90558</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12480,21 +12489,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12504,10 +12513,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503820</v>
+        <v>503835</v>
       </c>
       <c r="R112" t="n">
-        <v>7134705</v>
+        <v>7134640</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12566,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076639</v>
+        <v>120076634</v>
       </c>
       <c r="B113" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12578,25 +12587,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12606,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503430</v>
+        <v>503432</v>
       </c>
       <c r="R113" t="n">
-        <v>7134677</v>
+        <v>7134696</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12668,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076649</v>
+        <v>120076643</v>
       </c>
       <c r="B114" t="n">
-        <v>90558</v>
+        <v>78262</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12684,21 +12693,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12708,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503835</v>
+        <v>503820</v>
       </c>
       <c r="R114" t="n">
-        <v>7134640</v>
+        <v>7134705</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12770,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120065097</v>
+        <v>120076639</v>
       </c>
       <c r="B115" t="n">
-        <v>91886</v>
+        <v>79643</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12782,44 +12791,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>232140</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503748</v>
+        <v>503430</v>
       </c>
       <c r="R115" t="n">
-        <v>7134611</v>
+        <v>7134677</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12851,18 +12857,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076632</v>
+        <v>120076654</v>
       </c>
       <c r="B116" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12897,21 +12897,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503434</v>
+        <v>503821</v>
       </c>
       <c r="R116" t="n">
-        <v>7134673</v>
+        <v>7134659</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076648</v>
+        <v>120076653</v>
       </c>
       <c r="B117" t="n">
-        <v>89230</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12995,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503495</v>
+        <v>503608</v>
       </c>
       <c r="R117" t="n">
-        <v>7134638</v>
+        <v>7134763</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076654</v>
+        <v>120076632</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13101,21 +13101,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503821</v>
+        <v>503434</v>
       </c>
       <c r="R118" t="n">
-        <v>7134659</v>
+        <v>7134673</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076653</v>
+        <v>120076648</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>89230</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503608</v>
+        <v>503495</v>
       </c>
       <c r="R119" t="n">
-        <v>7134763</v>
+        <v>7134638</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -6023,10 +6023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120038086</v>
+        <v>120035291</v>
       </c>
       <c r="B49" t="n">
-        <v>78263</v>
+        <v>4863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6035,25 +6035,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>101675</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503980</v>
+        <v>504179</v>
       </c>
       <c r="R49" t="n">
-        <v>7134422</v>
+        <v>7134372</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6099,6 +6099,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6125,10 +6130,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035291</v>
+        <v>120038086</v>
       </c>
       <c r="B50" t="n">
-        <v>4863</v>
+        <v>78263</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6137,25 +6142,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101675</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6165,13 +6170,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504179</v>
+        <v>503980</v>
       </c>
       <c r="R50" t="n">
-        <v>7134372</v>
+        <v>7134422</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6201,11 +6206,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076660</v>
+        <v>120076614</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>79608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503616</v>
+        <v>503427</v>
       </c>
       <c r="R68" t="n">
-        <v>7134591</v>
+        <v>7134675</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076614</v>
+        <v>120076602</v>
       </c>
       <c r="B69" t="n">
-        <v>79608</v>
+        <v>89633</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503427</v>
+        <v>503489</v>
       </c>
       <c r="R69" t="n">
-        <v>7134675</v>
+        <v>7134637</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076602</v>
+        <v>120076617</v>
       </c>
       <c r="B70" t="n">
-        <v>89633</v>
+        <v>96868</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503489</v>
+        <v>503847</v>
       </c>
       <c r="R70" t="n">
-        <v>7134637</v>
+        <v>7134693</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076617</v>
+        <v>120076618</v>
       </c>
       <c r="B71" t="n">
         <v>96868</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503847</v>
+        <v>503850</v>
       </c>
       <c r="R71" t="n">
-        <v>7134693</v>
+        <v>7134617</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076618</v>
+        <v>120076660</v>
       </c>
       <c r="B72" t="n">
-        <v>96868</v>
+        <v>78171</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503850</v>
+        <v>503616</v>
       </c>
       <c r="R72" t="n">
-        <v>7134617</v>
+        <v>7134591</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076631</v>
+        <v>120076687</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>91834</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9517,21 +9517,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503624</v>
+        <v>503491</v>
       </c>
       <c r="R83" t="n">
-        <v>7134757</v>
+        <v>7134636</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076612</v>
+        <v>120076606</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9615,25 +9615,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503818</v>
+        <v>503427</v>
       </c>
       <c r="R84" t="n">
-        <v>7134671</v>
+        <v>7134680</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076606</v>
+        <v>120076631</v>
       </c>
       <c r="B85" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9717,25 +9717,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503427</v>
+        <v>503624</v>
       </c>
       <c r="R85" t="n">
-        <v>7134680</v>
+        <v>7134757</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076687</v>
+        <v>120076612</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>79608</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9823,21 +9823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503491</v>
+        <v>503818</v>
       </c>
       <c r="R86" t="n">
-        <v>7134636</v>
+        <v>7134671</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -11439,10 +11439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076628</v>
+        <v>120076616</v>
       </c>
       <c r="B102" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11455,21 +11455,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503570</v>
+        <v>503430</v>
       </c>
       <c r="R102" t="n">
-        <v>7134765</v>
+        <v>7134700</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11541,10 +11541,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076684</v>
+        <v>120076628</v>
       </c>
       <c r="B103" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11553,25 +11553,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11581,10 +11581,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503568</v>
+        <v>503570</v>
       </c>
       <c r="R103" t="n">
-        <v>7134774</v>
+        <v>7134765</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11643,10 +11643,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076616</v>
+        <v>120076684</v>
       </c>
       <c r="B104" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11655,25 +11655,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503430</v>
+        <v>503568</v>
       </c>
       <c r="R104" t="n">
-        <v>7134700</v>
+        <v>7134774</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076654</v>
+        <v>120076632</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12897,21 +12897,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503821</v>
+        <v>503434</v>
       </c>
       <c r="R116" t="n">
-        <v>7134659</v>
+        <v>7134673</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076653</v>
+        <v>120076648</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>89230</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12995,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503608</v>
+        <v>503495</v>
       </c>
       <c r="R117" t="n">
-        <v>7134763</v>
+        <v>7134638</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076632</v>
+        <v>120076654</v>
       </c>
       <c r="B118" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13101,21 +13101,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503434</v>
+        <v>503821</v>
       </c>
       <c r="R118" t="n">
-        <v>7134673</v>
+        <v>7134659</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076648</v>
+        <v>120076653</v>
       </c>
       <c r="B119" t="n">
-        <v>89230</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503495</v>
+        <v>503608</v>
       </c>
       <c r="R119" t="n">
-        <v>7134638</v>
+        <v>7134763</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076614</v>
+        <v>120076660</v>
       </c>
       <c r="B68" t="n">
-        <v>79608</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503427</v>
+        <v>503616</v>
       </c>
       <c r="R68" t="n">
-        <v>7134675</v>
+        <v>7134591</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076602</v>
+        <v>120076614</v>
       </c>
       <c r="B69" t="n">
-        <v>89633</v>
+        <v>79608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503489</v>
+        <v>503427</v>
       </c>
       <c r="R69" t="n">
-        <v>7134637</v>
+        <v>7134675</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076617</v>
+        <v>120076602</v>
       </c>
       <c r="B70" t="n">
-        <v>96868</v>
+        <v>89633</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503847</v>
+        <v>503489</v>
       </c>
       <c r="R70" t="n">
-        <v>7134693</v>
+        <v>7134637</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076618</v>
+        <v>120076617</v>
       </c>
       <c r="B71" t="n">
         <v>96868</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503850</v>
+        <v>503847</v>
       </c>
       <c r="R71" t="n">
-        <v>7134617</v>
+        <v>7134693</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076660</v>
+        <v>120076618</v>
       </c>
       <c r="B72" t="n">
-        <v>78171</v>
+        <v>96868</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503616</v>
+        <v>503850</v>
       </c>
       <c r="R72" t="n">
-        <v>7134591</v>
+        <v>7134617</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076687</v>
+        <v>120076631</v>
       </c>
       <c r="B83" t="n">
-        <v>91834</v>
+        <v>79607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9517,21 +9517,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503491</v>
+        <v>503624</v>
       </c>
       <c r="R83" t="n">
-        <v>7134636</v>
+        <v>7134757</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076606</v>
+        <v>120076612</v>
       </c>
       <c r="B84" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9615,25 +9615,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503427</v>
+        <v>503818</v>
       </c>
       <c r="R84" t="n">
-        <v>7134680</v>
+        <v>7134671</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076631</v>
+        <v>120076606</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9717,25 +9717,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503624</v>
+        <v>503427</v>
       </c>
       <c r="R85" t="n">
-        <v>7134757</v>
+        <v>7134680</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076612</v>
+        <v>120076687</v>
       </c>
       <c r="B86" t="n">
-        <v>79608</v>
+        <v>91834</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9823,21 +9823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503818</v>
+        <v>503491</v>
       </c>
       <c r="R86" t="n">
-        <v>7134671</v>
+        <v>7134636</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076601</v>
+        <v>120076641</v>
       </c>
       <c r="B87" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9925,21 +9925,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503546</v>
+        <v>503745</v>
       </c>
       <c r="R87" t="n">
-        <v>7134565</v>
+        <v>7134697</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076641</v>
+        <v>120076613</v>
       </c>
       <c r="B88" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503745</v>
+        <v>503646</v>
       </c>
       <c r="R88" t="n">
-        <v>7134697</v>
+        <v>7134570</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076613</v>
+        <v>120076619</v>
       </c>
       <c r="B89" t="n">
-        <v>79608</v>
+        <v>91832</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503646</v>
+        <v>503460</v>
       </c>
       <c r="R89" t="n">
-        <v>7134570</v>
+        <v>7134749</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076619</v>
+        <v>120076601</v>
       </c>
       <c r="B90" t="n">
-        <v>91832</v>
+        <v>79115</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503460</v>
+        <v>503546</v>
       </c>
       <c r="R90" t="n">
-        <v>7134749</v>
+        <v>7134565</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076615</v>
+        <v>120076600</v>
       </c>
       <c r="B126" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503430</v>
+        <v>503603</v>
       </c>
       <c r="R126" t="n">
-        <v>7134677</v>
+        <v>7134592</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076651</v>
+        <v>120076615</v>
       </c>
       <c r="B127" t="n">
-        <v>90712</v>
+        <v>79608</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503516</v>
+        <v>503430</v>
       </c>
       <c r="R127" t="n">
-        <v>7134622</v>
+        <v>7134677</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076610</v>
+        <v>120076651</v>
       </c>
       <c r="B128" t="n">
-        <v>79608</v>
+        <v>90712</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14117,25 +14117,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503592</v>
+        <v>503516</v>
       </c>
       <c r="R128" t="n">
-        <v>7134781</v>
+        <v>7134622</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076600</v>
+        <v>120076610</v>
       </c>
       <c r="B129" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503603</v>
+        <v>503592</v>
       </c>
       <c r="R129" t="n">
-        <v>7134592</v>
+        <v>7134781</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -10725,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076676</v>
+        <v>120076608</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,25 +10737,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503536</v>
+        <v>503530</v>
       </c>
       <c r="R95" t="n">
-        <v>7134619</v>
+        <v>7134813</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10827,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076608</v>
+        <v>120076599</v>
       </c>
       <c r="B96" t="n">
-        <v>79608</v>
+        <v>90527</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10839,25 +10839,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503530</v>
+        <v>503657</v>
       </c>
       <c r="R96" t="n">
-        <v>7134813</v>
+        <v>7134513</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10929,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076599</v>
+        <v>120076676</v>
       </c>
       <c r="B97" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10945,21 +10945,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503657</v>
+        <v>503536</v>
       </c>
       <c r="R97" t="n">
-        <v>7134513</v>
+        <v>7134619</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076632</v>
+        <v>120076654</v>
       </c>
       <c r="B116" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12897,21 +12897,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503434</v>
+        <v>503821</v>
       </c>
       <c r="R116" t="n">
-        <v>7134673</v>
+        <v>7134659</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076648</v>
+        <v>120076653</v>
       </c>
       <c r="B117" t="n">
-        <v>89230</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12995,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503495</v>
+        <v>503608</v>
       </c>
       <c r="R117" t="n">
-        <v>7134638</v>
+        <v>7134763</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076654</v>
+        <v>120076632</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13101,21 +13101,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503821</v>
+        <v>503434</v>
       </c>
       <c r="R118" t="n">
-        <v>7134659</v>
+        <v>7134673</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076653</v>
+        <v>120076648</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>89230</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503608</v>
+        <v>503495</v>
       </c>
       <c r="R119" t="n">
-        <v>7134763</v>
+        <v>7134638</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076600</v>
+        <v>120076615</v>
       </c>
       <c r="B126" t="n">
-        <v>79115</v>
+        <v>79608</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503603</v>
+        <v>503430</v>
       </c>
       <c r="R126" t="n">
-        <v>7134592</v>
+        <v>7134677</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076615</v>
+        <v>120076651</v>
       </c>
       <c r="B127" t="n">
-        <v>79608</v>
+        <v>90712</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503430</v>
+        <v>503516</v>
       </c>
       <c r="R127" t="n">
-        <v>7134677</v>
+        <v>7134622</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076651</v>
+        <v>120076610</v>
       </c>
       <c r="B128" t="n">
-        <v>90712</v>
+        <v>79608</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14117,25 +14117,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503516</v>
+        <v>503592</v>
       </c>
       <c r="R128" t="n">
-        <v>7134622</v>
+        <v>7134781</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076610</v>
+        <v>120076600</v>
       </c>
       <c r="B129" t="n">
-        <v>79608</v>
+        <v>79115</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503592</v>
+        <v>503603</v>
       </c>
       <c r="R129" t="n">
-        <v>7134781</v>
+        <v>7134592</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120035768</v>
+        <v>120035291</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>4863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>101675</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504187</v>
+        <v>504179</v>
       </c>
       <c r="R44" t="n">
-        <v>7134438</v>
+        <v>7134372</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5589,6 +5589,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5615,10 +5620,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120036022</v>
+        <v>120035768</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5655,13 +5660,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504145</v>
+        <v>504187</v>
       </c>
       <c r="R45" t="n">
-        <v>7134441</v>
+        <v>7134438</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5717,10 +5722,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120035474</v>
+        <v>120036399</v>
       </c>
       <c r="B46" t="n">
-        <v>79636</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5729,25 +5734,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,13 +5762,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504166</v>
+        <v>504083</v>
       </c>
       <c r="R46" t="n">
-        <v>7134391</v>
+        <v>7134453</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5793,6 +5798,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5819,10 +5829,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120034826</v>
+        <v>120039375</v>
       </c>
       <c r="B47" t="n">
-        <v>91844</v>
+        <v>78278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5831,25 +5841,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5859,10 +5869,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504226</v>
+        <v>503988</v>
       </c>
       <c r="R47" t="n">
-        <v>7134339</v>
+        <v>7134466</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5921,10 +5931,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120039375</v>
+        <v>120035871</v>
       </c>
       <c r="B48" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5937,21 +5947,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,10 +5971,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503988</v>
+        <v>504192</v>
       </c>
       <c r="R48" t="n">
-        <v>7134466</v>
+        <v>7134481</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6023,10 +6033,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035291</v>
+        <v>120035868</v>
       </c>
       <c r="B49" t="n">
-        <v>4863</v>
+        <v>78279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6035,25 +6045,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101675</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6063,13 +6073,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504179</v>
+        <v>504193</v>
       </c>
       <c r="R49" t="n">
-        <v>7134372</v>
+        <v>7134477</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6099,11 +6109,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6130,10 +6135,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120038086</v>
+        <v>120035474</v>
       </c>
       <c r="B50" t="n">
-        <v>78263</v>
+        <v>79652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6142,25 +6147,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,13 +6175,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503980</v>
+        <v>504166</v>
       </c>
       <c r="R50" t="n">
-        <v>7134422</v>
+        <v>7134391</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6232,10 +6237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120035542</v>
+        <v>120040383</v>
       </c>
       <c r="B51" t="n">
-        <v>79608</v>
+        <v>90825</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6244,41 +6249,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504175</v>
+        <v>503879</v>
       </c>
       <c r="R51" t="n">
-        <v>7134410</v>
+        <v>7134575</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6334,10 +6339,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120036399</v>
+        <v>120034383</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6350,21 +6355,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6374,13 +6379,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504083</v>
+        <v>504257</v>
       </c>
       <c r="R52" t="n">
-        <v>7134453</v>
+        <v>7134334</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6410,11 +6415,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6441,10 +6441,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120034574</v>
+        <v>120034826</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>91862</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6453,25 +6453,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6481,13 +6481,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504224</v>
+        <v>504226</v>
       </c>
       <c r="R53" t="n">
-        <v>7134352</v>
+        <v>7134339</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120035871</v>
+        <v>120034574</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6559,21 +6559,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6583,13 +6583,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504192</v>
+        <v>504224</v>
       </c>
       <c r="R54" t="n">
-        <v>7134481</v>
+        <v>7134352</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,10 +6645,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120040383</v>
+        <v>120035622</v>
       </c>
       <c r="B55" t="n">
-        <v>90807</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6657,41 +6657,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503879</v>
+        <v>504165</v>
       </c>
       <c r="R55" t="n">
-        <v>7134575</v>
+        <v>7134407</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,10 +6747,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120034383</v>
+        <v>120035015</v>
       </c>
       <c r="B56" t="n">
-        <v>78263</v>
+        <v>78278</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6763,21 +6763,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504257</v>
+        <v>504196</v>
       </c>
       <c r="R56" t="n">
-        <v>7134334</v>
+        <v>7134350</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035868</v>
+        <v>120035542</v>
       </c>
       <c r="B57" t="n">
-        <v>78263</v>
+        <v>79624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504193</v>
+        <v>504175</v>
       </c>
       <c r="R57" t="n">
-        <v>7134477</v>
+        <v>7134410</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120034479</v>
+        <v>120038086</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>78279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504252</v>
+        <v>503980</v>
       </c>
       <c r="R58" t="n">
-        <v>7134346</v>
+        <v>7134422</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>120035460</v>
       </c>
       <c r="B59" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120035015</v>
+        <v>120034479</v>
       </c>
       <c r="B60" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504196</v>
+        <v>504252</v>
       </c>
       <c r="R60" t="n">
-        <v>7134350</v>
+        <v>7134346</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120035622</v>
+        <v>120036022</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504165</v>
+        <v>504145</v>
       </c>
       <c r="R61" t="n">
-        <v>7134407</v>
+        <v>7134441</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120039963</v>
+        <v>120046464</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>78278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,41 +7371,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503904</v>
+        <v>503874</v>
       </c>
       <c r="R62" t="n">
-        <v>7134523</v>
+        <v>7134566</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7461,10 +7461,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120046464</v>
+        <v>120038261</v>
       </c>
       <c r="B63" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7473,41 +7473,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503874</v>
+        <v>503997</v>
       </c>
       <c r="R63" t="n">
-        <v>7134566</v>
+        <v>7134441</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120038261</v>
+        <v>120046468</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7599,17 +7599,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503997</v>
+        <v>503899</v>
       </c>
       <c r="R64" t="n">
-        <v>7134441</v>
+        <v>7134531</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120046465</v>
+        <v>120039963</v>
       </c>
       <c r="B65" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,41 +7677,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504001</v>
+        <v>503904</v>
       </c>
       <c r="R65" t="n">
-        <v>7134466</v>
+        <v>7134523</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120046468</v>
+        <v>120046465</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>78278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7779,25 +7779,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503899</v>
+        <v>504001</v>
       </c>
       <c r="R66" t="n">
-        <v>7134531</v>
+        <v>7134466</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076677</v>
+        <v>120076676</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503481</v>
+        <v>503536</v>
       </c>
       <c r="R67" t="n">
-        <v>7134655</v>
+        <v>7134619</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076660</v>
+        <v>120064794</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,41 +7983,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503616</v>
+        <v>503729</v>
       </c>
       <c r="R68" t="n">
-        <v>7134591</v>
+        <v>7134606</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076614</v>
+        <v>120060142</v>
       </c>
       <c r="B69" t="n">
-        <v>79608</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,41 +8085,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503427</v>
+        <v>503497</v>
       </c>
       <c r="R69" t="n">
-        <v>7134675</v>
+        <v>7134657</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076602</v>
+        <v>120076685</v>
       </c>
       <c r="B70" t="n">
-        <v>89633</v>
+        <v>79658</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503489</v>
+        <v>503819</v>
       </c>
       <c r="R70" t="n">
-        <v>7134637</v>
+        <v>7134668</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076617</v>
+        <v>120076684</v>
       </c>
       <c r="B71" t="n">
-        <v>96868</v>
+        <v>79658</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8293,21 +8293,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503847</v>
+        <v>503568</v>
       </c>
       <c r="R71" t="n">
-        <v>7134693</v>
+        <v>7134774</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076618</v>
+        <v>120076612</v>
       </c>
       <c r="B72" t="n">
-        <v>96868</v>
+        <v>79624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503850</v>
+        <v>503818</v>
       </c>
       <c r="R72" t="n">
-        <v>7134617</v>
+        <v>7134671</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076675</v>
+        <v>120076624</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>78279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503542</v>
+        <v>503630</v>
       </c>
       <c r="R73" t="n">
-        <v>7134610</v>
+        <v>7134529</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076625</v>
+        <v>120076634</v>
       </c>
       <c r="B74" t="n">
-        <v>78263</v>
+        <v>79623</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8599,21 +8599,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503539</v>
+        <v>503432</v>
       </c>
       <c r="R74" t="n">
-        <v>7134558</v>
+        <v>7134696</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076637</v>
+        <v>120076651</v>
       </c>
       <c r="B75" t="n">
-        <v>79643</v>
+        <v>90730</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,25 +8697,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503530</v>
+        <v>503516</v>
       </c>
       <c r="R75" t="n">
-        <v>7134806</v>
+        <v>7134622</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076609</v>
+        <v>120076638</v>
       </c>
       <c r="B76" t="n">
-        <v>79608</v>
+        <v>79659</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503567</v>
+        <v>503819</v>
       </c>
       <c r="R76" t="n">
-        <v>7134773</v>
+        <v>7134668</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076611</v>
+        <v>120076606</v>
       </c>
       <c r="B77" t="n">
-        <v>79608</v>
+        <v>79652</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503691</v>
+        <v>503427</v>
       </c>
       <c r="R77" t="n">
-        <v>7134749</v>
+        <v>7134680</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076673</v>
+        <v>120076599</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9007,21 +9007,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503532</v>
+        <v>503657</v>
       </c>
       <c r="R78" t="n">
-        <v>7134595</v>
+        <v>7134513</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076605</v>
+        <v>120076643</v>
       </c>
       <c r="B79" t="n">
-        <v>79636</v>
+        <v>78278</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9105,25 +9105,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503568</v>
+        <v>503820</v>
       </c>
       <c r="R79" t="n">
-        <v>7134774</v>
+        <v>7134705</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076624</v>
+        <v>120076661</v>
       </c>
       <c r="B80" t="n">
-        <v>78263</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9211,21 +9211,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503630</v>
+        <v>503604</v>
       </c>
       <c r="R80" t="n">
-        <v>7134529</v>
+        <v>7134590</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076664</v>
+        <v>120076640</v>
       </c>
       <c r="B81" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503543</v>
+        <v>503654</v>
       </c>
       <c r="R81" t="n">
-        <v>7134608</v>
+        <v>7134725</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076662</v>
+        <v>120076644</v>
       </c>
       <c r="B82" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9415,21 +9415,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503535</v>
+        <v>503748</v>
       </c>
       <c r="R82" t="n">
-        <v>7134599</v>
+        <v>7134611</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076631</v>
+        <v>120076628</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503624</v>
+        <v>503570</v>
       </c>
       <c r="R83" t="n">
-        <v>7134757</v>
+        <v>7134765</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076612</v>
+        <v>120076635</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>79623</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9619,21 +9619,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503818</v>
+        <v>503426</v>
       </c>
       <c r="R84" t="n">
-        <v>7134671</v>
+        <v>7134704</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076606</v>
+        <v>120076637</v>
       </c>
       <c r="B85" t="n">
-        <v>79636</v>
+        <v>79659</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9721,21 +9721,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503427</v>
+        <v>503530</v>
       </c>
       <c r="R85" t="n">
-        <v>7134680</v>
+        <v>7134806</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076687</v>
+        <v>120076681</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>12337</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9819,25 +9819,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>101283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503491</v>
+        <v>503867</v>
       </c>
       <c r="R86" t="n">
-        <v>7134636</v>
+        <v>7134650</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9883,6 +9883,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9909,10 +9914,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076641</v>
+        <v>120076653</v>
       </c>
       <c r="B87" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9925,21 +9930,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9949,10 +9954,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503745</v>
+        <v>503608</v>
       </c>
       <c r="R87" t="n">
-        <v>7134697</v>
+        <v>7134763</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10011,10 +10016,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076613</v>
+        <v>120076611</v>
       </c>
       <c r="B88" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10051,10 +10056,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503646</v>
+        <v>503691</v>
       </c>
       <c r="R88" t="n">
-        <v>7134570</v>
+        <v>7134749</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076619</v>
+        <v>120076630</v>
       </c>
       <c r="B89" t="n">
-        <v>91832</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10134,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503460</v>
+        <v>503592</v>
       </c>
       <c r="R89" t="n">
-        <v>7134749</v>
+        <v>7134781</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076601</v>
+        <v>120076633</v>
       </c>
       <c r="B90" t="n">
-        <v>79115</v>
+        <v>79623</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10231,21 +10236,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10260,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503546</v>
+        <v>503430</v>
       </c>
       <c r="R90" t="n">
-        <v>7134565</v>
+        <v>7134677</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10322,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076626</v>
+        <v>120076672</v>
       </c>
       <c r="B91" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10329,25 +10334,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10362,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503534</v>
+        <v>503543</v>
       </c>
       <c r="R91" t="n">
-        <v>7134804</v>
+        <v>7134573</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10419,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076635</v>
+        <v>120076631</v>
       </c>
       <c r="B92" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10459,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503426</v>
+        <v>503624</v>
       </c>
       <c r="R92" t="n">
-        <v>7134704</v>
+        <v>7134757</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10521,10 +10526,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076630</v>
+        <v>120065097</v>
       </c>
       <c r="B93" t="n">
-        <v>79607</v>
+        <v>91904</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10533,41 +10538,44 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503592</v>
+        <v>503748</v>
       </c>
       <c r="R93" t="n">
-        <v>7134781</v>
+        <v>7134611</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10599,12 +10607,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10623,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076646</v>
+        <v>120076600</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>79131</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10635,25 +10649,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10663,10 +10677,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503675</v>
+        <v>503603</v>
       </c>
       <c r="R94" t="n">
-        <v>7134737</v>
+        <v>7134592</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10725,10 +10739,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076608</v>
+        <v>120076646</v>
       </c>
       <c r="B95" t="n">
-        <v>79608</v>
+        <v>97930</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,25 +10751,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10779,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503530</v>
+        <v>503675</v>
       </c>
       <c r="R95" t="n">
-        <v>7134813</v>
+        <v>7134737</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10827,10 +10841,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076599</v>
+        <v>120076625</v>
       </c>
       <c r="B96" t="n">
-        <v>90527</v>
+        <v>78279</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10839,25 +10853,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10867,10 +10881,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503657</v>
+        <v>503539</v>
       </c>
       <c r="R96" t="n">
-        <v>7134513</v>
+        <v>7134558</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10943,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076676</v>
+        <v>120076609</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>79624</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10941,25 +10955,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10983,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503536</v>
+        <v>503567</v>
       </c>
       <c r="R97" t="n">
-        <v>7134619</v>
+        <v>7134773</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11031,10 +11045,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076638</v>
+        <v>120076602</v>
       </c>
       <c r="B98" t="n">
-        <v>79643</v>
+        <v>89650</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11043,25 +11057,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11071,10 +11085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503819</v>
+        <v>503489</v>
       </c>
       <c r="R98" t="n">
-        <v>7134668</v>
+        <v>7134637</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11133,10 +11147,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076647</v>
+        <v>120076616</v>
       </c>
       <c r="B99" t="n">
-        <v>97907</v>
+        <v>79624</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11145,25 +11159,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11173,10 +11187,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503790</v>
+        <v>503430</v>
       </c>
       <c r="R99" t="n">
-        <v>7134698</v>
+        <v>7134700</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11235,10 +11249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076627</v>
+        <v>120076686</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>79658</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11247,25 +11261,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11275,10 +11289,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503531</v>
+        <v>503428</v>
       </c>
       <c r="R100" t="n">
-        <v>7134812</v>
+        <v>7134677</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11337,10 +11351,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076623</v>
+        <v>120076617</v>
       </c>
       <c r="B101" t="n">
-        <v>78263</v>
+        <v>96891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11349,25 +11363,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11377,10 +11391,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503665</v>
+        <v>503847</v>
       </c>
       <c r="R101" t="n">
-        <v>7134523</v>
+        <v>7134693</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11439,10 +11453,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076616</v>
+        <v>120076615</v>
       </c>
       <c r="B102" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11482,7 +11496,7 @@
         <v>503430</v>
       </c>
       <c r="R102" t="n">
-        <v>7134700</v>
+        <v>7134677</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11541,10 +11555,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076628</v>
+        <v>120076623</v>
       </c>
       <c r="B103" t="n">
-        <v>79607</v>
+        <v>78279</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11557,21 +11571,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11581,10 +11595,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503570</v>
+        <v>503665</v>
       </c>
       <c r="R103" t="n">
-        <v>7134765</v>
+        <v>7134523</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11643,10 +11657,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076684</v>
+        <v>120076613</v>
       </c>
       <c r="B104" t="n">
-        <v>79642</v>
+        <v>79624</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11655,25 +11669,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11683,10 +11697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503568</v>
+        <v>503646</v>
       </c>
       <c r="R104" t="n">
-        <v>7134774</v>
+        <v>7134570</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11745,10 +11759,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076636</v>
+        <v>120076650</v>
       </c>
       <c r="B105" t="n">
-        <v>79643</v>
+        <v>90594</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11757,25 +11771,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11785,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503530</v>
+        <v>503633</v>
       </c>
       <c r="R105" t="n">
-        <v>7134813</v>
+        <v>7134566</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11847,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120064794</v>
+        <v>120076664</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>78187</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11859,41 +11873,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503729</v>
+        <v>503543</v>
       </c>
       <c r="R106" t="n">
-        <v>7134606</v>
+        <v>7134608</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11949,10 +11963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076644</v>
+        <v>120076641</v>
       </c>
       <c r="B107" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11989,10 +12003,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503748</v>
+        <v>503745</v>
       </c>
       <c r="R107" t="n">
-        <v>7134611</v>
+        <v>7134697</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12051,10 +12065,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076681</v>
+        <v>120076632</v>
       </c>
       <c r="B108" t="n">
-        <v>12337</v>
+        <v>79623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12063,25 +12077,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>101283</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12091,10 +12105,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503867</v>
+        <v>503434</v>
       </c>
       <c r="R108" t="n">
-        <v>7134650</v>
+        <v>7134673</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12127,11 +12141,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12158,10 +12167,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076620</v>
+        <v>120076636</v>
       </c>
       <c r="B109" t="n">
-        <v>92030</v>
+        <v>79659</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12170,25 +12179,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2079</v>
+        <v>6464</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12198,10 +12207,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503618</v>
+        <v>503530</v>
       </c>
       <c r="R109" t="n">
-        <v>7134495</v>
+        <v>7134813</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,10 +12269,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076661</v>
+        <v>120076610</v>
       </c>
       <c r="B110" t="n">
-        <v>78171</v>
+        <v>79624</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12276,21 +12285,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12300,10 +12309,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503604</v>
+        <v>503592</v>
       </c>
       <c r="R110" t="n">
-        <v>7134590</v>
+        <v>7134781</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12362,10 +12371,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120065097</v>
+        <v>120076674</v>
       </c>
       <c r="B111" t="n">
-        <v>91886</v>
+        <v>91858</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12374,44 +12383,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503748</v>
+        <v>503558</v>
       </c>
       <c r="R111" t="n">
-        <v>7134611</v>
+        <v>7134614</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12443,18 +12449,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12473,10 +12473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076649</v>
+        <v>120076673</v>
       </c>
       <c r="B112" t="n">
-        <v>90558</v>
+        <v>91858</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12485,25 +12485,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503835</v>
+        <v>503532</v>
       </c>
       <c r="R112" t="n">
-        <v>7134640</v>
+        <v>7134595</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076634</v>
+        <v>120076662</v>
       </c>
       <c r="B113" t="n">
-        <v>79607</v>
+        <v>78187</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12591,21 +12591,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503432</v>
+        <v>503535</v>
       </c>
       <c r="R113" t="n">
-        <v>7134696</v>
+        <v>7134599</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076643</v>
+        <v>120076605</v>
       </c>
       <c r="B114" t="n">
-        <v>78262</v>
+        <v>79652</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12689,25 +12689,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503820</v>
+        <v>503568</v>
       </c>
       <c r="R114" t="n">
-        <v>7134705</v>
+        <v>7134774</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076639</v>
+        <v>120076601</v>
       </c>
       <c r="B115" t="n">
-        <v>79643</v>
+        <v>79131</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12791,25 +12791,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503430</v>
+        <v>503546</v>
       </c>
       <c r="R115" t="n">
-        <v>7134677</v>
+        <v>7134565</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076654</v>
+        <v>120076671</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12893,25 +12893,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503821</v>
+        <v>503546</v>
       </c>
       <c r="R116" t="n">
-        <v>7134659</v>
+        <v>7134587</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076653</v>
+        <v>120076619</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>91850</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12999,21 +12999,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503608</v>
+        <v>503460</v>
       </c>
       <c r="R117" t="n">
-        <v>7134763</v>
+        <v>7134749</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076632</v>
+        <v>120076648</v>
       </c>
       <c r="B118" t="n">
-        <v>79607</v>
+        <v>89247</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>1596</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503434</v>
+        <v>503495</v>
       </c>
       <c r="R118" t="n">
-        <v>7134673</v>
+        <v>7134638</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076648</v>
+        <v>120076654</v>
       </c>
       <c r="B119" t="n">
-        <v>89230</v>
+        <v>78542</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503495</v>
+        <v>503821</v>
       </c>
       <c r="R119" t="n">
-        <v>7134638</v>
+        <v>7134659</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076670</v>
+        <v>120076647</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13301,25 +13301,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503626</v>
+        <v>503790</v>
       </c>
       <c r="R120" t="n">
-        <v>7134549</v>
+        <v>7134698</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076674</v>
+        <v>120076645</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503558</v>
+        <v>503601</v>
       </c>
       <c r="R121" t="n">
-        <v>7134614</v>
+        <v>7134773</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076672</v>
+        <v>120076626</v>
       </c>
       <c r="B122" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503543</v>
+        <v>503534</v>
       </c>
       <c r="R122" t="n">
-        <v>7134573</v>
+        <v>7134804</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076685</v>
+        <v>120076652</v>
       </c>
       <c r="B123" t="n">
-        <v>79642</v>
+        <v>78542</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13607,20 +13607,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503819</v>
+        <v>503526</v>
       </c>
       <c r="R123" t="n">
-        <v>7134668</v>
+        <v>7134815</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076629</v>
+        <v>120076608</v>
       </c>
       <c r="B124" t="n">
-        <v>79607</v>
+        <v>79624</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13713,21 +13713,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503568</v>
+        <v>503530</v>
       </c>
       <c r="R124" t="n">
-        <v>7134773</v>
+        <v>7134813</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076686</v>
+        <v>120076649</v>
       </c>
       <c r="B125" t="n">
-        <v>79642</v>
+        <v>90576</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,25 +13811,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503428</v>
+        <v>503835</v>
       </c>
       <c r="R125" t="n">
-        <v>7134677</v>
+        <v>7134640</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076615</v>
+        <v>120076614</v>
       </c>
       <c r="B126" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503430</v>
+        <v>503427</v>
       </c>
       <c r="R126" t="n">
-        <v>7134677</v>
+        <v>7134675</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076651</v>
+        <v>120076665</v>
       </c>
       <c r="B127" t="n">
-        <v>90712</v>
+        <v>78187</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503516</v>
+        <v>503480</v>
       </c>
       <c r="R127" t="n">
-        <v>7134622</v>
+        <v>7134647</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076610</v>
+        <v>120076629</v>
       </c>
       <c r="B128" t="n">
-        <v>79608</v>
+        <v>79623</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503592</v>
+        <v>503568</v>
       </c>
       <c r="R128" t="n">
-        <v>7134781</v>
+        <v>7134773</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076600</v>
+        <v>120076627</v>
       </c>
       <c r="B129" t="n">
-        <v>79115</v>
+        <v>79623</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503603</v>
+        <v>503531</v>
       </c>
       <c r="R129" t="n">
-        <v>7134592</v>
+        <v>7134812</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076665</v>
+        <v>120076618</v>
       </c>
       <c r="B130" t="n">
-        <v>78171</v>
+        <v>96891</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14321,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503480</v>
+        <v>503850</v>
       </c>
       <c r="R130" t="n">
-        <v>7134647</v>
+        <v>7134617</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076671</v>
+        <v>120076687</v>
       </c>
       <c r="B131" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14423,25 +14423,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503546</v>
+        <v>503491</v>
       </c>
       <c r="R131" t="n">
-        <v>7134587</v>
+        <v>7134636</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120060142</v>
+        <v>120076620</v>
       </c>
       <c r="B132" t="n">
-        <v>91840</v>
+        <v>92048</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14525,41 +14525,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503497</v>
+        <v>503618</v>
       </c>
       <c r="R132" t="n">
-        <v>7134657</v>
+        <v>7134495</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14615,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076652</v>
+        <v>120076675</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14627,25 +14627,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14655,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503526</v>
+        <v>503542</v>
       </c>
       <c r="R133" t="n">
-        <v>7134815</v>
+        <v>7134610</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14717,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076640</v>
+        <v>120076670</v>
       </c>
       <c r="B134" t="n">
-        <v>78262</v>
+        <v>91858</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14729,25 +14729,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503654</v>
+        <v>503626</v>
       </c>
       <c r="R134" t="n">
-        <v>7134725</v>
+        <v>7134549</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076633</v>
+        <v>120076677</v>
       </c>
       <c r="B135" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503430</v>
+        <v>503481</v>
       </c>
       <c r="R135" t="n">
-        <v>7134677</v>
+        <v>7134655</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076650</v>
+        <v>120076660</v>
       </c>
       <c r="B136" t="n">
-        <v>90576</v>
+        <v>78187</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14937,21 +14937,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503633</v>
+        <v>503616</v>
       </c>
       <c r="R136" t="n">
-        <v>7134566</v>
+        <v>7134591</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076645</v>
+        <v>120076639</v>
       </c>
       <c r="B137" t="n">
-        <v>97907</v>
+        <v>79659</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15035,25 +15035,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503601</v>
+        <v>503430</v>
       </c>
       <c r="R137" t="n">
-        <v>7134773</v>
+        <v>7134677</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076638</v>
+        <v>120076661</v>
       </c>
       <c r="B76" t="n">
-        <v>79659</v>
+        <v>78187</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503819</v>
+        <v>503604</v>
       </c>
       <c r="R76" t="n">
-        <v>7134668</v>
+        <v>7134590</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076606</v>
+        <v>120076599</v>
       </c>
       <c r="B77" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8905,21 +8905,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503427</v>
+        <v>503657</v>
       </c>
       <c r="R77" t="n">
-        <v>7134680</v>
+        <v>7134513</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076599</v>
+        <v>120076643</v>
       </c>
       <c r="B78" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9003,25 +9003,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503657</v>
+        <v>503820</v>
       </c>
       <c r="R78" t="n">
-        <v>7134513</v>
+        <v>7134705</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076643</v>
+        <v>120076638</v>
       </c>
       <c r="B79" t="n">
-        <v>78278</v>
+        <v>79659</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9105,25 +9105,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503820</v>
+        <v>503819</v>
       </c>
       <c r="R79" t="n">
-        <v>7134705</v>
+        <v>7134668</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076661</v>
+        <v>120076606</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9207,25 +9207,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503604</v>
+        <v>503427</v>
       </c>
       <c r="R80" t="n">
-        <v>7134590</v>
+        <v>7134680</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -11555,10 +11555,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076623</v>
+        <v>120076613</v>
       </c>
       <c r="B103" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11571,21 +11571,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503665</v>
+        <v>503646</v>
       </c>
       <c r="R103" t="n">
-        <v>7134523</v>
+        <v>7134570</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11657,10 +11657,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076613</v>
+        <v>120076650</v>
       </c>
       <c r="B104" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11673,21 +11673,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503646</v>
+        <v>503633</v>
       </c>
       <c r="R104" t="n">
-        <v>7134570</v>
+        <v>7134566</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11759,10 +11759,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076650</v>
+        <v>120076664</v>
       </c>
       <c r="B105" t="n">
-        <v>90594</v>
+        <v>78187</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11775,21 +11775,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503633</v>
+        <v>503543</v>
       </c>
       <c r="R105" t="n">
-        <v>7134566</v>
+        <v>7134608</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11861,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076664</v>
+        <v>120076641</v>
       </c>
       <c r="B106" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11877,21 +11877,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503543</v>
+        <v>503745</v>
       </c>
       <c r="R106" t="n">
-        <v>7134608</v>
+        <v>7134697</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11963,10 +11963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076641</v>
+        <v>120076632</v>
       </c>
       <c r="B107" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503745</v>
+        <v>503434</v>
       </c>
       <c r="R107" t="n">
-        <v>7134697</v>
+        <v>7134673</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076632</v>
+        <v>120076636</v>
       </c>
       <c r="B108" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12077,25 +12077,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12105,10 +12105,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503434</v>
+        <v>503530</v>
       </c>
       <c r="R108" t="n">
-        <v>7134673</v>
+        <v>7134813</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12167,10 +12167,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076636</v>
+        <v>120076623</v>
       </c>
       <c r="B109" t="n">
-        <v>79659</v>
+        <v>78279</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12179,25 +12179,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503530</v>
+        <v>503665</v>
       </c>
       <c r="R109" t="n">
-        <v>7134813</v>
+        <v>7134523</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076618</v>
+        <v>120076687</v>
       </c>
       <c r="B130" t="n">
-        <v>96891</v>
+        <v>91852</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14321,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503850</v>
+        <v>503491</v>
       </c>
       <c r="R130" t="n">
-        <v>7134617</v>
+        <v>7134636</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076687</v>
+        <v>120076618</v>
       </c>
       <c r="B131" t="n">
-        <v>91852</v>
+        <v>96891</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14423,25 +14423,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503491</v>
+        <v>503850</v>
       </c>
       <c r="R131" t="n">
-        <v>7134636</v>
+        <v>7134617</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120035291</v>
+        <v>120035768</v>
       </c>
       <c r="B44" t="n">
-        <v>4863</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101675</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504179</v>
+        <v>504187</v>
       </c>
       <c r="R44" t="n">
-        <v>7134372</v>
+        <v>7134438</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5589,11 +5589,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5620,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120035768</v>
+        <v>120035871</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5636,21 +5631,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5660,13 +5655,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504187</v>
+        <v>504192</v>
       </c>
       <c r="R45" t="n">
-        <v>7134438</v>
+        <v>7134481</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5722,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120036399</v>
+        <v>120035460</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5738,21 +5733,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5762,10 +5757,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504083</v>
+        <v>504169</v>
       </c>
       <c r="R46" t="n">
-        <v>7134453</v>
+        <v>7134407</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5798,11 +5793,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5829,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120039375</v>
+        <v>120040383</v>
       </c>
       <c r="B47" t="n">
-        <v>78278</v>
+        <v>90825</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5841,38 +5831,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503988</v>
+        <v>503879</v>
       </c>
       <c r="R47" t="n">
-        <v>7134466</v>
+        <v>7134575</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5931,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035871</v>
+        <v>120035542</v>
       </c>
       <c r="B48" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5947,21 +5937,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5971,13 +5961,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504192</v>
+        <v>504175</v>
       </c>
       <c r="R48" t="n">
-        <v>7134481</v>
+        <v>7134410</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6033,10 +6023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035868</v>
+        <v>120039375</v>
       </c>
       <c r="B49" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6049,21 +6039,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6073,10 +6063,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504193</v>
+        <v>503988</v>
       </c>
       <c r="R49" t="n">
-        <v>7134477</v>
+        <v>7134466</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6135,10 +6125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035474</v>
+        <v>120034479</v>
       </c>
       <c r="B50" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6147,25 +6137,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6175,13 +6165,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504166</v>
+        <v>504252</v>
       </c>
       <c r="R50" t="n">
-        <v>7134391</v>
+        <v>7134346</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6237,10 +6227,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120040383</v>
+        <v>120035622</v>
       </c>
       <c r="B51" t="n">
-        <v>90825</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6249,41 +6239,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503879</v>
+        <v>504165</v>
       </c>
       <c r="R51" t="n">
-        <v>7134575</v>
+        <v>7134407</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6339,10 +6329,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120034383</v>
+        <v>120035291</v>
       </c>
       <c r="B52" t="n">
-        <v>78279</v>
+        <v>4863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6351,25 +6341,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>101675</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6379,13 +6369,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504257</v>
+        <v>504179</v>
       </c>
       <c r="R52" t="n">
-        <v>7134334</v>
+        <v>7134372</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6415,6 +6405,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6441,10 +6436,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120034826</v>
+        <v>120035474</v>
       </c>
       <c r="B53" t="n">
-        <v>91862</v>
+        <v>79652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6453,25 +6448,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6481,10 +6476,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504226</v>
+        <v>504166</v>
       </c>
       <c r="R53" t="n">
-        <v>7134339</v>
+        <v>7134391</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6543,10 +6538,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120034574</v>
+        <v>120036399</v>
       </c>
       <c r="B54" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6559,21 +6554,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6583,10 +6578,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504224</v>
+        <v>504083</v>
       </c>
       <c r="R54" t="n">
-        <v>7134352</v>
+        <v>7134453</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6619,6 +6614,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6645,10 +6645,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120035622</v>
+        <v>120036022</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6661,21 +6661,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504165</v>
+        <v>504145</v>
       </c>
       <c r="R55" t="n">
-        <v>7134407</v>
+        <v>7134441</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120035015</v>
+        <v>120034574</v>
       </c>
       <c r="B56" t="n">
         <v>78278</v>
@@ -6787,10 +6787,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504196</v>
+        <v>504224</v>
       </c>
       <c r="R56" t="n">
-        <v>7134350</v>
+        <v>7134352</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035542</v>
+        <v>120035015</v>
       </c>
       <c r="B57" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504175</v>
+        <v>504196</v>
       </c>
       <c r="R57" t="n">
-        <v>7134410</v>
+        <v>7134350</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120038086</v>
+        <v>120035868</v>
       </c>
       <c r="B58" t="n">
         <v>78279</v>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503980</v>
+        <v>504193</v>
       </c>
       <c r="R58" t="n">
-        <v>7134422</v>
+        <v>7134477</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120035460</v>
+        <v>120034383</v>
       </c>
       <c r="B59" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7093,13 +7093,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504169</v>
+        <v>504257</v>
       </c>
       <c r="R59" t="n">
-        <v>7134407</v>
+        <v>7134334</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120034479</v>
+        <v>120034826</v>
       </c>
       <c r="B60" t="n">
-        <v>78278</v>
+        <v>91862</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,13 +7195,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504252</v>
+        <v>504226</v>
       </c>
       <c r="R60" t="n">
-        <v>7134346</v>
+        <v>7134339</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120036022</v>
+        <v>120038086</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504145</v>
+        <v>503980</v>
       </c>
       <c r="R61" t="n">
-        <v>7134441</v>
+        <v>7134422</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120038261</v>
+        <v>120039963</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -7501,13 +7501,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503997</v>
+        <v>503904</v>
       </c>
       <c r="R63" t="n">
-        <v>7134441</v>
+        <v>7134523</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120039963</v>
+        <v>120038261</v>
       </c>
       <c r="B65" t="n">
         <v>97930</v>
@@ -7705,13 +7705,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503904</v>
+        <v>503997</v>
       </c>
       <c r="R65" t="n">
-        <v>7134523</v>
+        <v>7134441</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076676</v>
+        <v>120076673</v>
       </c>
       <c r="B67" t="n">
         <v>91858</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503536</v>
+        <v>503532</v>
       </c>
       <c r="R67" t="n">
-        <v>7134619</v>
+        <v>7134595</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120064794</v>
+        <v>120076661</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,41 +7983,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503729</v>
+        <v>503604</v>
       </c>
       <c r="R68" t="n">
-        <v>7134606</v>
+        <v>7134590</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120060142</v>
+        <v>120076654</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,41 +8085,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503497</v>
+        <v>503821</v>
       </c>
       <c r="R69" t="n">
-        <v>7134657</v>
+        <v>7134659</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076685</v>
+        <v>120076623</v>
       </c>
       <c r="B70" t="n">
-        <v>79658</v>
+        <v>78279</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503819</v>
+        <v>503665</v>
       </c>
       <c r="R70" t="n">
-        <v>7134668</v>
+        <v>7134523</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076684</v>
+        <v>120076649</v>
       </c>
       <c r="B71" t="n">
-        <v>79658</v>
+        <v>90576</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503568</v>
+        <v>503835</v>
       </c>
       <c r="R71" t="n">
-        <v>7134774</v>
+        <v>7134640</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076612</v>
+        <v>120076615</v>
       </c>
       <c r="B72" t="n">
         <v>79624</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503818</v>
+        <v>503430</v>
       </c>
       <c r="R72" t="n">
-        <v>7134671</v>
+        <v>7134677</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076624</v>
+        <v>120076672</v>
       </c>
       <c r="B73" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503630</v>
+        <v>503543</v>
       </c>
       <c r="R73" t="n">
-        <v>7134529</v>
+        <v>7134573</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076634</v>
+        <v>120076617</v>
       </c>
       <c r="B74" t="n">
-        <v>79623</v>
+        <v>96891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503432</v>
+        <v>503847</v>
       </c>
       <c r="R74" t="n">
-        <v>7134696</v>
+        <v>7134693</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076651</v>
+        <v>120076618</v>
       </c>
       <c r="B75" t="n">
-        <v>90730</v>
+        <v>96891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,25 +8697,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503516</v>
+        <v>503850</v>
       </c>
       <c r="R75" t="n">
-        <v>7134622</v>
+        <v>7134617</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076661</v>
+        <v>120076606</v>
       </c>
       <c r="B76" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503604</v>
+        <v>503427</v>
       </c>
       <c r="R76" t="n">
-        <v>7134590</v>
+        <v>7134680</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076599</v>
+        <v>120076664</v>
       </c>
       <c r="B77" t="n">
-        <v>90545</v>
+        <v>78187</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503657</v>
+        <v>503543</v>
       </c>
       <c r="R77" t="n">
-        <v>7134513</v>
+        <v>7134608</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076643</v>
+        <v>120076627</v>
       </c>
       <c r="B78" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9007,21 +9007,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503820</v>
+        <v>503531</v>
       </c>
       <c r="R78" t="n">
-        <v>7134705</v>
+        <v>7134812</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076638</v>
+        <v>120064794</v>
       </c>
       <c r="B79" t="n">
-        <v>79659</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9109,37 +9109,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503819</v>
+        <v>503729</v>
       </c>
       <c r="R79" t="n">
-        <v>7134668</v>
+        <v>7134606</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076606</v>
+        <v>120076648</v>
       </c>
       <c r="B80" t="n">
-        <v>79652</v>
+        <v>89247</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9207,25 +9207,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>1596</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503427</v>
+        <v>503495</v>
       </c>
       <c r="R80" t="n">
-        <v>7134680</v>
+        <v>7134638</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076640</v>
+        <v>120076629</v>
       </c>
       <c r="B81" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503654</v>
+        <v>503568</v>
       </c>
       <c r="R81" t="n">
-        <v>7134725</v>
+        <v>7134773</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076644</v>
+        <v>120076637</v>
       </c>
       <c r="B82" t="n">
-        <v>78278</v>
+        <v>79659</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9411,25 +9411,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503748</v>
+        <v>503530</v>
       </c>
       <c r="R82" t="n">
-        <v>7134611</v>
+        <v>7134806</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076628</v>
+        <v>120076676</v>
       </c>
       <c r="B83" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9513,25 +9513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503570</v>
+        <v>503536</v>
       </c>
       <c r="R83" t="n">
-        <v>7134765</v>
+        <v>7134619</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076635</v>
+        <v>120060142</v>
       </c>
       <c r="B84" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9615,41 +9615,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503426</v>
+        <v>503497</v>
       </c>
       <c r="R84" t="n">
-        <v>7134704</v>
+        <v>7134657</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076637</v>
+        <v>120076681</v>
       </c>
       <c r="B85" t="n">
-        <v>79659</v>
+        <v>12337</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9717,25 +9717,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>101283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503530</v>
+        <v>503867</v>
       </c>
       <c r="R85" t="n">
-        <v>7134806</v>
+        <v>7134650</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9781,6 +9781,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9807,10 +9812,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076681</v>
+        <v>120076662</v>
       </c>
       <c r="B86" t="n">
-        <v>12337</v>
+        <v>78187</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9819,25 +9824,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>101283</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9852,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503867</v>
+        <v>503535</v>
       </c>
       <c r="R86" t="n">
-        <v>7134650</v>
+        <v>7134599</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9883,11 +9888,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9914,10 +9914,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076653</v>
+        <v>120076685</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503608</v>
+        <v>503819</v>
       </c>
       <c r="R87" t="n">
-        <v>7134763</v>
+        <v>7134668</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10016,10 +10016,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076611</v>
+        <v>120076620</v>
       </c>
       <c r="B88" t="n">
-        <v>79624</v>
+        <v>92048</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10032,21 +10032,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503691</v>
+        <v>503618</v>
       </c>
       <c r="R88" t="n">
-        <v>7134749</v>
+        <v>7134495</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10118,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076630</v>
+        <v>120065097</v>
       </c>
       <c r="B89" t="n">
-        <v>79623</v>
+        <v>91904</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10130,41 +10130,44 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503592</v>
+        <v>503748</v>
       </c>
       <c r="R89" t="n">
-        <v>7134781</v>
+        <v>7134611</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10196,12 +10199,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10220,10 +10229,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076633</v>
+        <v>120076643</v>
       </c>
       <c r="B90" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10236,21 +10245,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10260,10 +10269,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503430</v>
+        <v>503820</v>
       </c>
       <c r="R90" t="n">
-        <v>7134677</v>
+        <v>7134705</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10322,10 +10331,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076672</v>
+        <v>120076653</v>
       </c>
       <c r="B91" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10334,25 +10343,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10362,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503543</v>
+        <v>503608</v>
       </c>
       <c r="R91" t="n">
-        <v>7134573</v>
+        <v>7134763</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10424,10 +10433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076631</v>
+        <v>120076625</v>
       </c>
       <c r="B92" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10440,21 +10449,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503624</v>
+        <v>503539</v>
       </c>
       <c r="R92" t="n">
-        <v>7134757</v>
+        <v>7134558</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10526,10 +10535,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120065097</v>
+        <v>120076624</v>
       </c>
       <c r="B93" t="n">
-        <v>91904</v>
+        <v>78279</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10538,44 +10547,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232140</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503748</v>
+        <v>503630</v>
       </c>
       <c r="R93" t="n">
-        <v>7134611</v>
+        <v>7134529</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10607,18 +10613,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076600</v>
+        <v>120076636</v>
       </c>
       <c r="B94" t="n">
-        <v>79131</v>
+        <v>79659</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10649,25 +10649,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503603</v>
+        <v>503530</v>
       </c>
       <c r="R94" t="n">
-        <v>7134592</v>
+        <v>7134813</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10739,10 +10739,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076646</v>
+        <v>120076652</v>
       </c>
       <c r="B95" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10751,25 +10751,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503675</v>
+        <v>503526</v>
       </c>
       <c r="R95" t="n">
-        <v>7134737</v>
+        <v>7134815</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10841,10 +10841,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076625</v>
+        <v>120076633</v>
       </c>
       <c r="B96" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503539</v>
+        <v>503430</v>
       </c>
       <c r="R96" t="n">
-        <v>7134558</v>
+        <v>7134677</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10943,10 +10943,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076609</v>
+        <v>120076675</v>
       </c>
       <c r="B97" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10955,25 +10955,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503567</v>
+        <v>503542</v>
       </c>
       <c r="R97" t="n">
-        <v>7134773</v>
+        <v>7134610</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11045,10 +11045,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076602</v>
+        <v>120076671</v>
       </c>
       <c r="B98" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11057,25 +11057,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11085,10 +11085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503489</v>
+        <v>503546</v>
       </c>
       <c r="R98" t="n">
-        <v>7134637</v>
+        <v>7134587</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11147,7 +11147,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076616</v>
+        <v>120076610</v>
       </c>
       <c r="B99" t="n">
         <v>79624</v>
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503430</v>
+        <v>503592</v>
       </c>
       <c r="R99" t="n">
-        <v>7134700</v>
+        <v>7134781</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11249,10 +11249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076686</v>
+        <v>120076665</v>
       </c>
       <c r="B100" t="n">
-        <v>79658</v>
+        <v>78187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11261,25 +11261,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503428</v>
+        <v>503480</v>
       </c>
       <c r="R100" t="n">
-        <v>7134677</v>
+        <v>7134647</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11351,10 +11351,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076617</v>
+        <v>120076614</v>
       </c>
       <c r="B101" t="n">
-        <v>96891</v>
+        <v>79624</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11363,25 +11363,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503847</v>
+        <v>503427</v>
       </c>
       <c r="R101" t="n">
-        <v>7134693</v>
+        <v>7134675</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11453,10 +11453,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076615</v>
+        <v>120076619</v>
       </c>
       <c r="B102" t="n">
-        <v>79624</v>
+        <v>91850</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11469,21 +11469,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>4361</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11493,10 +11493,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503430</v>
+        <v>503460</v>
       </c>
       <c r="R102" t="n">
-        <v>7134677</v>
+        <v>7134749</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11555,10 +11555,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076613</v>
+        <v>120076630</v>
       </c>
       <c r="B103" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11571,21 +11571,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503646</v>
+        <v>503592</v>
       </c>
       <c r="R103" t="n">
-        <v>7134570</v>
+        <v>7134781</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11657,10 +11657,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076650</v>
+        <v>120076628</v>
       </c>
       <c r="B104" t="n">
-        <v>90594</v>
+        <v>79623</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11673,21 +11673,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503633</v>
+        <v>503570</v>
       </c>
       <c r="R104" t="n">
-        <v>7134566</v>
+        <v>7134765</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11759,10 +11759,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076664</v>
+        <v>120076638</v>
       </c>
       <c r="B105" t="n">
-        <v>78187</v>
+        <v>79659</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11771,25 +11771,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503543</v>
+        <v>503819</v>
       </c>
       <c r="R105" t="n">
-        <v>7134608</v>
+        <v>7134668</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11861,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076641</v>
+        <v>120076605</v>
       </c>
       <c r="B106" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11873,25 +11873,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503745</v>
+        <v>503568</v>
       </c>
       <c r="R106" t="n">
-        <v>7134697</v>
+        <v>7134774</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076636</v>
+        <v>120076613</v>
       </c>
       <c r="B108" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12077,25 +12077,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12105,10 +12105,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503530</v>
+        <v>503646</v>
       </c>
       <c r="R108" t="n">
-        <v>7134813</v>
+        <v>7134570</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12167,10 +12167,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076623</v>
+        <v>120076612</v>
       </c>
       <c r="B109" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12183,21 +12183,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503665</v>
+        <v>503818</v>
       </c>
       <c r="R109" t="n">
-        <v>7134523</v>
+        <v>7134671</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12269,7 +12269,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076610</v>
+        <v>120076616</v>
       </c>
       <c r="B110" t="n">
         <v>79624</v>
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503592</v>
+        <v>503430</v>
       </c>
       <c r="R110" t="n">
-        <v>7134781</v>
+        <v>7134700</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12371,10 +12371,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076674</v>
+        <v>120076687</v>
       </c>
       <c r="B111" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12383,25 +12383,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503558</v>
+        <v>503491</v>
       </c>
       <c r="R111" t="n">
-        <v>7134614</v>
+        <v>7134636</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12473,10 +12473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076673</v>
+        <v>120076601</v>
       </c>
       <c r="B112" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12485,25 +12485,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503532</v>
+        <v>503546</v>
       </c>
       <c r="R112" t="n">
-        <v>7134595</v>
+        <v>7134565</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076662</v>
+        <v>120076608</v>
       </c>
       <c r="B113" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12591,21 +12591,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503535</v>
+        <v>503530</v>
       </c>
       <c r="R113" t="n">
-        <v>7134599</v>
+        <v>7134813</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076605</v>
+        <v>120076602</v>
       </c>
       <c r="B114" t="n">
-        <v>79652</v>
+        <v>89650</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12689,25 +12689,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503568</v>
+        <v>503489</v>
       </c>
       <c r="R114" t="n">
-        <v>7134774</v>
+        <v>7134637</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076601</v>
+        <v>120076684</v>
       </c>
       <c r="B115" t="n">
-        <v>79131</v>
+        <v>79658</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12791,25 +12791,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503546</v>
+        <v>503568</v>
       </c>
       <c r="R115" t="n">
-        <v>7134565</v>
+        <v>7134774</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076671</v>
+        <v>120076631</v>
       </c>
       <c r="B116" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12893,25 +12893,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503546</v>
+        <v>503624</v>
       </c>
       <c r="R116" t="n">
-        <v>7134587</v>
+        <v>7134757</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076619</v>
+        <v>120076660</v>
       </c>
       <c r="B117" t="n">
-        <v>91850</v>
+        <v>78187</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12999,21 +12999,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503460</v>
+        <v>503616</v>
       </c>
       <c r="R117" t="n">
-        <v>7134749</v>
+        <v>7134591</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076648</v>
+        <v>120076677</v>
       </c>
       <c r="B118" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503495</v>
+        <v>503481</v>
       </c>
       <c r="R118" t="n">
-        <v>7134638</v>
+        <v>7134655</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076654</v>
+        <v>120076651</v>
       </c>
       <c r="B119" t="n">
-        <v>78542</v>
+        <v>90730</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503821</v>
+        <v>503516</v>
       </c>
       <c r="R119" t="n">
-        <v>7134659</v>
+        <v>7134622</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,7 +13289,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076647</v>
+        <v>120076646</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503790</v>
+        <v>503675</v>
       </c>
       <c r="R120" t="n">
-        <v>7134698</v>
+        <v>7134737</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076645</v>
+        <v>120076600</v>
       </c>
       <c r="B121" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503601</v>
+        <v>503603</v>
       </c>
       <c r="R121" t="n">
-        <v>7134773</v>
+        <v>7134592</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076626</v>
+        <v>120076640</v>
       </c>
       <c r="B122" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13509,21 +13509,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503534</v>
+        <v>503654</v>
       </c>
       <c r="R122" t="n">
-        <v>7134804</v>
+        <v>7134725</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076652</v>
+        <v>120076641</v>
       </c>
       <c r="B123" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503526</v>
+        <v>503745</v>
       </c>
       <c r="R123" t="n">
-        <v>7134815</v>
+        <v>7134697</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,7 +13697,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076608</v>
+        <v>120076609</v>
       </c>
       <c r="B124" t="n">
         <v>79624</v>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503530</v>
+        <v>503567</v>
       </c>
       <c r="R124" t="n">
-        <v>7134813</v>
+        <v>7134773</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076649</v>
+        <v>120076639</v>
       </c>
       <c r="B125" t="n">
-        <v>90576</v>
+        <v>79659</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,25 +13811,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503835</v>
+        <v>503430</v>
       </c>
       <c r="R125" t="n">
-        <v>7134640</v>
+        <v>7134677</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076614</v>
+        <v>120076634</v>
       </c>
       <c r="B126" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503427</v>
+        <v>503432</v>
       </c>
       <c r="R126" t="n">
-        <v>7134675</v>
+        <v>7134696</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076665</v>
+        <v>120076647</v>
       </c>
       <c r="B127" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503480</v>
+        <v>503790</v>
       </c>
       <c r="R127" t="n">
-        <v>7134647</v>
+        <v>7134698</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076629</v>
+        <v>120076650</v>
       </c>
       <c r="B128" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503568</v>
+        <v>503633</v>
       </c>
       <c r="R128" t="n">
-        <v>7134773</v>
+        <v>7134566</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076627</v>
+        <v>120076686</v>
       </c>
       <c r="B129" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14219,25 +14219,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503531</v>
+        <v>503428</v>
       </c>
       <c r="R129" t="n">
-        <v>7134812</v>
+        <v>7134677</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076687</v>
+        <v>120076645</v>
       </c>
       <c r="B130" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14321,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503491</v>
+        <v>503601</v>
       </c>
       <c r="R130" t="n">
-        <v>7134636</v>
+        <v>7134773</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076618</v>
+        <v>120076644</v>
       </c>
       <c r="B131" t="n">
-        <v>96891</v>
+        <v>78278</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14423,25 +14423,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503850</v>
+        <v>503748</v>
       </c>
       <c r="R131" t="n">
-        <v>7134617</v>
+        <v>7134611</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076620</v>
+        <v>120076674</v>
       </c>
       <c r="B132" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14525,25 +14525,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503618</v>
+        <v>503558</v>
       </c>
       <c r="R132" t="n">
-        <v>7134495</v>
+        <v>7134614</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14615,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076675</v>
+        <v>120076611</v>
       </c>
       <c r="B133" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14627,25 +14627,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14655,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503542</v>
+        <v>503691</v>
       </c>
       <c r="R133" t="n">
-        <v>7134610</v>
+        <v>7134749</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14717,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076670</v>
+        <v>120076599</v>
       </c>
       <c r="B134" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14733,21 +14733,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503626</v>
+        <v>503657</v>
       </c>
       <c r="R134" t="n">
-        <v>7134549</v>
+        <v>7134513</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076677</v>
+        <v>120076635</v>
       </c>
       <c r="B135" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503481</v>
+        <v>503426</v>
       </c>
       <c r="R135" t="n">
-        <v>7134655</v>
+        <v>7134704</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076660</v>
+        <v>120076626</v>
       </c>
       <c r="B136" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14937,21 +14937,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503616</v>
+        <v>503534</v>
       </c>
       <c r="R136" t="n">
-        <v>7134591</v>
+        <v>7134804</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076639</v>
+        <v>120076670</v>
       </c>
       <c r="B137" t="n">
-        <v>79659</v>
+        <v>91858</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15039,21 +15039,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503430</v>
+        <v>503626</v>
       </c>
       <c r="R137" t="n">
-        <v>7134677</v>
+        <v>7134549</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120035871</v>
+        <v>120035460</v>
       </c>
       <c r="B45" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504192</v>
+        <v>504169</v>
       </c>
       <c r="R45" t="n">
-        <v>7134481</v>
+        <v>7134407</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5717,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120035460</v>
+        <v>120035871</v>
       </c>
       <c r="B46" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5733,21 +5733,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,13 +5757,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504169</v>
+        <v>504192</v>
       </c>
       <c r="R46" t="n">
-        <v>7134407</v>
+        <v>7134481</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076649</v>
+        <v>120076672</v>
       </c>
       <c r="B71" t="n">
-        <v>90576</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503835</v>
+        <v>503543</v>
       </c>
       <c r="R71" t="n">
-        <v>7134640</v>
+        <v>7134573</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076615</v>
+        <v>120076649</v>
       </c>
       <c r="B72" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,21 +8395,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503430</v>
+        <v>503835</v>
       </c>
       <c r="R72" t="n">
-        <v>7134677</v>
+        <v>7134640</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076672</v>
+        <v>120076615</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503543</v>
+        <v>503430</v>
       </c>
       <c r="R73" t="n">
-        <v>7134573</v>
+        <v>7134677</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076648</v>
+        <v>120076629</v>
       </c>
       <c r="B80" t="n">
-        <v>89247</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9207,25 +9207,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1596</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503495</v>
+        <v>503568</v>
       </c>
       <c r="R80" t="n">
-        <v>7134638</v>
+        <v>7134773</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076629</v>
+        <v>120076637</v>
       </c>
       <c r="B81" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9309,25 +9309,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503568</v>
+        <v>503530</v>
       </c>
       <c r="R81" t="n">
-        <v>7134773</v>
+        <v>7134806</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076637</v>
+        <v>120076648</v>
       </c>
       <c r="B82" t="n">
-        <v>79659</v>
+        <v>89247</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9411,25 +9411,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>1596</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503530</v>
+        <v>503495</v>
       </c>
       <c r="R82" t="n">
-        <v>7134806</v>
+        <v>7134638</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9812,10 +9812,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076662</v>
+        <v>120076620</v>
       </c>
       <c r="B86" t="n">
-        <v>78187</v>
+        <v>92048</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9828,21 +9828,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503535</v>
+        <v>503618</v>
       </c>
       <c r="R86" t="n">
-        <v>7134599</v>
+        <v>7134495</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9914,10 +9914,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076685</v>
+        <v>120076662</v>
       </c>
       <c r="B87" t="n">
-        <v>79658</v>
+        <v>78187</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9926,25 +9926,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503819</v>
+        <v>503535</v>
       </c>
       <c r="R87" t="n">
-        <v>7134668</v>
+        <v>7134599</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10016,10 +10016,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076620</v>
+        <v>120076685</v>
       </c>
       <c r="B88" t="n">
-        <v>92048</v>
+        <v>79658</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10028,25 +10028,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503618</v>
+        <v>503819</v>
       </c>
       <c r="R88" t="n">
-        <v>7134495</v>
+        <v>7134668</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10433,10 +10433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076625</v>
+        <v>120076636</v>
       </c>
       <c r="B92" t="n">
-        <v>78279</v>
+        <v>79659</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10445,25 +10445,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503539</v>
+        <v>503530</v>
       </c>
       <c r="R92" t="n">
-        <v>7134558</v>
+        <v>7134813</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10535,10 +10535,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076624</v>
+        <v>120076652</v>
       </c>
       <c r="B93" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10551,21 +10551,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503630</v>
+        <v>503526</v>
       </c>
       <c r="R93" t="n">
-        <v>7134529</v>
+        <v>7134815</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076636</v>
+        <v>120076625</v>
       </c>
       <c r="B94" t="n">
-        <v>79659</v>
+        <v>78279</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10649,25 +10649,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503530</v>
+        <v>503539</v>
       </c>
       <c r="R94" t="n">
-        <v>7134813</v>
+        <v>7134558</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10739,10 +10739,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076652</v>
+        <v>120076624</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10755,21 +10755,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503526</v>
+        <v>503630</v>
       </c>
       <c r="R95" t="n">
-        <v>7134815</v>
+        <v>7134529</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10943,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076675</v>
+        <v>120076671</v>
       </c>
       <c r="B97" t="n">
         <v>91858</v>
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503542</v>
+        <v>503546</v>
       </c>
       <c r="R97" t="n">
-        <v>7134610</v>
+        <v>7134587</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11045,10 +11045,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076671</v>
+        <v>120076610</v>
       </c>
       <c r="B98" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11057,25 +11057,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11085,10 +11085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503546</v>
+        <v>503592</v>
       </c>
       <c r="R98" t="n">
-        <v>7134587</v>
+        <v>7134781</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11147,10 +11147,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076610</v>
+        <v>120076675</v>
       </c>
       <c r="B99" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11159,25 +11159,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503592</v>
+        <v>503542</v>
       </c>
       <c r="R99" t="n">
-        <v>7134781</v>
+        <v>7134610</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076677</v>
+        <v>120076646</v>
       </c>
       <c r="B118" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503481</v>
+        <v>503675</v>
       </c>
       <c r="R118" t="n">
-        <v>7134655</v>
+        <v>7134737</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076651</v>
+        <v>120076600</v>
       </c>
       <c r="B119" t="n">
-        <v>90730</v>
+        <v>79131</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503516</v>
+        <v>503603</v>
       </c>
       <c r="R119" t="n">
-        <v>7134622</v>
+        <v>7134592</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076646</v>
+        <v>120076651</v>
       </c>
       <c r="B120" t="n">
-        <v>97930</v>
+        <v>90730</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13305,21 +13305,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503675</v>
+        <v>503516</v>
       </c>
       <c r="R120" t="n">
-        <v>7134737</v>
+        <v>7134622</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076600</v>
+        <v>120076677</v>
       </c>
       <c r="B121" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503603</v>
+        <v>503481</v>
       </c>
       <c r="R121" t="n">
-        <v>7134592</v>
+        <v>7134655</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076640</v>
+        <v>120076639</v>
       </c>
       <c r="B122" t="n">
-        <v>78278</v>
+        <v>79659</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503654</v>
+        <v>503430</v>
       </c>
       <c r="R122" t="n">
-        <v>7134725</v>
+        <v>7134677</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,7 +13595,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076641</v>
+        <v>120076640</v>
       </c>
       <c r="B123" t="n">
         <v>78278</v>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503745</v>
+        <v>503654</v>
       </c>
       <c r="R123" t="n">
-        <v>7134697</v>
+        <v>7134725</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076609</v>
+        <v>120076641</v>
       </c>
       <c r="B124" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13713,21 +13713,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503567</v>
+        <v>503745</v>
       </c>
       <c r="R124" t="n">
-        <v>7134773</v>
+        <v>7134697</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076639</v>
+        <v>120076609</v>
       </c>
       <c r="B125" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,25 +13811,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503430</v>
+        <v>503567</v>
       </c>
       <c r="R125" t="n">
-        <v>7134677</v>
+        <v>7134773</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076626</v>
+        <v>120076670</v>
       </c>
       <c r="B136" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,25 +14933,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503534</v>
+        <v>503626</v>
       </c>
       <c r="R136" t="n">
-        <v>7134804</v>
+        <v>7134549</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076670</v>
+        <v>120076626</v>
       </c>
       <c r="B137" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15035,25 +15035,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503626</v>
+        <v>503534</v>
       </c>
       <c r="R137" t="n">
-        <v>7134549</v>
+        <v>7134804</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,7 +5513,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120035768</v>
+        <v>120036022</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504187</v>
+        <v>504145</v>
       </c>
       <c r="R44" t="n">
-        <v>7134438</v>
+        <v>7134441</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120035460</v>
+        <v>120036399</v>
       </c>
       <c r="B45" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504169</v>
+        <v>504083</v>
       </c>
       <c r="R45" t="n">
-        <v>7134407</v>
+        <v>7134453</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,6 +5691,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5717,10 +5722,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120035871</v>
+        <v>120038086</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5733,21 +5738,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,13 +5762,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504192</v>
+        <v>503980</v>
       </c>
       <c r="R46" t="n">
-        <v>7134481</v>
+        <v>7134422</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,10 +5824,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120040383</v>
+        <v>120035868</v>
       </c>
       <c r="B47" t="n">
-        <v>90825</v>
+        <v>78279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5831,38 +5836,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503879</v>
+        <v>504193</v>
       </c>
       <c r="R47" t="n">
-        <v>7134575</v>
+        <v>7134477</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5921,10 +5926,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035542</v>
+        <v>120035474</v>
       </c>
       <c r="B48" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5933,25 +5938,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,13 +5966,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504175</v>
+        <v>504166</v>
       </c>
       <c r="R48" t="n">
-        <v>7134410</v>
+        <v>7134391</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6023,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120039375</v>
+        <v>120035622</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6039,21 +6044,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6063,13 +6068,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503988</v>
+        <v>504165</v>
       </c>
       <c r="R49" t="n">
-        <v>7134466</v>
+        <v>7134407</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6125,10 +6130,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120034479</v>
+        <v>120035460</v>
       </c>
       <c r="B50" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6141,21 +6146,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6165,10 +6170,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504252</v>
+        <v>504169</v>
       </c>
       <c r="R50" t="n">
-        <v>7134346</v>
+        <v>7134407</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6227,10 +6232,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120035622</v>
+        <v>120039375</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6243,21 +6248,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6267,13 +6272,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504165</v>
+        <v>503988</v>
       </c>
       <c r="R51" t="n">
-        <v>7134407</v>
+        <v>7134466</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6329,10 +6334,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120035291</v>
+        <v>120034826</v>
       </c>
       <c r="B52" t="n">
-        <v>4863</v>
+        <v>91862</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6341,25 +6346,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101675</v>
+        <v>4365</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6369,13 +6374,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504179</v>
+        <v>504226</v>
       </c>
       <c r="R52" t="n">
-        <v>7134372</v>
+        <v>7134339</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6405,11 +6410,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6436,10 +6436,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120035474</v>
+        <v>120035768</v>
       </c>
       <c r="B53" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6448,25 +6448,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504166</v>
+        <v>504187</v>
       </c>
       <c r="R53" t="n">
-        <v>7134391</v>
+        <v>7134438</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120036399</v>
+        <v>120035291</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>4863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,25 +6550,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>101675</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504083</v>
+        <v>504179</v>
       </c>
       <c r="R54" t="n">
-        <v>7134453</v>
+        <v>7134372</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6645,10 +6645,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120036022</v>
+        <v>120035542</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6661,21 +6661,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504145</v>
+        <v>504175</v>
       </c>
       <c r="R55" t="n">
-        <v>7134441</v>
+        <v>7134410</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,10 +6747,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120034574</v>
+        <v>120034383</v>
       </c>
       <c r="B56" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6763,21 +6763,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504224</v>
+        <v>504257</v>
       </c>
       <c r="R56" t="n">
-        <v>7134352</v>
+        <v>7134334</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035015</v>
+        <v>120040383</v>
       </c>
       <c r="B57" t="n">
-        <v>78278</v>
+        <v>90825</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6861,41 +6861,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504196</v>
+        <v>503879</v>
       </c>
       <c r="R57" t="n">
-        <v>7134350</v>
+        <v>7134575</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120035868</v>
+        <v>120035015</v>
       </c>
       <c r="B58" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504193</v>
+        <v>504196</v>
       </c>
       <c r="R58" t="n">
-        <v>7134477</v>
+        <v>7134350</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120034383</v>
+        <v>120034574</v>
       </c>
       <c r="B59" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7093,13 +7093,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504257</v>
+        <v>504224</v>
       </c>
       <c r="R59" t="n">
-        <v>7134334</v>
+        <v>7134352</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120034826</v>
+        <v>120035871</v>
       </c>
       <c r="B60" t="n">
-        <v>91862</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504226</v>
+        <v>504192</v>
       </c>
       <c r="R60" t="n">
-        <v>7134339</v>
+        <v>7134481</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120038086</v>
+        <v>120034479</v>
       </c>
       <c r="B61" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503980</v>
+        <v>504252</v>
       </c>
       <c r="R61" t="n">
-        <v>7134422</v>
+        <v>7134346</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120046464</v>
+        <v>120046468</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,25 +7371,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503874</v>
+        <v>503899</v>
       </c>
       <c r="R62" t="n">
-        <v>7134566</v>
+        <v>7134531</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120039963</v>
+        <v>120038261</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -7501,13 +7501,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503904</v>
+        <v>503997</v>
       </c>
       <c r="R63" t="n">
-        <v>7134523</v>
+        <v>7134441</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120046468</v>
+        <v>120046464</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,25 +7575,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503899</v>
+        <v>503874</v>
       </c>
       <c r="R64" t="n">
-        <v>7134531</v>
+        <v>7134566</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120038261</v>
+        <v>120046465</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,41 +7677,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503997</v>
+        <v>504001</v>
       </c>
       <c r="R65" t="n">
-        <v>7134441</v>
+        <v>7134466</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120046465</v>
+        <v>120039963</v>
       </c>
       <c r="B66" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7779,41 +7779,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504001</v>
+        <v>503904</v>
       </c>
       <c r="R66" t="n">
-        <v>7134466</v>
+        <v>7134523</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076673</v>
+        <v>120076674</v>
       </c>
       <c r="B67" t="n">
         <v>91858</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503532</v>
+        <v>503558</v>
       </c>
       <c r="R67" t="n">
-        <v>7134595</v>
+        <v>7134614</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076661</v>
+        <v>120076646</v>
       </c>
       <c r="B68" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,25 +7983,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503604</v>
+        <v>503675</v>
       </c>
       <c r="R68" t="n">
-        <v>7134590</v>
+        <v>7134737</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076654</v>
+        <v>120076664</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503821</v>
+        <v>503543</v>
       </c>
       <c r="R69" t="n">
-        <v>7134659</v>
+        <v>7134608</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076623</v>
+        <v>120076616</v>
       </c>
       <c r="B70" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8191,21 +8191,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503665</v>
+        <v>503430</v>
       </c>
       <c r="R70" t="n">
-        <v>7134523</v>
+        <v>7134700</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076672</v>
+        <v>120076670</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503543</v>
+        <v>503626</v>
       </c>
       <c r="R71" t="n">
-        <v>7134573</v>
+        <v>7134549</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076649</v>
+        <v>120076687</v>
       </c>
       <c r="B72" t="n">
-        <v>90576</v>
+        <v>91852</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,21 +8395,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503835</v>
+        <v>503491</v>
       </c>
       <c r="R72" t="n">
-        <v>7134640</v>
+        <v>7134636</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076615</v>
+        <v>120076628</v>
       </c>
       <c r="B73" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8497,21 +8497,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503430</v>
+        <v>503570</v>
       </c>
       <c r="R73" t="n">
-        <v>7134677</v>
+        <v>7134765</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076617</v>
+        <v>120076640</v>
       </c>
       <c r="B74" t="n">
-        <v>96891</v>
+        <v>78278</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503847</v>
+        <v>503654</v>
       </c>
       <c r="R74" t="n">
-        <v>7134693</v>
+        <v>7134725</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076618</v>
+        <v>120076649</v>
       </c>
       <c r="B75" t="n">
-        <v>96891</v>
+        <v>90576</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,25 +8697,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503850</v>
+        <v>503835</v>
       </c>
       <c r="R75" t="n">
-        <v>7134617</v>
+        <v>7134640</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076606</v>
+        <v>120076650</v>
       </c>
       <c r="B76" t="n">
-        <v>79652</v>
+        <v>90594</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503427</v>
+        <v>503633</v>
       </c>
       <c r="R76" t="n">
-        <v>7134680</v>
+        <v>7134566</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076664</v>
+        <v>120076671</v>
       </c>
       <c r="B77" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503543</v>
+        <v>503546</v>
       </c>
       <c r="R77" t="n">
-        <v>7134608</v>
+        <v>7134587</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076627</v>
+        <v>120076675</v>
       </c>
       <c r="B78" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9003,25 +9003,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503531</v>
+        <v>503542</v>
       </c>
       <c r="R78" t="n">
-        <v>7134812</v>
+        <v>7134610</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120064794</v>
+        <v>120076627</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9105,41 +9105,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503729</v>
+        <v>503531</v>
       </c>
       <c r="R79" t="n">
-        <v>7134606</v>
+        <v>7134812</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076629</v>
+        <v>120076665</v>
       </c>
       <c r="B80" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9211,21 +9211,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503568</v>
+        <v>503480</v>
       </c>
       <c r="R80" t="n">
-        <v>7134773</v>
+        <v>7134647</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076637</v>
+        <v>120076614</v>
       </c>
       <c r="B81" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9309,25 +9309,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503530</v>
+        <v>503427</v>
       </c>
       <c r="R81" t="n">
-        <v>7134806</v>
+        <v>7134675</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076648</v>
+        <v>120076605</v>
       </c>
       <c r="B82" t="n">
-        <v>89247</v>
+        <v>79652</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9411,25 +9411,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1596</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503495</v>
+        <v>503568</v>
       </c>
       <c r="R82" t="n">
-        <v>7134638</v>
+        <v>7134774</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076676</v>
+        <v>120076633</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9513,25 +9513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503536</v>
+        <v>503430</v>
       </c>
       <c r="R83" t="n">
-        <v>7134619</v>
+        <v>7134677</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,7 +9603,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120060142</v>
+        <v>120076673</v>
       </c>
       <c r="B84" t="n">
         <v>91858</v>
@@ -9639,17 +9639,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503497</v>
+        <v>503532</v>
       </c>
       <c r="R84" t="n">
-        <v>7134657</v>
+        <v>7134595</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076681</v>
+        <v>120076661</v>
       </c>
       <c r="B85" t="n">
-        <v>12337</v>
+        <v>78187</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9717,25 +9717,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>101283</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503867</v>
+        <v>503604</v>
       </c>
       <c r="R85" t="n">
-        <v>7134650</v>
+        <v>7134590</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9781,11 +9781,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9812,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076620</v>
+        <v>120076613</v>
       </c>
       <c r="B86" t="n">
-        <v>92048</v>
+        <v>79624</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9828,21 +9823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9852,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503618</v>
+        <v>503646</v>
       </c>
       <c r="R86" t="n">
-        <v>7134495</v>
+        <v>7134570</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9914,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076662</v>
+        <v>120060142</v>
       </c>
       <c r="B87" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9926,41 +9921,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503535</v>
+        <v>503497</v>
       </c>
       <c r="R87" t="n">
-        <v>7134599</v>
+        <v>7134657</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10016,7 +10011,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076685</v>
+        <v>120076686</v>
       </c>
       <c r="B88" t="n">
         <v>79658</v>
@@ -10056,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503819</v>
+        <v>503428</v>
       </c>
       <c r="R88" t="n">
-        <v>7134668</v>
+        <v>7134677</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10118,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120065097</v>
+        <v>120076639</v>
       </c>
       <c r="B89" t="n">
-        <v>91904</v>
+        <v>79659</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10130,44 +10125,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>232140</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503748</v>
+        <v>503430</v>
       </c>
       <c r="R89" t="n">
-        <v>7134611</v>
+        <v>7134677</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10199,18 +10191,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10229,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076643</v>
+        <v>120076606</v>
       </c>
       <c r="B90" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10241,25 +10227,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10269,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503820</v>
+        <v>503427</v>
       </c>
       <c r="R90" t="n">
-        <v>7134705</v>
+        <v>7134680</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10331,10 +10317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076653</v>
+        <v>120076626</v>
       </c>
       <c r="B91" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10347,21 +10333,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503608</v>
+        <v>503534</v>
       </c>
       <c r="R91" t="n">
-        <v>7134763</v>
+        <v>7134804</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10433,10 +10419,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076636</v>
+        <v>120076600</v>
       </c>
       <c r="B92" t="n">
-        <v>79659</v>
+        <v>79131</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10445,25 +10431,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10459,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503530</v>
+        <v>503603</v>
       </c>
       <c r="R92" t="n">
-        <v>7134813</v>
+        <v>7134592</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10535,10 +10521,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076652</v>
+        <v>120076618</v>
       </c>
       <c r="B93" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10547,25 +10533,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10561,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503526</v>
+        <v>503850</v>
       </c>
       <c r="R93" t="n">
-        <v>7134815</v>
+        <v>7134617</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10637,10 +10623,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076625</v>
+        <v>120076620</v>
       </c>
       <c r="B94" t="n">
-        <v>78279</v>
+        <v>92048</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10653,21 +10639,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10677,10 +10663,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503539</v>
+        <v>503618</v>
       </c>
       <c r="R94" t="n">
-        <v>7134558</v>
+        <v>7134495</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10739,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076624</v>
+        <v>120076629</v>
       </c>
       <c r="B95" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10755,21 +10741,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10779,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503630</v>
+        <v>503568</v>
       </c>
       <c r="R95" t="n">
-        <v>7134529</v>
+        <v>7134773</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10841,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076633</v>
+        <v>120076636</v>
       </c>
       <c r="B96" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10853,25 +10839,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10881,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503430</v>
+        <v>503530</v>
       </c>
       <c r="R96" t="n">
-        <v>7134677</v>
+        <v>7134813</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10943,7 +10929,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076671</v>
+        <v>120076676</v>
       </c>
       <c r="B97" t="n">
         <v>91858</v>
@@ -10983,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503546</v>
+        <v>503536</v>
       </c>
       <c r="R97" t="n">
-        <v>7134587</v>
+        <v>7134619</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11045,10 +11031,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076610</v>
+        <v>120076630</v>
       </c>
       <c r="B98" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11061,21 +11047,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11147,10 +11133,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076675</v>
+        <v>120076637</v>
       </c>
       <c r="B99" t="n">
-        <v>91858</v>
+        <v>79659</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11163,21 +11149,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11187,10 +11173,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503542</v>
+        <v>503530</v>
       </c>
       <c r="R99" t="n">
-        <v>7134610</v>
+        <v>7134806</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11249,10 +11235,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076665</v>
+        <v>120076641</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11265,21 +11251,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11289,10 +11275,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503480</v>
+        <v>503745</v>
       </c>
       <c r="R100" t="n">
-        <v>7134647</v>
+        <v>7134697</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11351,10 +11337,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076614</v>
+        <v>120076645</v>
       </c>
       <c r="B101" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11363,25 +11349,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11391,10 +11377,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503427</v>
+        <v>503601</v>
       </c>
       <c r="R101" t="n">
-        <v>7134675</v>
+        <v>7134773</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11453,10 +11439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076619</v>
+        <v>120076610</v>
       </c>
       <c r="B102" t="n">
-        <v>91850</v>
+        <v>79624</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11469,21 +11455,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4361</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11493,10 +11479,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503460</v>
+        <v>503592</v>
       </c>
       <c r="R102" t="n">
-        <v>7134749</v>
+        <v>7134781</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11555,10 +11541,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076630</v>
+        <v>120076681</v>
       </c>
       <c r="B103" t="n">
-        <v>79623</v>
+        <v>12337</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11567,25 +11553,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>101283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11595,10 +11581,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503592</v>
+        <v>503867</v>
       </c>
       <c r="R103" t="n">
-        <v>7134781</v>
+        <v>7134650</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11631,6 +11617,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11657,10 +11648,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076628</v>
+        <v>120076619</v>
       </c>
       <c r="B104" t="n">
-        <v>79623</v>
+        <v>91850</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11673,21 +11664,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11697,10 +11688,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503570</v>
+        <v>503460</v>
       </c>
       <c r="R104" t="n">
-        <v>7134765</v>
+        <v>7134749</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11759,10 +11750,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076638</v>
+        <v>120076602</v>
       </c>
       <c r="B105" t="n">
-        <v>79659</v>
+        <v>89650</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11771,25 +11762,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11799,10 +11790,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503819</v>
+        <v>503489</v>
       </c>
       <c r="R105" t="n">
-        <v>7134668</v>
+        <v>7134637</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11861,10 +11852,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076605</v>
+        <v>120076684</v>
       </c>
       <c r="B106" t="n">
-        <v>79652</v>
+        <v>79658</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11877,21 +11868,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11963,7 +11954,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076632</v>
+        <v>120076635</v>
       </c>
       <c r="B107" t="n">
         <v>79623</v>
@@ -12003,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503434</v>
+        <v>503426</v>
       </c>
       <c r="R107" t="n">
-        <v>7134673</v>
+        <v>7134704</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12065,10 +12056,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076613</v>
+        <v>120076634</v>
       </c>
       <c r="B108" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12081,21 +12072,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12105,10 +12096,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503646</v>
+        <v>503432</v>
       </c>
       <c r="R108" t="n">
-        <v>7134570</v>
+        <v>7134696</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12167,10 +12158,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076612</v>
+        <v>120064794</v>
       </c>
       <c r="B109" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12179,41 +12170,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503818</v>
+        <v>503729</v>
       </c>
       <c r="R109" t="n">
-        <v>7134671</v>
+        <v>7134606</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12269,10 +12260,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076616</v>
+        <v>120076599</v>
       </c>
       <c r="B110" t="n">
-        <v>79624</v>
+        <v>90545</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12281,25 +12272,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12309,10 +12300,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503430</v>
+        <v>503657</v>
       </c>
       <c r="R110" t="n">
-        <v>7134700</v>
+        <v>7134513</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12371,10 +12362,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076687</v>
+        <v>120076654</v>
       </c>
       <c r="B111" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12387,21 +12378,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12411,10 +12402,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503491</v>
+        <v>503821</v>
       </c>
       <c r="R111" t="n">
-        <v>7134636</v>
+        <v>7134659</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12473,10 +12464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076601</v>
+        <v>120076651</v>
       </c>
       <c r="B112" t="n">
-        <v>79131</v>
+        <v>90730</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12485,25 +12476,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12504,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503546</v>
+        <v>503516</v>
       </c>
       <c r="R112" t="n">
-        <v>7134565</v>
+        <v>7134622</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,7 +12566,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076608</v>
+        <v>120076611</v>
       </c>
       <c r="B113" t="n">
         <v>79624</v>
@@ -12615,10 +12606,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503530</v>
+        <v>503691</v>
       </c>
       <c r="R113" t="n">
-        <v>7134813</v>
+        <v>7134749</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12668,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076602</v>
+        <v>120076632</v>
       </c>
       <c r="B114" t="n">
-        <v>89650</v>
+        <v>79623</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12693,21 +12684,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12708,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503489</v>
+        <v>503434</v>
       </c>
       <c r="R114" t="n">
-        <v>7134637</v>
+        <v>7134673</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12770,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076684</v>
+        <v>120076644</v>
       </c>
       <c r="B115" t="n">
-        <v>79658</v>
+        <v>78278</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12791,25 +12782,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12810,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503568</v>
+        <v>503748</v>
       </c>
       <c r="R115" t="n">
-        <v>7134774</v>
+        <v>7134611</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,10 +12872,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076631</v>
+        <v>120076624</v>
       </c>
       <c r="B116" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12897,21 +12888,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12912,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503624</v>
+        <v>503630</v>
       </c>
       <c r="R116" t="n">
-        <v>7134757</v>
+        <v>7134529</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12974,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076660</v>
+        <v>120076615</v>
       </c>
       <c r="B117" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12999,21 +12990,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13014,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503616</v>
+        <v>503430</v>
       </c>
       <c r="R117" t="n">
-        <v>7134591</v>
+        <v>7134677</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13076,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076646</v>
+        <v>120076638</v>
       </c>
       <c r="B118" t="n">
-        <v>97930</v>
+        <v>79659</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13088,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13116,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503675</v>
+        <v>503819</v>
       </c>
       <c r="R118" t="n">
-        <v>7134737</v>
+        <v>7134668</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13178,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076600</v>
+        <v>120076631</v>
       </c>
       <c r="B119" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13203,21 +13194,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13218,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503603</v>
+        <v>503624</v>
       </c>
       <c r="R119" t="n">
-        <v>7134592</v>
+        <v>7134757</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13280,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076651</v>
+        <v>120076672</v>
       </c>
       <c r="B120" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13301,25 +13292,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13320,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503516</v>
+        <v>503543</v>
       </c>
       <c r="R120" t="n">
-        <v>7134622</v>
+        <v>7134573</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13382,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076677</v>
+        <v>120076647</v>
       </c>
       <c r="B121" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13394,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13422,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503481</v>
+        <v>503790</v>
       </c>
       <c r="R121" t="n">
-        <v>7134655</v>
+        <v>7134698</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13484,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076639</v>
+        <v>120076601</v>
       </c>
       <c r="B122" t="n">
-        <v>79659</v>
+        <v>79131</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13496,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6464</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13524,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503430</v>
+        <v>503546</v>
       </c>
       <c r="R122" t="n">
-        <v>7134677</v>
+        <v>7134565</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13586,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076640</v>
+        <v>120076677</v>
       </c>
       <c r="B123" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13607,25 +13598,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13626,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503654</v>
+        <v>503481</v>
       </c>
       <c r="R123" t="n">
-        <v>7134725</v>
+        <v>7134655</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13688,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076641</v>
+        <v>120076617</v>
       </c>
       <c r="B124" t="n">
-        <v>78278</v>
+        <v>96891</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13709,25 +13700,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13728,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503745</v>
+        <v>503847</v>
       </c>
       <c r="R124" t="n">
-        <v>7134697</v>
+        <v>7134693</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13790,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076609</v>
+        <v>120076662</v>
       </c>
       <c r="B125" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13815,21 +13806,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13830,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503567</v>
+        <v>503535</v>
       </c>
       <c r="R125" t="n">
-        <v>7134773</v>
+        <v>7134599</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13901,10 +13892,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076634</v>
+        <v>120076609</v>
       </c>
       <c r="B126" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13908,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13932,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503432</v>
+        <v>503567</v>
       </c>
       <c r="R126" t="n">
-        <v>7134696</v>
+        <v>7134773</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +13994,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076647</v>
+        <v>120076612</v>
       </c>
       <c r="B127" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14006,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14034,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503790</v>
+        <v>503818</v>
       </c>
       <c r="R127" t="n">
-        <v>7134698</v>
+        <v>7134671</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14096,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076650</v>
+        <v>120076652</v>
       </c>
       <c r="B128" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14121,21 +14112,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14136,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503633</v>
+        <v>503526</v>
       </c>
       <c r="R128" t="n">
-        <v>7134566</v>
+        <v>7134815</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,7 +14198,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076686</v>
+        <v>120076685</v>
       </c>
       <c r="B129" t="n">
         <v>79658</v>
@@ -14247,10 +14238,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503428</v>
+        <v>503819</v>
       </c>
       <c r="R129" t="n">
-        <v>7134677</v>
+        <v>7134668</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14300,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076645</v>
+        <v>120076625</v>
       </c>
       <c r="B130" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14312,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14340,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503601</v>
+        <v>503539</v>
       </c>
       <c r="R130" t="n">
-        <v>7134773</v>
+        <v>7134558</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14402,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076644</v>
+        <v>120076608</v>
       </c>
       <c r="B131" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14427,21 +14418,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14442,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503748</v>
+        <v>503530</v>
       </c>
       <c r="R131" t="n">
-        <v>7134611</v>
+        <v>7134813</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14504,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076674</v>
+        <v>120076643</v>
       </c>
       <c r="B132" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14525,25 +14516,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14553,10 +14544,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503558</v>
+        <v>503820</v>
       </c>
       <c r="R132" t="n">
-        <v>7134614</v>
+        <v>7134705</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14615,10 +14606,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076611</v>
+        <v>120076648</v>
       </c>
       <c r="B133" t="n">
-        <v>79624</v>
+        <v>89247</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14627,25 +14618,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>1596</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503691</v>
+        <v>503495</v>
       </c>
       <c r="R133" t="n">
-        <v>7134749</v>
+        <v>7134638</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076599</v>
+        <v>120076660</v>
       </c>
       <c r="B134" t="n">
-        <v>90545</v>
+        <v>78187</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14729,25 +14720,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14748,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503657</v>
+        <v>503616</v>
       </c>
       <c r="R134" t="n">
-        <v>7134513</v>
+        <v>7134591</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14810,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076635</v>
+        <v>120076653</v>
       </c>
       <c r="B135" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14835,21 +14826,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14850,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503426</v>
+        <v>503608</v>
       </c>
       <c r="R135" t="n">
-        <v>7134704</v>
+        <v>7134763</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14912,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076670</v>
+        <v>120065097</v>
       </c>
       <c r="B136" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,41 +14924,44 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503626</v>
+        <v>503748</v>
       </c>
       <c r="R136" t="n">
-        <v>7134549</v>
+        <v>7134611</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14999,12 +14993,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076626</v>
+        <v>120076623</v>
       </c>
       <c r="B137" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15039,21 +15039,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503534</v>
+        <v>503665</v>
       </c>
       <c r="R137" t="n">
-        <v>7134804</v>
+        <v>7134523</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -6028,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035622</v>
+        <v>120035460</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6044,21 +6044,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504165</v>
+        <v>504169</v>
       </c>
       <c r="R49" t="n">
         <v>7134407</v>
@@ -6130,10 +6130,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035460</v>
+        <v>120035622</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6146,21 +6146,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504169</v>
+        <v>504165</v>
       </c>
       <c r="R50" t="n">
         <v>7134407</v>
@@ -6334,10 +6334,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120034826</v>
+        <v>120035291</v>
       </c>
       <c r="B52" t="n">
-        <v>91862</v>
+        <v>4863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6346,25 +6346,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4365</v>
+        <v>101675</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6374,13 +6374,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504226</v>
+        <v>504179</v>
       </c>
       <c r="R52" t="n">
-        <v>7134339</v>
+        <v>7134372</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6410,6 +6410,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6436,10 +6441,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120035768</v>
+        <v>120034826</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>91862</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6448,25 +6453,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6476,13 +6481,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504187</v>
+        <v>504226</v>
       </c>
       <c r="R53" t="n">
-        <v>7134438</v>
+        <v>7134339</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,10 +6543,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120035291</v>
+        <v>120035768</v>
       </c>
       <c r="B54" t="n">
-        <v>4863</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,25 +6555,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101675</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6578,10 +6583,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504179</v>
+        <v>504187</v>
       </c>
       <c r="R54" t="n">
-        <v>7134372</v>
+        <v>7134438</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6614,11 +6619,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -10929,10 +10929,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076676</v>
+        <v>120076630</v>
       </c>
       <c r="B97" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10941,25 +10941,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503536</v>
+        <v>503592</v>
       </c>
       <c r="R97" t="n">
-        <v>7134619</v>
+        <v>7134781</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11031,10 +11031,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076630</v>
+        <v>120076637</v>
       </c>
       <c r="B98" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11043,25 +11043,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11071,10 +11071,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503592</v>
+        <v>503530</v>
       </c>
       <c r="R98" t="n">
-        <v>7134781</v>
+        <v>7134806</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11133,10 +11133,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076637</v>
+        <v>120076641</v>
       </c>
       <c r="B99" t="n">
-        <v>79659</v>
+        <v>78278</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11145,25 +11145,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11173,10 +11173,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503530</v>
+        <v>503745</v>
       </c>
       <c r="R99" t="n">
-        <v>7134806</v>
+        <v>7134697</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11235,10 +11235,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076641</v>
+        <v>120076676</v>
       </c>
       <c r="B100" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11247,25 +11247,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11275,10 +11275,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503745</v>
+        <v>503536</v>
       </c>
       <c r="R100" t="n">
-        <v>7134697</v>
+        <v>7134619</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12464,10 +12464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076651</v>
+        <v>120076632</v>
       </c>
       <c r="B112" t="n">
-        <v>90730</v>
+        <v>79623</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12476,25 +12476,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503516</v>
+        <v>503434</v>
       </c>
       <c r="R112" t="n">
-        <v>7134622</v>
+        <v>7134673</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076611</v>
+        <v>120076651</v>
       </c>
       <c r="B113" t="n">
-        <v>79624</v>
+        <v>90730</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12578,25 +12578,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12606,10 +12606,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503691</v>
+        <v>503516</v>
       </c>
       <c r="R113" t="n">
-        <v>7134749</v>
+        <v>7134622</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12668,10 +12668,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076632</v>
+        <v>120076611</v>
       </c>
       <c r="B114" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12684,21 +12684,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12708,10 +12708,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503434</v>
+        <v>503691</v>
       </c>
       <c r="R114" t="n">
-        <v>7134673</v>
+        <v>7134749</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120036022</v>
+        <v>120035622</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5529,21 +5529,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504145</v>
+        <v>504165</v>
       </c>
       <c r="R44" t="n">
-        <v>7134441</v>
+        <v>7134407</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120036399</v>
+        <v>120035015</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504083</v>
+        <v>504196</v>
       </c>
       <c r="R45" t="n">
-        <v>7134453</v>
+        <v>7134350</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,11 +5691,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5722,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120038086</v>
+        <v>120034574</v>
       </c>
       <c r="B46" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5738,21 +5733,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5762,13 +5757,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503980</v>
+        <v>504224</v>
       </c>
       <c r="R46" t="n">
-        <v>7134422</v>
+        <v>7134352</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5824,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120035868</v>
+        <v>120034479</v>
       </c>
       <c r="B47" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5840,21 +5835,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5864,13 +5859,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504193</v>
+        <v>504252</v>
       </c>
       <c r="R47" t="n">
-        <v>7134477</v>
+        <v>7134346</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6028,10 +6023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120035460</v>
+        <v>120036022</v>
       </c>
       <c r="B49" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6044,21 +6039,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6068,13 +6063,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504169</v>
+        <v>504145</v>
       </c>
       <c r="R49" t="n">
-        <v>7134407</v>
+        <v>7134441</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6130,10 +6125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035622</v>
+        <v>120035871</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6146,21 +6141,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,13 +6165,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504165</v>
+        <v>504192</v>
       </c>
       <c r="R50" t="n">
-        <v>7134407</v>
+        <v>7134481</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6232,10 +6227,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120039375</v>
+        <v>120036399</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6248,21 +6243,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6272,13 +6267,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503988</v>
+        <v>504083</v>
       </c>
       <c r="R51" t="n">
-        <v>7134466</v>
+        <v>7134453</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6308,6 +6303,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,10 +6334,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120035291</v>
+        <v>120035542</v>
       </c>
       <c r="B52" t="n">
-        <v>4863</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6346,25 +6346,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101675</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504179</v>
+        <v>504175</v>
       </c>
       <c r="R52" t="n">
-        <v>7134372</v>
+        <v>7134410</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,11 +6410,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6645,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120035542</v>
+        <v>120039375</v>
       </c>
       <c r="B55" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6661,21 +6656,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6685,13 +6680,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504175</v>
+        <v>503988</v>
       </c>
       <c r="R55" t="n">
-        <v>7134410</v>
+        <v>7134466</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,7 +6742,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120034383</v>
+        <v>120035868</v>
       </c>
       <c r="B56" t="n">
         <v>78279</v>
@@ -6787,10 +6782,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504257</v>
+        <v>504193</v>
       </c>
       <c r="R56" t="n">
-        <v>7134334</v>
+        <v>7134477</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6849,10 +6844,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120040383</v>
+        <v>120035291</v>
       </c>
       <c r="B57" t="n">
-        <v>90825</v>
+        <v>4863</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6861,41 +6856,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>101675</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503879</v>
+        <v>504179</v>
       </c>
       <c r="R57" t="n">
-        <v>7134575</v>
+        <v>7134372</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6925,6 +6920,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120035015</v>
+        <v>120035460</v>
       </c>
       <c r="B58" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504196</v>
+        <v>504169</v>
       </c>
       <c r="R58" t="n">
-        <v>7134350</v>
+        <v>7134407</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120034574</v>
+        <v>120040383</v>
       </c>
       <c r="B59" t="n">
-        <v>78278</v>
+        <v>90825</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7065,41 +7065,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504224</v>
+        <v>503879</v>
       </c>
       <c r="R59" t="n">
-        <v>7134352</v>
+        <v>7134575</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120035871</v>
+        <v>120038086</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,21 +7171,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,13 +7195,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504192</v>
+        <v>503980</v>
       </c>
       <c r="R60" t="n">
-        <v>7134481</v>
+        <v>7134422</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120034479</v>
+        <v>120034383</v>
       </c>
       <c r="B61" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504252</v>
+        <v>504257</v>
       </c>
       <c r="R61" t="n">
-        <v>7134346</v>
+        <v>7134334</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120046468</v>
+        <v>120046464</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,25 +7371,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503899</v>
+        <v>503874</v>
       </c>
       <c r="R62" t="n">
-        <v>7134531</v>
+        <v>7134566</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120038261</v>
+        <v>120046468</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -7497,17 +7497,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503997</v>
+        <v>503899</v>
       </c>
       <c r="R63" t="n">
-        <v>7134441</v>
+        <v>7134531</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120046464</v>
+        <v>120038261</v>
       </c>
       <c r="B64" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,41 +7575,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503874</v>
+        <v>503997</v>
       </c>
       <c r="R64" t="n">
-        <v>7134566</v>
+        <v>7134441</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120046465</v>
+        <v>120039963</v>
       </c>
       <c r="B65" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,41 +7677,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504001</v>
+        <v>503904</v>
       </c>
       <c r="R65" t="n">
-        <v>7134466</v>
+        <v>7134523</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120039963</v>
+        <v>120046465</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7779,41 +7779,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503904</v>
+        <v>504001</v>
       </c>
       <c r="R66" t="n">
-        <v>7134523</v>
+        <v>7134466</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076674</v>
+        <v>120076627</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503558</v>
+        <v>503531</v>
       </c>
       <c r="R67" t="n">
-        <v>7134614</v>
+        <v>7134812</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076646</v>
+        <v>120076671</v>
       </c>
       <c r="B68" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,25 +7983,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503675</v>
+        <v>503546</v>
       </c>
       <c r="R68" t="n">
-        <v>7134737</v>
+        <v>7134587</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076664</v>
+        <v>120076670</v>
       </c>
       <c r="B69" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503543</v>
+        <v>503626</v>
       </c>
       <c r="R69" t="n">
-        <v>7134608</v>
+        <v>7134549</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076616</v>
+        <v>120076674</v>
       </c>
       <c r="B70" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503430</v>
+        <v>503558</v>
       </c>
       <c r="R70" t="n">
-        <v>7134700</v>
+        <v>7134614</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076670</v>
+        <v>120076640</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503626</v>
+        <v>503654</v>
       </c>
       <c r="R71" t="n">
-        <v>7134549</v>
+        <v>7134725</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076687</v>
+        <v>120076686</v>
       </c>
       <c r="B72" t="n">
-        <v>91852</v>
+        <v>79658</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503491</v>
+        <v>503428</v>
       </c>
       <c r="R72" t="n">
-        <v>7134636</v>
+        <v>7134677</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076628</v>
+        <v>120076599</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503570</v>
+        <v>503657</v>
       </c>
       <c r="R73" t="n">
-        <v>7134765</v>
+        <v>7134513</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076640</v>
+        <v>120076654</v>
       </c>
       <c r="B74" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8599,21 +8599,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503654</v>
+        <v>503821</v>
       </c>
       <c r="R74" t="n">
-        <v>7134725</v>
+        <v>7134659</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076649</v>
+        <v>120076626</v>
       </c>
       <c r="B75" t="n">
-        <v>90576</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8701,21 +8701,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503835</v>
+        <v>503534</v>
       </c>
       <c r="R75" t="n">
-        <v>7134640</v>
+        <v>7134804</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076650</v>
+        <v>120076623</v>
       </c>
       <c r="B76" t="n">
-        <v>90594</v>
+        <v>78279</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8803,21 +8803,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503633</v>
+        <v>503665</v>
       </c>
       <c r="R76" t="n">
-        <v>7134566</v>
+        <v>7134523</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076671</v>
+        <v>120076616</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503546</v>
+        <v>503430</v>
       </c>
       <c r="R77" t="n">
-        <v>7134587</v>
+        <v>7134700</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,7 +8991,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076675</v>
+        <v>120064794</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -9027,17 +9027,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503542</v>
+        <v>503729</v>
       </c>
       <c r="R78" t="n">
-        <v>7134610</v>
+        <v>7134606</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076627</v>
+        <v>120076628</v>
       </c>
       <c r="B79" t="n">
         <v>79623</v>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503531</v>
+        <v>503570</v>
       </c>
       <c r="R79" t="n">
-        <v>7134812</v>
+        <v>7134765</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076665</v>
+        <v>120076641</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9211,21 +9211,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503480</v>
+        <v>503745</v>
       </c>
       <c r="R80" t="n">
-        <v>7134647</v>
+        <v>7134697</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,7 +9297,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076614</v>
+        <v>120076612</v>
       </c>
       <c r="B81" t="n">
         <v>79624</v>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503427</v>
+        <v>503818</v>
       </c>
       <c r="R81" t="n">
-        <v>7134675</v>
+        <v>7134671</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076605</v>
+        <v>120076685</v>
       </c>
       <c r="B82" t="n">
-        <v>79652</v>
+        <v>79658</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9415,21 +9415,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503568</v>
+        <v>503819</v>
       </c>
       <c r="R82" t="n">
-        <v>7134774</v>
+        <v>7134668</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,7 +9501,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076633</v>
+        <v>120076630</v>
       </c>
       <c r="B83" t="n">
         <v>79623</v>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503430</v>
+        <v>503592</v>
       </c>
       <c r="R83" t="n">
-        <v>7134677</v>
+        <v>7134781</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076673</v>
+        <v>120076648</v>
       </c>
       <c r="B84" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9615,25 +9615,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503532</v>
+        <v>503495</v>
       </c>
       <c r="R84" t="n">
-        <v>7134595</v>
+        <v>7134638</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076661</v>
+        <v>120076615</v>
       </c>
       <c r="B85" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9721,21 +9721,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503604</v>
+        <v>503430</v>
       </c>
       <c r="R85" t="n">
-        <v>7134590</v>
+        <v>7134677</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076613</v>
+        <v>120076635</v>
       </c>
       <c r="B86" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9823,21 +9823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503646</v>
+        <v>503426</v>
       </c>
       <c r="R86" t="n">
-        <v>7134570</v>
+        <v>7134704</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9909,7 +9909,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120060142</v>
+        <v>120076673</v>
       </c>
       <c r="B87" t="n">
         <v>91858</v>
@@ -9945,17 +9945,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503497</v>
+        <v>503532</v>
       </c>
       <c r="R87" t="n">
-        <v>7134657</v>
+        <v>7134595</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076686</v>
+        <v>120076618</v>
       </c>
       <c r="B88" t="n">
-        <v>79658</v>
+        <v>96891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503428</v>
+        <v>503850</v>
       </c>
       <c r="R88" t="n">
-        <v>7134677</v>
+        <v>7134617</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076639</v>
+        <v>120076664</v>
       </c>
       <c r="B89" t="n">
-        <v>79659</v>
+        <v>78187</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10125,25 +10125,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503430</v>
+        <v>503543</v>
       </c>
       <c r="R89" t="n">
-        <v>7134677</v>
+        <v>7134608</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076606</v>
+        <v>120076611</v>
       </c>
       <c r="B90" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10227,25 +10227,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503427</v>
+        <v>503691</v>
       </c>
       <c r="R90" t="n">
-        <v>7134680</v>
+        <v>7134749</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076626</v>
+        <v>120076638</v>
       </c>
       <c r="B91" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10329,25 +10329,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503534</v>
+        <v>503819</v>
       </c>
       <c r="R91" t="n">
-        <v>7134804</v>
+        <v>7134668</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10419,10 +10419,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076600</v>
+        <v>120076633</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10459,10 +10459,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503603</v>
+        <v>503430</v>
       </c>
       <c r="R92" t="n">
-        <v>7134592</v>
+        <v>7134677</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10521,10 +10521,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076618</v>
+        <v>120076649</v>
       </c>
       <c r="B93" t="n">
-        <v>96891</v>
+        <v>90576</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10533,25 +10533,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10561,10 +10561,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503850</v>
+        <v>503835</v>
       </c>
       <c r="R93" t="n">
-        <v>7134617</v>
+        <v>7134640</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076620</v>
+        <v>120076632</v>
       </c>
       <c r="B94" t="n">
-        <v>92048</v>
+        <v>79623</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10639,21 +10639,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10663,10 +10663,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503618</v>
+        <v>503434</v>
       </c>
       <c r="R94" t="n">
-        <v>7134495</v>
+        <v>7134673</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10725,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076629</v>
+        <v>120065097</v>
       </c>
       <c r="B95" t="n">
-        <v>79623</v>
+        <v>91904</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,41 +10737,44 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503568</v>
+        <v>503748</v>
       </c>
       <c r="R95" t="n">
-        <v>7134773</v>
+        <v>7134611</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10803,12 +10806,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10827,7 +10836,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076636</v>
+        <v>120076639</v>
       </c>
       <c r="B96" t="n">
         <v>79659</v>
@@ -10867,10 +10876,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503530</v>
+        <v>503430</v>
       </c>
       <c r="R96" t="n">
-        <v>7134813</v>
+        <v>7134677</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10938,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076630</v>
+        <v>120076620</v>
       </c>
       <c r="B97" t="n">
-        <v>79623</v>
+        <v>92048</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10945,21 +10954,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10978,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503592</v>
+        <v>503618</v>
       </c>
       <c r="R97" t="n">
-        <v>7134781</v>
+        <v>7134495</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11031,10 +11040,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076637</v>
+        <v>120076606</v>
       </c>
       <c r="B98" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11047,21 +11056,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11071,10 +11080,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503530</v>
+        <v>503427</v>
       </c>
       <c r="R98" t="n">
-        <v>7134806</v>
+        <v>7134680</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11133,10 +11142,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076641</v>
+        <v>120076647</v>
       </c>
       <c r="B99" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11145,25 +11154,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11173,10 +11182,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503745</v>
+        <v>503790</v>
       </c>
       <c r="R99" t="n">
-        <v>7134697</v>
+        <v>7134698</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11235,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076676</v>
+        <v>120076629</v>
       </c>
       <c r="B100" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11247,25 +11256,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11275,10 +11284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503536</v>
+        <v>503568</v>
       </c>
       <c r="R100" t="n">
-        <v>7134619</v>
+        <v>7134773</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11337,10 +11346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076645</v>
+        <v>120076605</v>
       </c>
       <c r="B101" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11349,25 +11358,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11377,10 +11386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503601</v>
+        <v>503568</v>
       </c>
       <c r="R101" t="n">
-        <v>7134773</v>
+        <v>7134774</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11439,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076610</v>
+        <v>120076644</v>
       </c>
       <c r="B102" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11455,21 +11464,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11479,10 +11488,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503592</v>
+        <v>503748</v>
       </c>
       <c r="R102" t="n">
-        <v>7134781</v>
+        <v>7134611</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11541,10 +11550,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076681</v>
+        <v>120076609</v>
       </c>
       <c r="B103" t="n">
-        <v>12337</v>
+        <v>79624</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11553,25 +11562,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>101283</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11581,10 +11590,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503867</v>
+        <v>503567</v>
       </c>
       <c r="R103" t="n">
-        <v>7134650</v>
+        <v>7134773</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11617,11 +11626,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11648,10 +11652,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076619</v>
+        <v>120076652</v>
       </c>
       <c r="B104" t="n">
-        <v>91850</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11664,21 +11668,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11688,10 +11692,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503460</v>
+        <v>503526</v>
       </c>
       <c r="R104" t="n">
-        <v>7134749</v>
+        <v>7134815</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11750,10 +11754,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076602</v>
+        <v>120076681</v>
       </c>
       <c r="B105" t="n">
-        <v>89650</v>
+        <v>12337</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11762,25 +11766,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1962</v>
+        <v>101283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11790,10 +11794,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503489</v>
+        <v>503867</v>
       </c>
       <c r="R105" t="n">
-        <v>7134637</v>
+        <v>7134650</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11826,6 +11830,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11852,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076684</v>
+        <v>120060142</v>
       </c>
       <c r="B106" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11868,37 +11877,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503568</v>
+        <v>503497</v>
       </c>
       <c r="R106" t="n">
-        <v>7134774</v>
+        <v>7134657</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11954,10 +11963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076635</v>
+        <v>120076645</v>
       </c>
       <c r="B107" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11966,25 +11975,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +12003,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503426</v>
+        <v>503601</v>
       </c>
       <c r="R107" t="n">
-        <v>7134704</v>
+        <v>7134773</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12056,10 +12065,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076634</v>
+        <v>120076661</v>
       </c>
       <c r="B108" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12072,21 +12081,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12096,10 +12105,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503432</v>
+        <v>503604</v>
       </c>
       <c r="R108" t="n">
-        <v>7134696</v>
+        <v>7134590</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12158,10 +12167,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120064794</v>
+        <v>120076684</v>
       </c>
       <c r="B109" t="n">
-        <v>91858</v>
+        <v>79658</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12174,37 +12183,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503729</v>
+        <v>503568</v>
       </c>
       <c r="R109" t="n">
-        <v>7134606</v>
+        <v>7134774</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12260,10 +12269,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076599</v>
+        <v>120076636</v>
       </c>
       <c r="B110" t="n">
-        <v>90545</v>
+        <v>79659</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12276,21 +12285,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12300,10 +12309,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503657</v>
+        <v>503530</v>
       </c>
       <c r="R110" t="n">
-        <v>7134513</v>
+        <v>7134813</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12362,10 +12371,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076654</v>
+        <v>120076675</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12374,25 +12383,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12402,10 +12411,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503821</v>
+        <v>503542</v>
       </c>
       <c r="R111" t="n">
-        <v>7134659</v>
+        <v>7134610</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12464,10 +12473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076632</v>
+        <v>120076677</v>
       </c>
       <c r="B112" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12476,25 +12485,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12504,10 +12513,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503434</v>
+        <v>503481</v>
       </c>
       <c r="R112" t="n">
-        <v>7134673</v>
+        <v>7134655</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12566,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076651</v>
+        <v>120076601</v>
       </c>
       <c r="B113" t="n">
-        <v>90730</v>
+        <v>79131</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12578,25 +12587,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12606,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503516</v>
+        <v>503546</v>
       </c>
       <c r="R113" t="n">
-        <v>7134622</v>
+        <v>7134565</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12668,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076611</v>
+        <v>120076637</v>
       </c>
       <c r="B114" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12680,25 +12689,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12708,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503691</v>
+        <v>503530</v>
       </c>
       <c r="R114" t="n">
-        <v>7134749</v>
+        <v>7134806</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12770,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076644</v>
+        <v>120076624</v>
       </c>
       <c r="B115" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12786,21 +12795,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12810,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503748</v>
+        <v>503630</v>
       </c>
       <c r="R115" t="n">
-        <v>7134611</v>
+        <v>7134529</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12872,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076624</v>
+        <v>120076672</v>
       </c>
       <c r="B116" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12884,25 +12893,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12912,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503630</v>
+        <v>503543</v>
       </c>
       <c r="R116" t="n">
-        <v>7134529</v>
+        <v>7134573</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12974,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076615</v>
+        <v>120076602</v>
       </c>
       <c r="B117" t="n">
-        <v>79624</v>
+        <v>89650</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12990,21 +12999,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13014,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503430</v>
+        <v>503489</v>
       </c>
       <c r="R117" t="n">
-        <v>7134677</v>
+        <v>7134637</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13076,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076638</v>
+        <v>120076634</v>
       </c>
       <c r="B118" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13088,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13116,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503819</v>
+        <v>503432</v>
       </c>
       <c r="R118" t="n">
-        <v>7134668</v>
+        <v>7134696</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13178,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076631</v>
+        <v>120076600</v>
       </c>
       <c r="B119" t="n">
-        <v>79623</v>
+        <v>79131</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13194,21 +13203,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13218,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503624</v>
+        <v>503603</v>
       </c>
       <c r="R119" t="n">
-        <v>7134757</v>
+        <v>7134592</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13280,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076672</v>
+        <v>120076646</v>
       </c>
       <c r="B120" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13292,25 +13301,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13320,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503543</v>
+        <v>503675</v>
       </c>
       <c r="R120" t="n">
-        <v>7134573</v>
+        <v>7134737</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13382,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076647</v>
+        <v>120076625</v>
       </c>
       <c r="B121" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13394,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13422,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503790</v>
+        <v>503539</v>
       </c>
       <c r="R121" t="n">
-        <v>7134698</v>
+        <v>7134558</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13484,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076601</v>
+        <v>120076650</v>
       </c>
       <c r="B122" t="n">
-        <v>79131</v>
+        <v>90594</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13500,21 +13509,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13524,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503546</v>
+        <v>503633</v>
       </c>
       <c r="R122" t="n">
-        <v>7134565</v>
+        <v>7134566</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13586,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076677</v>
+        <v>120076665</v>
       </c>
       <c r="B123" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13598,25 +13607,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13626,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503481</v>
+        <v>503480</v>
       </c>
       <c r="R123" t="n">
-        <v>7134655</v>
+        <v>7134647</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13688,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076617</v>
+        <v>120076651</v>
       </c>
       <c r="B124" t="n">
-        <v>96891</v>
+        <v>90730</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13700,25 +13709,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13728,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503847</v>
+        <v>503516</v>
       </c>
       <c r="R124" t="n">
-        <v>7134693</v>
+        <v>7134622</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13790,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076662</v>
+        <v>120076610</v>
       </c>
       <c r="B125" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13806,21 +13815,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13830,10 +13839,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503535</v>
+        <v>503592</v>
       </c>
       <c r="R125" t="n">
-        <v>7134599</v>
+        <v>7134781</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13892,7 +13901,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076609</v>
+        <v>120076614</v>
       </c>
       <c r="B126" t="n">
         <v>79624</v>
@@ -13932,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503567</v>
+        <v>503427</v>
       </c>
       <c r="R126" t="n">
-        <v>7134773</v>
+        <v>7134675</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13994,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076612</v>
+        <v>120076653</v>
       </c>
       <c r="B127" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14010,21 +14019,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14034,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503818</v>
+        <v>503608</v>
       </c>
       <c r="R127" t="n">
-        <v>7134671</v>
+        <v>7134763</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14096,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076652</v>
+        <v>120076608</v>
       </c>
       <c r="B128" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14112,21 +14121,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14136,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503526</v>
+        <v>503530</v>
       </c>
       <c r="R128" t="n">
-        <v>7134815</v>
+        <v>7134813</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14198,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076685</v>
+        <v>120076676</v>
       </c>
       <c r="B129" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14214,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14238,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503819</v>
+        <v>503536</v>
       </c>
       <c r="R129" t="n">
-        <v>7134668</v>
+        <v>7134619</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14300,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076625</v>
+        <v>120076619</v>
       </c>
       <c r="B130" t="n">
-        <v>78279</v>
+        <v>91850</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14316,21 +14325,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14340,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503539</v>
+        <v>503460</v>
       </c>
       <c r="R130" t="n">
-        <v>7134558</v>
+        <v>7134749</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14402,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076608</v>
+        <v>120076643</v>
       </c>
       <c r="B131" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14418,21 +14427,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14442,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503530</v>
+        <v>503820</v>
       </c>
       <c r="R131" t="n">
-        <v>7134813</v>
+        <v>7134705</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14504,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076643</v>
+        <v>120076617</v>
       </c>
       <c r="B132" t="n">
-        <v>78278</v>
+        <v>96891</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14516,25 +14525,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14544,10 +14553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503820</v>
+        <v>503847</v>
       </c>
       <c r="R132" t="n">
-        <v>7134705</v>
+        <v>7134693</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14606,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076648</v>
+        <v>120076660</v>
       </c>
       <c r="B133" t="n">
-        <v>89247</v>
+        <v>78187</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14618,25 +14627,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1596</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14646,10 +14655,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503495</v>
+        <v>503616</v>
       </c>
       <c r="R133" t="n">
-        <v>7134638</v>
+        <v>7134591</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14708,10 +14717,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076660</v>
+        <v>120076613</v>
       </c>
       <c r="B134" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14724,21 +14733,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14748,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503616</v>
+        <v>503646</v>
       </c>
       <c r="R134" t="n">
-        <v>7134591</v>
+        <v>7134570</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14810,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076653</v>
+        <v>120076631</v>
       </c>
       <c r="B135" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14826,21 +14835,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14850,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503608</v>
+        <v>503624</v>
       </c>
       <c r="R135" t="n">
-        <v>7134763</v>
+        <v>7134757</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14912,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120065097</v>
+        <v>120076687</v>
       </c>
       <c r="B136" t="n">
-        <v>91904</v>
+        <v>91852</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14924,44 +14933,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>232140</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503748</v>
+        <v>503491</v>
       </c>
       <c r="R136" t="n">
-        <v>7134611</v>
+        <v>7134636</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14993,18 +14999,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076623</v>
+        <v>120076662</v>
       </c>
       <c r="B137" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15039,21 +15039,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503665</v>
+        <v>503535</v>
       </c>
       <c r="R137" t="n">
-        <v>7134523</v>
+        <v>7134599</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120035622</v>
+        <v>120039375</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5529,21 +5529,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504165</v>
+        <v>503988</v>
       </c>
       <c r="R44" t="n">
-        <v>7134407</v>
+        <v>7134466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120035015</v>
+        <v>120040383</v>
       </c>
       <c r="B45" t="n">
-        <v>78278</v>
+        <v>90825</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5627,41 +5627,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504196</v>
+        <v>503879</v>
       </c>
       <c r="R45" t="n">
-        <v>7134350</v>
+        <v>7134575</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5717,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120034574</v>
+        <v>120035460</v>
       </c>
       <c r="B46" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5733,21 +5733,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504224</v>
+        <v>504169</v>
       </c>
       <c r="R46" t="n">
-        <v>7134352</v>
+        <v>7134407</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120034479</v>
+        <v>120036399</v>
       </c>
       <c r="B47" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504252</v>
+        <v>504083</v>
       </c>
       <c r="R47" t="n">
-        <v>7134346</v>
+        <v>7134453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5895,6 +5895,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5921,10 +5926,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035474</v>
+        <v>120035291</v>
       </c>
       <c r="B48" t="n">
-        <v>79652</v>
+        <v>4863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5937,21 +5942,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>101675</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,13 +5966,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504166</v>
+        <v>504179</v>
       </c>
       <c r="R48" t="n">
-        <v>7134391</v>
+        <v>7134372</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5997,6 +6002,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6023,10 +6033,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120036022</v>
+        <v>120034574</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6039,21 +6049,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6063,13 +6073,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504145</v>
+        <v>504224</v>
       </c>
       <c r="R49" t="n">
-        <v>7134441</v>
+        <v>7134352</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6125,10 +6135,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035871</v>
+        <v>120034826</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>91862</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6137,25 +6147,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6165,10 +6175,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504192</v>
+        <v>504226</v>
       </c>
       <c r="R50" t="n">
-        <v>7134481</v>
+        <v>7134339</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6227,10 +6237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120036399</v>
+        <v>120035868</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6243,21 +6253,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6267,13 +6277,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504083</v>
+        <v>504193</v>
       </c>
       <c r="R51" t="n">
-        <v>7134453</v>
+        <v>7134477</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6303,11 +6313,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6436,10 +6441,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120034826</v>
+        <v>120035474</v>
       </c>
       <c r="B53" t="n">
-        <v>91862</v>
+        <v>79652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6448,25 +6453,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6476,10 +6481,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504226</v>
+        <v>504166</v>
       </c>
       <c r="R53" t="n">
-        <v>7134339</v>
+        <v>7134391</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6538,10 +6543,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120035768</v>
+        <v>120035015</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6554,21 +6559,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6578,10 +6583,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504187</v>
+        <v>504196</v>
       </c>
       <c r="R54" t="n">
-        <v>7134438</v>
+        <v>7134350</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6640,10 +6645,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120039375</v>
+        <v>120038086</v>
       </c>
       <c r="B55" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6656,21 +6661,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6680,13 +6685,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503988</v>
+        <v>503980</v>
       </c>
       <c r="R55" t="n">
-        <v>7134466</v>
+        <v>7134422</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6742,10 +6747,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120035868</v>
+        <v>120034479</v>
       </c>
       <c r="B56" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6758,21 +6763,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6782,13 +6787,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504193</v>
+        <v>504252</v>
       </c>
       <c r="R56" t="n">
-        <v>7134477</v>
+        <v>7134346</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6844,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035291</v>
+        <v>120034383</v>
       </c>
       <c r="B57" t="n">
-        <v>4863</v>
+        <v>78279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6856,25 +6861,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101675</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504179</v>
+        <v>504257</v>
       </c>
       <c r="R57" t="n">
-        <v>7134372</v>
+        <v>7134334</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6920,11 +6925,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120035460</v>
+        <v>120035622</v>
       </c>
       <c r="B58" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504169</v>
+        <v>504165</v>
       </c>
       <c r="R58" t="n">
         <v>7134407</v>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120040383</v>
+        <v>120035768</v>
       </c>
       <c r="B59" t="n">
-        <v>90825</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7065,41 +7065,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503879</v>
+        <v>504187</v>
       </c>
       <c r="R59" t="n">
-        <v>7134575</v>
+        <v>7134438</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120038086</v>
+        <v>120036022</v>
       </c>
       <c r="B60" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,21 +7171,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,13 +7195,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503980</v>
+        <v>504145</v>
       </c>
       <c r="R60" t="n">
-        <v>7134422</v>
+        <v>7134441</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120034383</v>
+        <v>120035871</v>
       </c>
       <c r="B61" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504257</v>
+        <v>504192</v>
       </c>
       <c r="R61" t="n">
-        <v>7134334</v>
+        <v>7134481</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120046464</v>
+        <v>120039963</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,41 +7371,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503874</v>
+        <v>503904</v>
       </c>
       <c r="R62" t="n">
-        <v>7134566</v>
+        <v>7134523</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120039963</v>
+        <v>120046465</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,41 +7677,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503904</v>
+        <v>504001</v>
       </c>
       <c r="R65" t="n">
-        <v>7134523</v>
+        <v>7134466</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120046465</v>
+        <v>120046464</v>
       </c>
       <c r="B66" t="n">
         <v>78278</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504001</v>
+        <v>503874</v>
       </c>
       <c r="R66" t="n">
-        <v>7134466</v>
+        <v>7134566</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076627</v>
+        <v>120076650</v>
       </c>
       <c r="B67" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7885,21 +7885,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503531</v>
+        <v>503633</v>
       </c>
       <c r="R67" t="n">
-        <v>7134812</v>
+        <v>7134566</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076671</v>
+        <v>120076618</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503546</v>
+        <v>503850</v>
       </c>
       <c r="R68" t="n">
-        <v>7134587</v>
+        <v>7134617</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076670</v>
+        <v>120076635</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503626</v>
+        <v>503426</v>
       </c>
       <c r="R69" t="n">
-        <v>7134549</v>
+        <v>7134704</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076674</v>
+        <v>120076633</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503558</v>
+        <v>503430</v>
       </c>
       <c r="R70" t="n">
-        <v>7134614</v>
+        <v>7134677</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076640</v>
+        <v>120076647</v>
       </c>
       <c r="B71" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503654</v>
+        <v>503790</v>
       </c>
       <c r="R71" t="n">
-        <v>7134725</v>
+        <v>7134698</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076686</v>
+        <v>120076662</v>
       </c>
       <c r="B72" t="n">
-        <v>79658</v>
+        <v>78187</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503428</v>
+        <v>503535</v>
       </c>
       <c r="R72" t="n">
-        <v>7134677</v>
+        <v>7134599</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076599</v>
+        <v>120076673</v>
       </c>
       <c r="B73" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8497,21 +8497,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503657</v>
+        <v>503532</v>
       </c>
       <c r="R73" t="n">
-        <v>7134513</v>
+        <v>7134595</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076654</v>
+        <v>120076606</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503821</v>
+        <v>503427</v>
       </c>
       <c r="R74" t="n">
-        <v>7134659</v>
+        <v>7134680</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,7 +8685,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076626</v>
+        <v>120076631</v>
       </c>
       <c r="B75" t="n">
         <v>79623</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503534</v>
+        <v>503624</v>
       </c>
       <c r="R75" t="n">
-        <v>7134804</v>
+        <v>7134757</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076623</v>
+        <v>120076671</v>
       </c>
       <c r="B76" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503665</v>
+        <v>503546</v>
       </c>
       <c r="R76" t="n">
-        <v>7134523</v>
+        <v>7134587</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076616</v>
+        <v>120076645</v>
       </c>
       <c r="B77" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503430</v>
+        <v>503601</v>
       </c>
       <c r="R77" t="n">
-        <v>7134700</v>
+        <v>7134773</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120064794</v>
+        <v>120076629</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9003,41 +9003,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503729</v>
+        <v>503568</v>
       </c>
       <c r="R78" t="n">
-        <v>7134606</v>
+        <v>7134773</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076628</v>
+        <v>120076646</v>
       </c>
       <c r="B79" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9105,25 +9105,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503570</v>
+        <v>503675</v>
       </c>
       <c r="R79" t="n">
-        <v>7134765</v>
+        <v>7134737</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076641</v>
+        <v>120076615</v>
       </c>
       <c r="B80" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9211,21 +9211,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503745</v>
+        <v>503430</v>
       </c>
       <c r="R80" t="n">
-        <v>7134697</v>
+        <v>7134677</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076612</v>
+        <v>120076648</v>
       </c>
       <c r="B81" t="n">
-        <v>79624</v>
+        <v>89247</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9309,25 +9309,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>1596</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503818</v>
+        <v>503495</v>
       </c>
       <c r="R81" t="n">
-        <v>7134671</v>
+        <v>7134638</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076685</v>
+        <v>120076612</v>
       </c>
       <c r="B82" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9411,25 +9411,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503819</v>
+        <v>503818</v>
       </c>
       <c r="R82" t="n">
-        <v>7134668</v>
+        <v>7134671</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076630</v>
+        <v>120076641</v>
       </c>
       <c r="B83" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9517,21 +9517,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503592</v>
+        <v>503745</v>
       </c>
       <c r="R83" t="n">
-        <v>7134781</v>
+        <v>7134697</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076648</v>
+        <v>120076627</v>
       </c>
       <c r="B84" t="n">
-        <v>89247</v>
+        <v>79623</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9615,25 +9615,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1596</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503495</v>
+        <v>503531</v>
       </c>
       <c r="R84" t="n">
-        <v>7134638</v>
+        <v>7134812</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076615</v>
+        <v>120076643</v>
       </c>
       <c r="B85" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9721,21 +9721,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503430</v>
+        <v>503820</v>
       </c>
       <c r="R85" t="n">
-        <v>7134677</v>
+        <v>7134705</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076635</v>
+        <v>120076665</v>
       </c>
       <c r="B86" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9823,21 +9823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503426</v>
+        <v>503480</v>
       </c>
       <c r="R86" t="n">
-        <v>7134704</v>
+        <v>7134647</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9909,7 +9909,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076673</v>
+        <v>120076670</v>
       </c>
       <c r="B87" t="n">
         <v>91858</v>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503532</v>
+        <v>503626</v>
       </c>
       <c r="R87" t="n">
-        <v>7134595</v>
+        <v>7134549</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076618</v>
+        <v>120076616</v>
       </c>
       <c r="B88" t="n">
-        <v>96891</v>
+        <v>79624</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10023,25 +10023,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503850</v>
+        <v>503430</v>
       </c>
       <c r="R88" t="n">
-        <v>7134617</v>
+        <v>7134700</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076664</v>
+        <v>120076611</v>
       </c>
       <c r="B89" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503543</v>
+        <v>503691</v>
       </c>
       <c r="R89" t="n">
-        <v>7134608</v>
+        <v>7134749</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076611</v>
+        <v>120076625</v>
       </c>
       <c r="B90" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503691</v>
+        <v>503539</v>
       </c>
       <c r="R90" t="n">
-        <v>7134749</v>
+        <v>7134558</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076638</v>
+        <v>120076624</v>
       </c>
       <c r="B91" t="n">
-        <v>79659</v>
+        <v>78279</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10329,25 +10329,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503819</v>
+        <v>503630</v>
       </c>
       <c r="R91" t="n">
-        <v>7134668</v>
+        <v>7134529</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10419,10 +10419,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076633</v>
+        <v>120076654</v>
       </c>
       <c r="B92" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10459,10 +10459,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503430</v>
+        <v>503821</v>
       </c>
       <c r="R92" t="n">
-        <v>7134677</v>
+        <v>7134659</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10521,10 +10521,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076649</v>
+        <v>120065097</v>
       </c>
       <c r="B93" t="n">
-        <v>90576</v>
+        <v>91904</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10533,41 +10533,44 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>232140</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503835</v>
+        <v>503748</v>
       </c>
       <c r="R93" t="n">
-        <v>7134640</v>
+        <v>7134611</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10599,12 +10602,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10623,10 +10632,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076632</v>
+        <v>120076620</v>
       </c>
       <c r="B94" t="n">
-        <v>79623</v>
+        <v>92048</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10639,21 +10648,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10663,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503434</v>
+        <v>503618</v>
       </c>
       <c r="R94" t="n">
-        <v>7134673</v>
+        <v>7134495</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10725,10 +10734,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120065097</v>
+        <v>120076608</v>
       </c>
       <c r="B95" t="n">
-        <v>91904</v>
+        <v>79624</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,44 +10746,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>232140</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503748</v>
+        <v>503530</v>
       </c>
       <c r="R95" t="n">
-        <v>7134611</v>
+        <v>7134813</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10806,18 +10812,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10836,10 +10836,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076639</v>
+        <v>120076602</v>
       </c>
       <c r="B96" t="n">
-        <v>79659</v>
+        <v>89650</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10848,25 +10848,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503430</v>
+        <v>503489</v>
       </c>
       <c r="R96" t="n">
-        <v>7134677</v>
+        <v>7134637</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076620</v>
+        <v>120076675</v>
       </c>
       <c r="B97" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10950,25 +10950,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503618</v>
+        <v>503542</v>
       </c>
       <c r="R97" t="n">
-        <v>7134495</v>
+        <v>7134610</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11040,10 +11040,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076606</v>
+        <v>120064794</v>
       </c>
       <c r="B98" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11056,37 +11056,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503427</v>
+        <v>503729</v>
       </c>
       <c r="R98" t="n">
-        <v>7134680</v>
+        <v>7134606</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11142,10 +11142,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076647</v>
+        <v>120076619</v>
       </c>
       <c r="B99" t="n">
-        <v>97930</v>
+        <v>91850</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11154,25 +11154,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11182,10 +11182,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503790</v>
+        <v>503460</v>
       </c>
       <c r="R99" t="n">
-        <v>7134698</v>
+        <v>7134749</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076629</v>
+        <v>120076652</v>
       </c>
       <c r="B100" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11260,21 +11260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503568</v>
+        <v>503526</v>
       </c>
       <c r="R100" t="n">
-        <v>7134773</v>
+        <v>7134815</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11346,10 +11346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076605</v>
+        <v>120076681</v>
       </c>
       <c r="B101" t="n">
-        <v>79652</v>
+        <v>12337</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11358,25 +11358,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>101283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503568</v>
+        <v>503867</v>
       </c>
       <c r="R101" t="n">
-        <v>7134774</v>
+        <v>7134650</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11422,6 +11422,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11453,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076644</v>
+        <v>120076599</v>
       </c>
       <c r="B102" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11460,25 +11465,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11488,10 +11493,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503748</v>
+        <v>503657</v>
       </c>
       <c r="R102" t="n">
-        <v>7134611</v>
+        <v>7134513</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11652,10 +11657,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076652</v>
+        <v>120076626</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11668,21 +11673,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11692,10 +11697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503526</v>
+        <v>503534</v>
       </c>
       <c r="R104" t="n">
-        <v>7134815</v>
+        <v>7134804</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11754,10 +11759,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076681</v>
+        <v>120076640</v>
       </c>
       <c r="B105" t="n">
-        <v>12337</v>
+        <v>78278</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11766,25 +11771,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>101283</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11794,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503867</v>
+        <v>503654</v>
       </c>
       <c r="R105" t="n">
-        <v>7134650</v>
+        <v>7134725</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11830,11 +11835,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11861,10 +11861,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120060142</v>
+        <v>120076639</v>
       </c>
       <c r="B106" t="n">
-        <v>91858</v>
+        <v>79659</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11877,37 +11877,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503497</v>
+        <v>503430</v>
       </c>
       <c r="R106" t="n">
-        <v>7134657</v>
+        <v>7134677</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11963,10 +11963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076645</v>
+        <v>120076600</v>
       </c>
       <c r="B107" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11975,25 +11975,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503601</v>
+        <v>503603</v>
       </c>
       <c r="R107" t="n">
-        <v>7134773</v>
+        <v>7134592</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076661</v>
+        <v>120076610</v>
       </c>
       <c r="B108" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12081,21 +12081,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12105,10 +12105,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503604</v>
+        <v>503592</v>
       </c>
       <c r="R108" t="n">
-        <v>7134590</v>
+        <v>7134781</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12269,7 +12269,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076636</v>
+        <v>120076638</v>
       </c>
       <c r="B110" t="n">
         <v>79659</v>
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503530</v>
+        <v>503819</v>
       </c>
       <c r="R110" t="n">
-        <v>7134813</v>
+        <v>7134668</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12371,10 +12371,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076675</v>
+        <v>120076601</v>
       </c>
       <c r="B111" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12383,25 +12383,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503542</v>
+        <v>503546</v>
       </c>
       <c r="R111" t="n">
-        <v>7134610</v>
+        <v>7134565</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12473,10 +12473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076677</v>
+        <v>120076636</v>
       </c>
       <c r="B112" t="n">
-        <v>91858</v>
+        <v>79659</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12489,21 +12489,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503481</v>
+        <v>503530</v>
       </c>
       <c r="R112" t="n">
-        <v>7134655</v>
+        <v>7134813</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076601</v>
+        <v>120076617</v>
       </c>
       <c r="B113" t="n">
-        <v>79131</v>
+        <v>96891</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12587,25 +12587,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503546</v>
+        <v>503847</v>
       </c>
       <c r="R113" t="n">
-        <v>7134565</v>
+        <v>7134693</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076637</v>
+        <v>120076661</v>
       </c>
       <c r="B114" t="n">
-        <v>79659</v>
+        <v>78187</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12689,25 +12689,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503530</v>
+        <v>503604</v>
       </c>
       <c r="R114" t="n">
-        <v>7134806</v>
+        <v>7134590</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076624</v>
+        <v>120076628</v>
       </c>
       <c r="B115" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12795,21 +12795,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503630</v>
+        <v>503570</v>
       </c>
       <c r="R115" t="n">
-        <v>7134529</v>
+        <v>7134765</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076672</v>
+        <v>120076634</v>
       </c>
       <c r="B116" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12893,25 +12893,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503543</v>
+        <v>503432</v>
       </c>
       <c r="R116" t="n">
-        <v>7134573</v>
+        <v>7134696</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076602</v>
+        <v>120076687</v>
       </c>
       <c r="B117" t="n">
-        <v>89650</v>
+        <v>91852</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12999,21 +12999,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503489</v>
+        <v>503491</v>
       </c>
       <c r="R117" t="n">
-        <v>7134637</v>
+        <v>7134636</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076634</v>
+        <v>120076686</v>
       </c>
       <c r="B118" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13097,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503432</v>
+        <v>503428</v>
       </c>
       <c r="R118" t="n">
-        <v>7134696</v>
+        <v>7134677</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076600</v>
+        <v>120076651</v>
       </c>
       <c r="B119" t="n">
-        <v>79131</v>
+        <v>90730</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13199,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503603</v>
+        <v>503516</v>
       </c>
       <c r="R119" t="n">
-        <v>7134592</v>
+        <v>7134622</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13289,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076646</v>
+        <v>120076677</v>
       </c>
       <c r="B120" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13301,25 +13301,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503675</v>
+        <v>503481</v>
       </c>
       <c r="R120" t="n">
-        <v>7134737</v>
+        <v>7134655</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076625</v>
+        <v>120076605</v>
       </c>
       <c r="B121" t="n">
-        <v>78279</v>
+        <v>79652</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13403,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503539</v>
+        <v>503568</v>
       </c>
       <c r="R121" t="n">
-        <v>7134558</v>
+        <v>7134774</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076650</v>
+        <v>120076637</v>
       </c>
       <c r="B122" t="n">
-        <v>90594</v>
+        <v>79659</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503633</v>
+        <v>503530</v>
       </c>
       <c r="R122" t="n">
-        <v>7134566</v>
+        <v>7134806</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,7 +13595,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076665</v>
+        <v>120076664</v>
       </c>
       <c r="B123" t="n">
         <v>78187</v>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503480</v>
+        <v>503543</v>
       </c>
       <c r="R123" t="n">
-        <v>7134647</v>
+        <v>7134608</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076651</v>
+        <v>120076674</v>
       </c>
       <c r="B124" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13709,25 +13709,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503516</v>
+        <v>503558</v>
       </c>
       <c r="R124" t="n">
-        <v>7134622</v>
+        <v>7134614</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076610</v>
+        <v>120060142</v>
       </c>
       <c r="B125" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,41 +13811,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503592</v>
+        <v>503497</v>
       </c>
       <c r="R125" t="n">
-        <v>7134781</v>
+        <v>7134657</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076614</v>
+        <v>120076660</v>
       </c>
       <c r="B126" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503427</v>
+        <v>503616</v>
       </c>
       <c r="R126" t="n">
-        <v>7134675</v>
+        <v>7134591</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076653</v>
+        <v>120076649</v>
       </c>
       <c r="B127" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14019,21 +14019,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503608</v>
+        <v>503835</v>
       </c>
       <c r="R127" t="n">
-        <v>7134763</v>
+        <v>7134640</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076608</v>
+        <v>120076623</v>
       </c>
       <c r="B128" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503530</v>
+        <v>503665</v>
       </c>
       <c r="R128" t="n">
-        <v>7134813</v>
+        <v>7134523</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076619</v>
+        <v>120076614</v>
       </c>
       <c r="B130" t="n">
-        <v>91850</v>
+        <v>79624</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14325,21 +14325,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4361</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503460</v>
+        <v>503427</v>
       </c>
       <c r="R130" t="n">
-        <v>7134749</v>
+        <v>7134675</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076643</v>
+        <v>120076685</v>
       </c>
       <c r="B131" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14423,25 +14423,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503820</v>
+        <v>503819</v>
       </c>
       <c r="R131" t="n">
-        <v>7134705</v>
+        <v>7134668</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076617</v>
+        <v>120076630</v>
       </c>
       <c r="B132" t="n">
-        <v>96891</v>
+        <v>79623</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14525,25 +14525,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503847</v>
+        <v>503592</v>
       </c>
       <c r="R132" t="n">
-        <v>7134693</v>
+        <v>7134781</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14615,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076660</v>
+        <v>120076613</v>
       </c>
       <c r="B133" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14631,21 +14631,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14655,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503616</v>
+        <v>503646</v>
       </c>
       <c r="R133" t="n">
-        <v>7134591</v>
+        <v>7134570</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14717,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076613</v>
+        <v>120076672</v>
       </c>
       <c r="B134" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14729,25 +14729,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503646</v>
+        <v>503543</v>
       </c>
       <c r="R134" t="n">
-        <v>7134570</v>
+        <v>7134573</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076631</v>
+        <v>120076644</v>
       </c>
       <c r="B135" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14835,21 +14835,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503624</v>
+        <v>503748</v>
       </c>
       <c r="R135" t="n">
-        <v>7134757</v>
+        <v>7134611</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076687</v>
+        <v>120076653</v>
       </c>
       <c r="B136" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14937,21 +14937,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503491</v>
+        <v>503608</v>
       </c>
       <c r="R136" t="n">
-        <v>7134636</v>
+        <v>7134763</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076662</v>
+        <v>120076632</v>
       </c>
       <c r="B137" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15039,21 +15039,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503535</v>
+        <v>503434</v>
       </c>
       <c r="R137" t="n">
-        <v>7134599</v>
+        <v>7134673</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076650</v>
+        <v>120076618</v>
       </c>
       <c r="B67" t="n">
-        <v>90594</v>
+        <v>96891</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503633</v>
+        <v>503850</v>
       </c>
       <c r="R67" t="n">
-        <v>7134566</v>
+        <v>7134617</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076618</v>
+        <v>120076650</v>
       </c>
       <c r="B68" t="n">
-        <v>96891</v>
+        <v>90594</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7983,25 +7983,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503850</v>
+        <v>503633</v>
       </c>
       <c r="R68" t="n">
-        <v>7134617</v>
+        <v>7134566</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076671</v>
+        <v>120076645</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503546</v>
+        <v>503601</v>
       </c>
       <c r="R76" t="n">
-        <v>7134587</v>
+        <v>7134773</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076645</v>
+        <v>120076671</v>
       </c>
       <c r="B77" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503601</v>
+        <v>503546</v>
       </c>
       <c r="R77" t="n">
-        <v>7134773</v>
+        <v>7134587</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076616</v>
+        <v>120076625</v>
       </c>
       <c r="B88" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503430</v>
+        <v>503539</v>
       </c>
       <c r="R88" t="n">
-        <v>7134700</v>
+        <v>7134558</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076611</v>
+        <v>120076624</v>
       </c>
       <c r="B89" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503691</v>
+        <v>503630</v>
       </c>
       <c r="R89" t="n">
-        <v>7134749</v>
+        <v>7134529</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076625</v>
+        <v>120076616</v>
       </c>
       <c r="B90" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503539</v>
+        <v>503430</v>
       </c>
       <c r="R90" t="n">
-        <v>7134558</v>
+        <v>7134700</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076624</v>
+        <v>120076611</v>
       </c>
       <c r="B91" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10333,21 +10333,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503630</v>
+        <v>503691</v>
       </c>
       <c r="R91" t="n">
-        <v>7134529</v>
+        <v>7134749</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -12575,10 +12575,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076617</v>
+        <v>120076628</v>
       </c>
       <c r="B113" t="n">
-        <v>96891</v>
+        <v>79623</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12587,25 +12587,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503847</v>
+        <v>503570</v>
       </c>
       <c r="R113" t="n">
-        <v>7134693</v>
+        <v>7134765</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076661</v>
+        <v>120076634</v>
       </c>
       <c r="B114" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12693,21 +12693,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503604</v>
+        <v>503432</v>
       </c>
       <c r="R114" t="n">
-        <v>7134590</v>
+        <v>7134696</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12779,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076628</v>
+        <v>120076617</v>
       </c>
       <c r="B115" t="n">
-        <v>79623</v>
+        <v>96891</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12791,25 +12791,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503570</v>
+        <v>503847</v>
       </c>
       <c r="R115" t="n">
-        <v>7134765</v>
+        <v>7134693</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076634</v>
+        <v>120076661</v>
       </c>
       <c r="B116" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12897,21 +12897,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503432</v>
+        <v>503604</v>
       </c>
       <c r="R116" t="n">
-        <v>7134696</v>
+        <v>7134590</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120039375</v>
+        <v>120035768</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5529,21 +5529,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503988</v>
+        <v>504187</v>
       </c>
       <c r="R44" t="n">
-        <v>7134466</v>
+        <v>7134438</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120040383</v>
+        <v>120035291</v>
       </c>
       <c r="B45" t="n">
-        <v>90825</v>
+        <v>4863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5627,41 +5627,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>101675</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503879</v>
+        <v>504179</v>
       </c>
       <c r="R45" t="n">
-        <v>7134575</v>
+        <v>7134372</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,6 +5691,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5717,10 +5722,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120035460</v>
+        <v>120038086</v>
       </c>
       <c r="B46" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5733,21 +5738,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5757,13 +5762,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504169</v>
+        <v>503980</v>
       </c>
       <c r="R46" t="n">
-        <v>7134407</v>
+        <v>7134422</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,10 +5824,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120036399</v>
+        <v>120035474</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5831,25 +5836,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5859,13 +5864,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504083</v>
+        <v>504166</v>
       </c>
       <c r="R47" t="n">
-        <v>7134453</v>
+        <v>7134391</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5895,11 +5900,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035291</v>
+        <v>120035015</v>
       </c>
       <c r="B48" t="n">
-        <v>4863</v>
+        <v>78278</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5938,25 +5938,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101675</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504179</v>
+        <v>504196</v>
       </c>
       <c r="R48" t="n">
-        <v>7134372</v>
+        <v>7134350</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6002,11 +6002,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6033,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120034574</v>
+        <v>120034383</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6049,21 +6044,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6073,13 +6068,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504224</v>
+        <v>504257</v>
       </c>
       <c r="R49" t="n">
-        <v>7134352</v>
+        <v>7134334</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6135,10 +6130,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120034826</v>
+        <v>120035460</v>
       </c>
       <c r="B50" t="n">
-        <v>91862</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6147,25 +6142,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4365</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6175,13 +6170,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504226</v>
+        <v>504169</v>
       </c>
       <c r="R50" t="n">
-        <v>7134339</v>
+        <v>7134407</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6237,10 +6232,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120035868</v>
+        <v>120035871</v>
       </c>
       <c r="B51" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6253,21 +6248,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6277,10 +6272,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504193</v>
+        <v>504192</v>
       </c>
       <c r="R51" t="n">
-        <v>7134477</v>
+        <v>7134481</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6441,10 +6436,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120035474</v>
+        <v>120036022</v>
       </c>
       <c r="B53" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6453,25 +6448,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6481,10 +6476,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504166</v>
+        <v>504145</v>
       </c>
       <c r="R53" t="n">
-        <v>7134391</v>
+        <v>7134441</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6543,10 +6538,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120035015</v>
+        <v>120034826</v>
       </c>
       <c r="B54" t="n">
-        <v>78278</v>
+        <v>91862</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6555,25 +6550,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6583,13 +6578,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504196</v>
+        <v>504226</v>
       </c>
       <c r="R54" t="n">
-        <v>7134350</v>
+        <v>7134339</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6645,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120038086</v>
+        <v>120039375</v>
       </c>
       <c r="B55" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6661,21 +6656,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6685,13 +6680,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503980</v>
+        <v>503988</v>
       </c>
       <c r="R55" t="n">
-        <v>7134422</v>
+        <v>7134466</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,10 +6742,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120034479</v>
+        <v>120036399</v>
       </c>
       <c r="B56" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6763,21 +6758,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6787,10 +6782,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504252</v>
+        <v>504083</v>
       </c>
       <c r="R56" t="n">
-        <v>7134346</v>
+        <v>7134453</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6823,6 +6818,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120034383</v>
+        <v>120035622</v>
       </c>
       <c r="B57" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504257</v>
+        <v>504165</v>
       </c>
       <c r="R57" t="n">
-        <v>7134334</v>
+        <v>7134407</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120035622</v>
+        <v>120034479</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504165</v>
+        <v>504252</v>
       </c>
       <c r="R58" t="n">
-        <v>7134407</v>
+        <v>7134346</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120035768</v>
+        <v>120035868</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7093,13 +7093,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504187</v>
+        <v>504193</v>
       </c>
       <c r="R59" t="n">
-        <v>7134438</v>
+        <v>7134477</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120036022</v>
+        <v>120040383</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>90825</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7167,38 +7167,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504145</v>
+        <v>503879</v>
       </c>
       <c r="R60" t="n">
-        <v>7134441</v>
+        <v>7134575</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120035871</v>
+        <v>120034574</v>
       </c>
       <c r="B61" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504192</v>
+        <v>504224</v>
       </c>
       <c r="R61" t="n">
-        <v>7134481</v>
+        <v>7134352</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120039963</v>
+        <v>120046465</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,41 +7371,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503904</v>
+        <v>504001</v>
       </c>
       <c r="R62" t="n">
-        <v>7134523</v>
+        <v>7134466</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120046468</v>
+        <v>120039963</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -7497,17 +7497,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503899</v>
+        <v>503904</v>
       </c>
       <c r="R63" t="n">
-        <v>7134531</v>
+        <v>7134523</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120046465</v>
+        <v>120046464</v>
       </c>
       <c r="B65" t="n">
         <v>78278</v>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504001</v>
+        <v>503874</v>
       </c>
       <c r="R65" t="n">
-        <v>7134466</v>
+        <v>7134566</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120046464</v>
+        <v>120046468</v>
       </c>
       <c r="B66" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7779,25 +7779,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503874</v>
+        <v>503899</v>
       </c>
       <c r="R66" t="n">
-        <v>7134566</v>
+        <v>7134531</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076618</v>
+        <v>120076672</v>
       </c>
       <c r="B67" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7885,21 +7885,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503850</v>
+        <v>503543</v>
       </c>
       <c r="R67" t="n">
-        <v>7134617</v>
+        <v>7134573</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076650</v>
+        <v>120076626</v>
       </c>
       <c r="B68" t="n">
-        <v>90594</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503633</v>
+        <v>503534</v>
       </c>
       <c r="R68" t="n">
-        <v>7134566</v>
+        <v>7134804</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076635</v>
+        <v>120076630</v>
       </c>
       <c r="B69" t="n">
         <v>79623</v>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503426</v>
+        <v>503592</v>
       </c>
       <c r="R69" t="n">
-        <v>7134704</v>
+        <v>7134781</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076633</v>
+        <v>120076637</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503430</v>
+        <v>503530</v>
       </c>
       <c r="R70" t="n">
-        <v>7134677</v>
+        <v>7134806</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120076647</v>
+        <v>120076618</v>
       </c>
       <c r="B71" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503790</v>
+        <v>503850</v>
       </c>
       <c r="R71" t="n">
-        <v>7134698</v>
+        <v>7134617</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076662</v>
+        <v>120076660</v>
       </c>
       <c r="B72" t="n">
         <v>78187</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503535</v>
+        <v>503616</v>
       </c>
       <c r="R72" t="n">
-        <v>7134599</v>
+        <v>7134591</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076673</v>
+        <v>120076614</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503532</v>
+        <v>503427</v>
       </c>
       <c r="R73" t="n">
-        <v>7134595</v>
+        <v>7134675</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076606</v>
+        <v>120076687</v>
       </c>
       <c r="B74" t="n">
-        <v>79652</v>
+        <v>91852</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8595,25 +8595,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503427</v>
+        <v>503491</v>
       </c>
       <c r="R74" t="n">
-        <v>7134680</v>
+        <v>7134636</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,7 +8685,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076631</v>
+        <v>120076635</v>
       </c>
       <c r="B75" t="n">
         <v>79623</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503624</v>
+        <v>503426</v>
       </c>
       <c r="R75" t="n">
-        <v>7134757</v>
+        <v>7134704</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076645</v>
+        <v>120076644</v>
       </c>
       <c r="B76" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503601</v>
+        <v>503748</v>
       </c>
       <c r="R76" t="n">
-        <v>7134773</v>
+        <v>7134611</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076671</v>
+        <v>120076617</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8905,21 +8905,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503546</v>
+        <v>503847</v>
       </c>
       <c r="R77" t="n">
-        <v>7134587</v>
+        <v>7134693</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076629</v>
+        <v>120076623</v>
       </c>
       <c r="B78" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9007,21 +9007,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503568</v>
+        <v>503665</v>
       </c>
       <c r="R78" t="n">
-        <v>7134773</v>
+        <v>7134523</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076646</v>
+        <v>120076616</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9105,25 +9105,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503675</v>
+        <v>503430</v>
       </c>
       <c r="R79" t="n">
-        <v>7134737</v>
+        <v>7134700</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,7 +9195,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076615</v>
+        <v>120076610</v>
       </c>
       <c r="B80" t="n">
         <v>79624</v>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503430</v>
+        <v>503592</v>
       </c>
       <c r="R80" t="n">
-        <v>7134677</v>
+        <v>7134781</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076648</v>
+        <v>120060142</v>
       </c>
       <c r="B81" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9309,41 +9309,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503495</v>
+        <v>503497</v>
       </c>
       <c r="R81" t="n">
-        <v>7134638</v>
+        <v>7134657</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076612</v>
+        <v>120076628</v>
       </c>
       <c r="B82" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9415,21 +9415,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503818</v>
+        <v>503570</v>
       </c>
       <c r="R82" t="n">
-        <v>7134671</v>
+        <v>7134765</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076641</v>
+        <v>120076684</v>
       </c>
       <c r="B83" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9513,25 +9513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503745</v>
+        <v>503568</v>
       </c>
       <c r="R83" t="n">
-        <v>7134697</v>
+        <v>7134774</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076627</v>
+        <v>120076640</v>
       </c>
       <c r="B84" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9619,21 +9619,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503531</v>
+        <v>503654</v>
       </c>
       <c r="R84" t="n">
-        <v>7134812</v>
+        <v>7134725</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076643</v>
+        <v>120076633</v>
       </c>
       <c r="B85" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9721,21 +9721,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503820</v>
+        <v>503430</v>
       </c>
       <c r="R85" t="n">
-        <v>7134705</v>
+        <v>7134677</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,7 +9807,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076665</v>
+        <v>120076661</v>
       </c>
       <c r="B86" t="n">
         <v>78187</v>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503480</v>
+        <v>503604</v>
       </c>
       <c r="R86" t="n">
-        <v>7134647</v>
+        <v>7134590</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076670</v>
+        <v>120076620</v>
       </c>
       <c r="B87" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9921,25 +9921,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503626</v>
+        <v>503618</v>
       </c>
       <c r="R87" t="n">
-        <v>7134549</v>
+        <v>7134495</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076625</v>
+        <v>120076647</v>
       </c>
       <c r="B88" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10023,25 +10023,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503539</v>
+        <v>503790</v>
       </c>
       <c r="R88" t="n">
-        <v>7134558</v>
+        <v>7134698</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076624</v>
+        <v>120076631</v>
       </c>
       <c r="B89" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10129,21 +10129,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503630</v>
+        <v>503624</v>
       </c>
       <c r="R89" t="n">
-        <v>7134529</v>
+        <v>7134757</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10215,10 +10215,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076616</v>
+        <v>120076638</v>
       </c>
       <c r="B90" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10227,25 +10227,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503430</v>
+        <v>503819</v>
       </c>
       <c r="R90" t="n">
-        <v>7134700</v>
+        <v>7134668</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076611</v>
+        <v>120076643</v>
       </c>
       <c r="B91" t="n">
-        <v>79624</v>
+        <v>78278</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10333,21 +10333,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503691</v>
+        <v>503820</v>
       </c>
       <c r="R91" t="n">
-        <v>7134749</v>
+        <v>7134705</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10419,10 +10419,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076654</v>
+        <v>120076602</v>
       </c>
       <c r="B92" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10459,10 +10459,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503821</v>
+        <v>503489</v>
       </c>
       <c r="R92" t="n">
-        <v>7134659</v>
+        <v>7134637</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10521,10 +10521,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120065097</v>
+        <v>120076671</v>
       </c>
       <c r="B93" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10533,44 +10533,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503748</v>
+        <v>503546</v>
       </c>
       <c r="R93" t="n">
-        <v>7134611</v>
+        <v>7134587</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10602,18 +10599,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10632,10 +10623,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076620</v>
+        <v>120076625</v>
       </c>
       <c r="B94" t="n">
-        <v>92048</v>
+        <v>78279</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10648,21 +10639,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10663,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503618</v>
+        <v>503539</v>
       </c>
       <c r="R94" t="n">
-        <v>7134495</v>
+        <v>7134558</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10734,10 +10725,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076608</v>
+        <v>120076601</v>
       </c>
       <c r="B95" t="n">
-        <v>79624</v>
+        <v>79131</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10750,21 +10741,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10774,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503530</v>
+        <v>503546</v>
       </c>
       <c r="R95" t="n">
-        <v>7134813</v>
+        <v>7134565</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10836,10 +10827,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076602</v>
+        <v>120076665</v>
       </c>
       <c r="B96" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10852,21 +10843,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10876,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503489</v>
+        <v>503480</v>
       </c>
       <c r="R96" t="n">
-        <v>7134637</v>
+        <v>7134647</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10938,10 +10929,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076675</v>
+        <v>120076613</v>
       </c>
       <c r="B97" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10950,25 +10941,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10978,10 +10969,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503542</v>
+        <v>503646</v>
       </c>
       <c r="R97" t="n">
-        <v>7134610</v>
+        <v>7134570</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11040,10 +11031,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120064794</v>
+        <v>120076615</v>
       </c>
       <c r="B98" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11052,41 +11043,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503729</v>
+        <v>503430</v>
       </c>
       <c r="R98" t="n">
-        <v>7134606</v>
+        <v>7134677</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11142,10 +11133,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076619</v>
+        <v>120076681</v>
       </c>
       <c r="B99" t="n">
-        <v>91850</v>
+        <v>12337</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11154,25 +11145,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4361</v>
+        <v>101283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11182,10 +11173,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503460</v>
+        <v>503867</v>
       </c>
       <c r="R99" t="n">
-        <v>7134749</v>
+        <v>7134650</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11218,6 +11209,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11244,10 +11240,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076652</v>
+        <v>120076662</v>
       </c>
       <c r="B100" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11260,21 +11256,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11284,10 +11280,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503526</v>
+        <v>503535</v>
       </c>
       <c r="R100" t="n">
-        <v>7134815</v>
+        <v>7134599</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11346,10 +11342,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076681</v>
+        <v>120076599</v>
       </c>
       <c r="B101" t="n">
-        <v>12337</v>
+        <v>90545</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11358,25 +11354,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>101283</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11386,10 +11382,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503867</v>
+        <v>503657</v>
       </c>
       <c r="R101" t="n">
-        <v>7134650</v>
+        <v>7134513</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11422,11 +11418,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11453,10 +11444,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076599</v>
+        <v>120076649</v>
       </c>
       <c r="B102" t="n">
-        <v>90545</v>
+        <v>90576</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11465,25 +11456,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11493,10 +11484,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503657</v>
+        <v>503835</v>
       </c>
       <c r="R102" t="n">
-        <v>7134513</v>
+        <v>7134640</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11555,10 +11546,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076609</v>
+        <v>120076653</v>
       </c>
       <c r="B103" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11571,21 +11562,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11595,10 +11586,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503567</v>
+        <v>503608</v>
       </c>
       <c r="R103" t="n">
-        <v>7134773</v>
+        <v>7134763</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11657,10 +11648,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076626</v>
+        <v>120076652</v>
       </c>
       <c r="B104" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11673,21 +11664,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11697,10 +11688,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503534</v>
+        <v>503526</v>
       </c>
       <c r="R104" t="n">
-        <v>7134804</v>
+        <v>7134815</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11759,10 +11750,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076640</v>
+        <v>120076627</v>
       </c>
       <c r="B105" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11775,21 +11766,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11799,10 +11790,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503654</v>
+        <v>503531</v>
       </c>
       <c r="R105" t="n">
-        <v>7134725</v>
+        <v>7134812</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11861,10 +11852,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076639</v>
+        <v>120076609</v>
       </c>
       <c r="B106" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11873,25 +11864,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11901,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503430</v>
+        <v>503567</v>
       </c>
       <c r="R106" t="n">
-        <v>7134677</v>
+        <v>7134773</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11963,10 +11954,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076600</v>
+        <v>120076676</v>
       </c>
       <c r="B107" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11975,25 +11966,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12003,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503603</v>
+        <v>503536</v>
       </c>
       <c r="R107" t="n">
-        <v>7134592</v>
+        <v>7134619</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12065,10 +12056,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076610</v>
+        <v>120076677</v>
       </c>
       <c r="B108" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12077,25 +12068,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12105,10 +12096,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503592</v>
+        <v>503481</v>
       </c>
       <c r="R108" t="n">
-        <v>7134781</v>
+        <v>7134655</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12167,10 +12158,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076684</v>
+        <v>120076600</v>
       </c>
       <c r="B109" t="n">
-        <v>79658</v>
+        <v>79131</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12179,25 +12170,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12207,10 +12198,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503568</v>
+        <v>503603</v>
       </c>
       <c r="R109" t="n">
-        <v>7134774</v>
+        <v>7134592</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12269,10 +12260,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076638</v>
+        <v>120076632</v>
       </c>
       <c r="B110" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12281,25 +12272,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12309,10 +12300,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503819</v>
+        <v>503434</v>
       </c>
       <c r="R110" t="n">
-        <v>7134668</v>
+        <v>7134673</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12371,10 +12362,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076601</v>
+        <v>120076685</v>
       </c>
       <c r="B111" t="n">
-        <v>79131</v>
+        <v>79658</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12383,25 +12374,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12411,10 +12402,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503546</v>
+        <v>503819</v>
       </c>
       <c r="R111" t="n">
-        <v>7134565</v>
+        <v>7134668</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12473,10 +12464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076636</v>
+        <v>120076641</v>
       </c>
       <c r="B112" t="n">
-        <v>79659</v>
+        <v>78278</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12485,25 +12476,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12513,10 +12504,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503530</v>
+        <v>503745</v>
       </c>
       <c r="R112" t="n">
-        <v>7134813</v>
+        <v>7134697</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12575,10 +12566,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076628</v>
+        <v>120076608</v>
       </c>
       <c r="B113" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12591,21 +12582,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12615,10 +12606,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503570</v>
+        <v>503530</v>
       </c>
       <c r="R113" t="n">
-        <v>7134765</v>
+        <v>7134813</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12677,10 +12668,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076634</v>
+        <v>120076650</v>
       </c>
       <c r="B114" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12693,21 +12684,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12717,10 +12708,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503432</v>
+        <v>503633</v>
       </c>
       <c r="R114" t="n">
-        <v>7134696</v>
+        <v>7134566</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12779,10 +12770,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076617</v>
+        <v>120076673</v>
       </c>
       <c r="B115" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12795,21 +12786,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12810,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503847</v>
+        <v>503532</v>
       </c>
       <c r="R115" t="n">
-        <v>7134693</v>
+        <v>7134595</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12881,10 +12872,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120076661</v>
+        <v>120065097</v>
       </c>
       <c r="B116" t="n">
-        <v>78187</v>
+        <v>91904</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12893,41 +12884,44 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>232140</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503604</v>
+        <v>503748</v>
       </c>
       <c r="R116" t="n">
-        <v>7134590</v>
+        <v>7134611</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12959,12 +12953,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076687</v>
+        <v>120076639</v>
       </c>
       <c r="B117" t="n">
-        <v>91852</v>
+        <v>79659</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12995,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503491</v>
+        <v>503430</v>
       </c>
       <c r="R117" t="n">
-        <v>7134636</v>
+        <v>7134677</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076686</v>
+        <v>120076675</v>
       </c>
       <c r="B118" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13101,21 +13101,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503428</v>
+        <v>503542</v>
       </c>
       <c r="R118" t="n">
-        <v>7134677</v>
+        <v>7134610</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076651</v>
+        <v>120076646</v>
       </c>
       <c r="B119" t="n">
-        <v>90730</v>
+        <v>97930</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13203,21 +13203,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503516</v>
+        <v>503675</v>
       </c>
       <c r="R119" t="n">
-        <v>7134622</v>
+        <v>7134737</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,7 +13289,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076677</v>
+        <v>120064794</v>
       </c>
       <c r="B120" t="n">
         <v>91858</v>
@@ -13325,17 +13325,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503481</v>
+        <v>503729</v>
       </c>
       <c r="R120" t="n">
-        <v>7134655</v>
+        <v>7134606</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076605</v>
+        <v>120076686</v>
       </c>
       <c r="B121" t="n">
-        <v>79652</v>
+        <v>79658</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13407,21 +13407,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503568</v>
+        <v>503428</v>
       </c>
       <c r="R121" t="n">
-        <v>7134774</v>
+        <v>7134677</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076637</v>
+        <v>120076634</v>
       </c>
       <c r="B122" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503530</v>
+        <v>503432</v>
       </c>
       <c r="R122" t="n">
-        <v>7134806</v>
+        <v>7134696</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076664</v>
+        <v>120076619</v>
       </c>
       <c r="B123" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503543</v>
+        <v>503460</v>
       </c>
       <c r="R123" t="n">
-        <v>7134608</v>
+        <v>7134749</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076674</v>
+        <v>120076612</v>
       </c>
       <c r="B124" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13709,25 +13709,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503558</v>
+        <v>503818</v>
       </c>
       <c r="R124" t="n">
-        <v>7134614</v>
+        <v>7134671</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120060142</v>
+        <v>120076611</v>
       </c>
       <c r="B125" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,41 +13811,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503497</v>
+        <v>503691</v>
       </c>
       <c r="R125" t="n">
-        <v>7134657</v>
+        <v>7134749</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13901,10 +13901,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076660</v>
+        <v>120076651</v>
       </c>
       <c r="B126" t="n">
-        <v>78187</v>
+        <v>90730</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13913,25 +13913,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503616</v>
+        <v>503516</v>
       </c>
       <c r="R126" t="n">
-        <v>7134591</v>
+        <v>7134622</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076649</v>
+        <v>120076645</v>
       </c>
       <c r="B127" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503835</v>
+        <v>503601</v>
       </c>
       <c r="R127" t="n">
-        <v>7134640</v>
+        <v>7134773</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,10 +14105,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076623</v>
+        <v>120076664</v>
       </c>
       <c r="B128" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503665</v>
+        <v>503543</v>
       </c>
       <c r="R128" t="n">
-        <v>7134523</v>
+        <v>7134608</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14207,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076676</v>
+        <v>120076606</v>
       </c>
       <c r="B129" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14223,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503536</v>
+        <v>503427</v>
       </c>
       <c r="R129" t="n">
-        <v>7134619</v>
+        <v>7134680</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076614</v>
+        <v>120076670</v>
       </c>
       <c r="B130" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14321,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14349,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503427</v>
+        <v>503626</v>
       </c>
       <c r="R130" t="n">
-        <v>7134675</v>
+        <v>7134549</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076685</v>
+        <v>120076674</v>
       </c>
       <c r="B131" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14427,21 +14427,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503819</v>
+        <v>503558</v>
       </c>
       <c r="R131" t="n">
-        <v>7134668</v>
+        <v>7134614</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076630</v>
+        <v>120076624</v>
       </c>
       <c r="B132" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14529,21 +14529,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503592</v>
+        <v>503630</v>
       </c>
       <c r="R132" t="n">
-        <v>7134781</v>
+        <v>7134529</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14615,10 +14615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076613</v>
+        <v>120076654</v>
       </c>
       <c r="B133" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14631,21 +14631,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14655,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503646</v>
+        <v>503821</v>
       </c>
       <c r="R133" t="n">
-        <v>7134570</v>
+        <v>7134659</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14717,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076672</v>
+        <v>120076648</v>
       </c>
       <c r="B134" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14729,25 +14729,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503543</v>
+        <v>503495</v>
       </c>
       <c r="R134" t="n">
-        <v>7134573</v>
+        <v>7134638</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076644</v>
+        <v>120076605</v>
       </c>
       <c r="B135" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503748</v>
+        <v>503568</v>
       </c>
       <c r="R135" t="n">
-        <v>7134611</v>
+        <v>7134774</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076653</v>
+        <v>120076629</v>
       </c>
       <c r="B136" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14937,21 +14937,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503608</v>
+        <v>503568</v>
       </c>
       <c r="R136" t="n">
-        <v>7134763</v>
+        <v>7134773</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076632</v>
+        <v>120076636</v>
       </c>
       <c r="B137" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15035,25 +15035,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503434</v>
+        <v>503530</v>
       </c>
       <c r="R137" t="n">
-        <v>7134673</v>
+        <v>7134813</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120035768</v>
+        <v>120035474</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504187</v>
+        <v>504166</v>
       </c>
       <c r="R44" t="n">
-        <v>7134438</v>
+        <v>7134391</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120035291</v>
+        <v>120034574</v>
       </c>
       <c r="B45" t="n">
-        <v>4863</v>
+        <v>78278</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5627,25 +5627,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101675</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504179</v>
+        <v>504224</v>
       </c>
       <c r="R45" t="n">
-        <v>7134372</v>
+        <v>7134352</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,11 +5691,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5722,10 +5717,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120038086</v>
+        <v>120035542</v>
       </c>
       <c r="B46" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5738,21 +5733,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5762,13 +5757,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503980</v>
+        <v>504175</v>
       </c>
       <c r="R46" t="n">
-        <v>7134422</v>
+        <v>7134410</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5824,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120035474</v>
+        <v>120035871</v>
       </c>
       <c r="B47" t="n">
-        <v>79652</v>
+        <v>78187</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5836,25 +5831,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5864,10 +5859,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504166</v>
+        <v>504192</v>
       </c>
       <c r="R47" t="n">
-        <v>7134391</v>
+        <v>7134481</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5926,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120035015</v>
+        <v>120036022</v>
       </c>
       <c r="B48" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5942,21 +5937,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5966,13 +5961,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504196</v>
+        <v>504145</v>
       </c>
       <c r="R48" t="n">
-        <v>7134350</v>
+        <v>7134441</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120034383</v>
+        <v>120035868</v>
       </c>
       <c r="B49" t="n">
         <v>78279</v>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504257</v>
+        <v>504193</v>
       </c>
       <c r="R49" t="n">
-        <v>7134334</v>
+        <v>7134477</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6130,10 +6125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120035460</v>
+        <v>120035768</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6146,21 +6141,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6170,10 +6165,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504169</v>
+        <v>504187</v>
       </c>
       <c r="R50" t="n">
-        <v>7134407</v>
+        <v>7134438</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6232,10 +6227,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120035871</v>
+        <v>120034826</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>91862</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6244,25 +6239,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6272,10 +6267,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504192</v>
+        <v>504226</v>
       </c>
       <c r="R51" t="n">
-        <v>7134481</v>
+        <v>7134339</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6334,10 +6329,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120035542</v>
+        <v>120038086</v>
       </c>
       <c r="B52" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6350,21 +6345,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6374,13 +6369,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504175</v>
+        <v>503980</v>
       </c>
       <c r="R52" t="n">
-        <v>7134410</v>
+        <v>7134422</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6436,10 +6431,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120036022</v>
+        <v>120035015</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6452,21 +6447,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6476,13 +6471,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504145</v>
+        <v>504196</v>
       </c>
       <c r="R53" t="n">
-        <v>7134441</v>
+        <v>7134350</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6538,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120034826</v>
+        <v>120034479</v>
       </c>
       <c r="B54" t="n">
-        <v>91862</v>
+        <v>78278</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,25 +6545,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6578,13 +6573,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504226</v>
+        <v>504252</v>
       </c>
       <c r="R54" t="n">
-        <v>7134339</v>
+        <v>7134346</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6640,10 +6635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120039375</v>
+        <v>120035291</v>
       </c>
       <c r="B55" t="n">
-        <v>78278</v>
+        <v>4863</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6652,25 +6647,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>101675</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6680,13 +6675,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503988</v>
+        <v>504179</v>
       </c>
       <c r="R55" t="n">
-        <v>7134466</v>
+        <v>7134372</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6716,6 +6711,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Kläckhål i äldre asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120035622</v>
+        <v>120034383</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504165</v>
+        <v>504257</v>
       </c>
       <c r="R57" t="n">
-        <v>7134407</v>
+        <v>7134334</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120034479</v>
+        <v>120039375</v>
       </c>
       <c r="B58" t="n">
         <v>78278</v>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504252</v>
+        <v>503988</v>
       </c>
       <c r="R58" t="n">
-        <v>7134346</v>
+        <v>7134466</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120035868</v>
+        <v>120040383</v>
       </c>
       <c r="B59" t="n">
-        <v>78279</v>
+        <v>90825</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7065,38 +7065,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Strömsund, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504193</v>
+        <v>503879</v>
       </c>
       <c r="R59" t="n">
-        <v>7134477</v>
+        <v>7134575</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120040383</v>
+        <v>120035460</v>
       </c>
       <c r="B60" t="n">
-        <v>90825</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7167,41 +7167,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Strömsund, Strömsund, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503879</v>
+        <v>504169</v>
       </c>
       <c r="R60" t="n">
-        <v>7134575</v>
+        <v>7134407</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120034574</v>
+        <v>120035622</v>
       </c>
       <c r="B61" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504224</v>
+        <v>504165</v>
       </c>
       <c r="R61" t="n">
-        <v>7134352</v>
+        <v>7134407</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120046465</v>
+        <v>120046468</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7371,25 +7371,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504001</v>
+        <v>503899</v>
       </c>
       <c r="R62" t="n">
-        <v>7134466</v>
+        <v>7134531</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120038261</v>
+        <v>120046464</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,41 +7575,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503997</v>
+        <v>503874</v>
       </c>
       <c r="R64" t="n">
-        <v>7134441</v>
+        <v>7134566</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120046464</v>
+        <v>120038261</v>
       </c>
       <c r="B65" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7677,41 +7677,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåberget, Sönner-Storåberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503874</v>
+        <v>503997</v>
       </c>
       <c r="R65" t="n">
-        <v>7134566</v>
+        <v>7134441</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120046468</v>
+        <v>120046465</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7779,25 +7779,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503899</v>
+        <v>504001</v>
       </c>
       <c r="R66" t="n">
-        <v>7134531</v>
+        <v>7134466</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076672</v>
+        <v>120076665</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503543</v>
+        <v>503480</v>
       </c>
       <c r="R67" t="n">
-        <v>7134573</v>
+        <v>7134647</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076626</v>
+        <v>120076620</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>92048</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503534</v>
+        <v>503618</v>
       </c>
       <c r="R68" t="n">
-        <v>7134804</v>
+        <v>7134495</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8073,10 +8073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120076630</v>
+        <v>120076615</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503592</v>
+        <v>503430</v>
       </c>
       <c r="R69" t="n">
-        <v>7134781</v>
+        <v>7134677</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076637</v>
+        <v>120076645</v>
       </c>
       <c r="B70" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503530</v>
+        <v>503601</v>
       </c>
       <c r="R70" t="n">
-        <v>7134806</v>
+        <v>7134773</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076660</v>
+        <v>120076624</v>
       </c>
       <c r="B72" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8395,21 +8395,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503616</v>
+        <v>503630</v>
       </c>
       <c r="R72" t="n">
-        <v>7134591</v>
+        <v>7134529</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076614</v>
+        <v>120076626</v>
       </c>
       <c r="B73" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8497,21 +8497,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503427</v>
+        <v>503534</v>
       </c>
       <c r="R73" t="n">
-        <v>7134675</v>
+        <v>7134804</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8583,10 +8583,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120076687</v>
+        <v>120076613</v>
       </c>
       <c r="B74" t="n">
-        <v>91852</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8599,21 +8599,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503491</v>
+        <v>503646</v>
       </c>
       <c r="R74" t="n">
-        <v>7134636</v>
+        <v>7134570</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120076635</v>
+        <v>120076677</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,25 +8697,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503426</v>
+        <v>503481</v>
       </c>
       <c r="R75" t="n">
-        <v>7134704</v>
+        <v>7134655</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8787,10 +8787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120076644</v>
+        <v>120076673</v>
       </c>
       <c r="B76" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8799,25 +8799,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503748</v>
+        <v>503532</v>
       </c>
       <c r="R76" t="n">
-        <v>7134611</v>
+        <v>7134595</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120076617</v>
+        <v>120076600</v>
       </c>
       <c r="B77" t="n">
-        <v>96891</v>
+        <v>79131</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503847</v>
+        <v>503603</v>
       </c>
       <c r="R77" t="n">
-        <v>7134693</v>
+        <v>7134592</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120076623</v>
+        <v>120076641</v>
       </c>
       <c r="B78" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9007,21 +9007,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503665</v>
+        <v>503745</v>
       </c>
       <c r="R78" t="n">
-        <v>7134523</v>
+        <v>7134697</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120076616</v>
+        <v>120076649</v>
       </c>
       <c r="B79" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9109,21 +9109,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503430</v>
+        <v>503835</v>
       </c>
       <c r="R79" t="n">
-        <v>7134700</v>
+        <v>7134640</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120076610</v>
+        <v>120076662</v>
       </c>
       <c r="B80" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9211,21 +9211,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503592</v>
+        <v>503535</v>
       </c>
       <c r="R80" t="n">
-        <v>7134781</v>
+        <v>7134599</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9297,7 +9297,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120060142</v>
+        <v>120076671</v>
       </c>
       <c r="B81" t="n">
         <v>91858</v>
@@ -9333,17 +9333,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503497</v>
+        <v>503546</v>
       </c>
       <c r="R81" t="n">
-        <v>7134657</v>
+        <v>7134587</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076628</v>
+        <v>120076672</v>
       </c>
       <c r="B82" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9411,25 +9411,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503570</v>
+        <v>503543</v>
       </c>
       <c r="R82" t="n">
-        <v>7134765</v>
+        <v>7134573</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076684</v>
+        <v>120076602</v>
       </c>
       <c r="B83" t="n">
-        <v>79658</v>
+        <v>89650</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9513,25 +9513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>1962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503568</v>
+        <v>503489</v>
       </c>
       <c r="R83" t="n">
-        <v>7134774</v>
+        <v>7134637</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120076640</v>
+        <v>120076652</v>
       </c>
       <c r="B84" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9619,21 +9619,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503654</v>
+        <v>503526</v>
       </c>
       <c r="R84" t="n">
-        <v>7134725</v>
+        <v>7134815</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120076633</v>
+        <v>120076654</v>
       </c>
       <c r="B85" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9721,21 +9721,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503430</v>
+        <v>503821</v>
       </c>
       <c r="R85" t="n">
-        <v>7134677</v>
+        <v>7134659</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120076661</v>
+        <v>120076605</v>
       </c>
       <c r="B86" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9819,25 +9819,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503604</v>
+        <v>503568</v>
       </c>
       <c r="R86" t="n">
-        <v>7134590</v>
+        <v>7134774</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120076620</v>
+        <v>120076633</v>
       </c>
       <c r="B87" t="n">
-        <v>92048</v>
+        <v>79623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9925,21 +9925,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503618</v>
+        <v>503430</v>
       </c>
       <c r="R87" t="n">
-        <v>7134495</v>
+        <v>7134677</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120076647</v>
+        <v>120076681</v>
       </c>
       <c r="B88" t="n">
-        <v>97930</v>
+        <v>12337</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10023,25 +10023,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503790</v>
+        <v>503867</v>
       </c>
       <c r="R88" t="n">
-        <v>7134698</v>
+        <v>7134650</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10087,6 +10087,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10113,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120076631</v>
+        <v>120060142</v>
       </c>
       <c r="B89" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10125,41 +10130,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503624</v>
+        <v>503497</v>
       </c>
       <c r="R89" t="n">
-        <v>7134757</v>
+        <v>7134657</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10215,10 +10220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120076638</v>
+        <v>120076647</v>
       </c>
       <c r="B90" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10227,25 +10232,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10260,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>503819</v>
+        <v>503790</v>
       </c>
       <c r="R90" t="n">
-        <v>7134668</v>
+        <v>7134698</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10317,10 +10322,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120076643</v>
+        <v>120076617</v>
       </c>
       <c r="B91" t="n">
-        <v>78278</v>
+        <v>96891</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10329,25 +10334,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10357,10 +10362,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>503820</v>
+        <v>503847</v>
       </c>
       <c r="R91" t="n">
-        <v>7134705</v>
+        <v>7134693</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10419,10 +10424,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120076602</v>
+        <v>120076601</v>
       </c>
       <c r="B92" t="n">
-        <v>89650</v>
+        <v>79131</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10435,21 +10440,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10459,10 +10464,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>503489</v>
+        <v>503546</v>
       </c>
       <c r="R92" t="n">
-        <v>7134637</v>
+        <v>7134565</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10521,10 +10526,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120076671</v>
+        <v>120076623</v>
       </c>
       <c r="B93" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10533,25 +10538,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10561,10 +10566,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>503546</v>
+        <v>503665</v>
       </c>
       <c r="R93" t="n">
-        <v>7134587</v>
+        <v>7134523</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10623,10 +10628,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076625</v>
+        <v>120076609</v>
       </c>
       <c r="B94" t="n">
-        <v>78279</v>
+        <v>79624</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10639,21 +10644,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10663,10 +10668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503539</v>
+        <v>503567</v>
       </c>
       <c r="R94" t="n">
-        <v>7134558</v>
+        <v>7134773</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10725,10 +10730,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076601</v>
+        <v>120076611</v>
       </c>
       <c r="B95" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10741,21 +10746,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10770,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503546</v>
+        <v>503691</v>
       </c>
       <c r="R95" t="n">
-        <v>7134565</v>
+        <v>7134749</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10827,10 +10832,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076665</v>
+        <v>120076634</v>
       </c>
       <c r="B96" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10843,21 +10848,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10867,10 +10872,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503480</v>
+        <v>503432</v>
       </c>
       <c r="R96" t="n">
-        <v>7134647</v>
+        <v>7134696</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10929,10 +10934,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076613</v>
+        <v>120076636</v>
       </c>
       <c r="B97" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10941,25 +10946,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10969,10 +10974,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503646</v>
+        <v>503530</v>
       </c>
       <c r="R97" t="n">
-        <v>7134570</v>
+        <v>7134813</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11031,10 +11036,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076615</v>
+        <v>120076631</v>
       </c>
       <c r="B98" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11047,21 +11052,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11071,10 +11076,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503430</v>
+        <v>503624</v>
       </c>
       <c r="R98" t="n">
-        <v>7134677</v>
+        <v>7134757</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11133,10 +11138,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120076681</v>
+        <v>120076661</v>
       </c>
       <c r="B99" t="n">
-        <v>12337</v>
+        <v>78187</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11145,25 +11150,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>101283</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11173,10 +11178,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503867</v>
+        <v>503604</v>
       </c>
       <c r="R99" t="n">
-        <v>7134650</v>
+        <v>7134590</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11209,11 +11214,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11240,10 +11240,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120076662</v>
+        <v>120076619</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11256,21 +11256,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11280,10 +11280,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>503535</v>
+        <v>503460</v>
       </c>
       <c r="R100" t="n">
-        <v>7134599</v>
+        <v>7134749</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11342,10 +11342,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120076599</v>
+        <v>120076643</v>
       </c>
       <c r="B101" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11354,25 +11354,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11382,10 +11382,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503657</v>
+        <v>503820</v>
       </c>
       <c r="R101" t="n">
-        <v>7134513</v>
+        <v>7134705</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11444,10 +11444,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120076649</v>
+        <v>120076637</v>
       </c>
       <c r="B102" t="n">
-        <v>90576</v>
+        <v>79659</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11456,25 +11456,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503835</v>
+        <v>503530</v>
       </c>
       <c r="R102" t="n">
-        <v>7134640</v>
+        <v>7134806</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11546,10 +11546,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120076653</v>
+        <v>120076614</v>
       </c>
       <c r="B103" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11562,21 +11562,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503608</v>
+        <v>503427</v>
       </c>
       <c r="R103" t="n">
-        <v>7134763</v>
+        <v>7134675</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120076652</v>
+        <v>120076629</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11664,21 +11664,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503526</v>
+        <v>503568</v>
       </c>
       <c r="R104" t="n">
-        <v>7134815</v>
+        <v>7134773</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11750,10 +11750,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076627</v>
+        <v>120076648</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>89247</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11762,25 +11762,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1596</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503531</v>
+        <v>503495</v>
       </c>
       <c r="R105" t="n">
-        <v>7134812</v>
+        <v>7134638</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11852,7 +11852,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076609</v>
+        <v>120076608</v>
       </c>
       <c r="B106" t="n">
         <v>79624</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503567</v>
+        <v>503530</v>
       </c>
       <c r="R106" t="n">
-        <v>7134773</v>
+        <v>7134813</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11954,10 +11954,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076676</v>
+        <v>120076612</v>
       </c>
       <c r="B107" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11966,25 +11966,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503536</v>
+        <v>503818</v>
       </c>
       <c r="R107" t="n">
-        <v>7134619</v>
+        <v>7134671</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076677</v>
+        <v>120076628</v>
       </c>
       <c r="B108" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12068,25 +12068,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12096,10 +12096,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503481</v>
+        <v>503570</v>
       </c>
       <c r="R108" t="n">
-        <v>7134655</v>
+        <v>7134765</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12158,10 +12158,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076600</v>
+        <v>120076635</v>
       </c>
       <c r="B109" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12174,21 +12174,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12198,10 +12198,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503603</v>
+        <v>503426</v>
       </c>
       <c r="R109" t="n">
-        <v>7134592</v>
+        <v>7134704</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,10 +12260,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076632</v>
+        <v>120076639</v>
       </c>
       <c r="B110" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12272,25 +12272,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12300,10 +12300,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503434</v>
+        <v>503430</v>
       </c>
       <c r="R110" t="n">
-        <v>7134673</v>
+        <v>7134677</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12362,10 +12362,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120076685</v>
+        <v>120064794</v>
       </c>
       <c r="B111" t="n">
-        <v>79658</v>
+        <v>91858</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12378,37 +12378,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503819</v>
+        <v>503729</v>
       </c>
       <c r="R111" t="n">
-        <v>7134668</v>
+        <v>7134606</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12464,10 +12464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076641</v>
+        <v>120076664</v>
       </c>
       <c r="B112" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12480,21 +12480,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503745</v>
+        <v>503543</v>
       </c>
       <c r="R112" t="n">
-        <v>7134697</v>
+        <v>7134608</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120076608</v>
+        <v>120076653</v>
       </c>
       <c r="B113" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12582,21 +12582,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12606,10 +12606,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503530</v>
+        <v>503608</v>
       </c>
       <c r="R113" t="n">
-        <v>7134813</v>
+        <v>7134763</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12668,10 +12668,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120076650</v>
+        <v>120076610</v>
       </c>
       <c r="B114" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12684,21 +12684,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12708,10 +12708,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503633</v>
+        <v>503592</v>
       </c>
       <c r="R114" t="n">
-        <v>7134566</v>
+        <v>7134781</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12770,10 +12770,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120076673</v>
+        <v>120076684</v>
       </c>
       <c r="B115" t="n">
-        <v>91858</v>
+        <v>79658</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12786,21 +12786,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12810,10 +12810,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503532</v>
+        <v>503568</v>
       </c>
       <c r="R115" t="n">
-        <v>7134595</v>
+        <v>7134774</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12872,10 +12872,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120065097</v>
+        <v>120076644</v>
       </c>
       <c r="B116" t="n">
-        <v>91904</v>
+        <v>78278</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12884,34 +12884,31 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -12921,7 +12918,7 @@
         <v>7134611</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12953,18 +12950,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12983,10 +12974,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120076639</v>
+        <v>120076646</v>
       </c>
       <c r="B117" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12986,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13014,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503430</v>
+        <v>503675</v>
       </c>
       <c r="R117" t="n">
-        <v>7134677</v>
+        <v>7134737</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13085,10 +13076,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120076675</v>
+        <v>120076650</v>
       </c>
       <c r="B118" t="n">
-        <v>91858</v>
+        <v>90594</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13097,25 +13088,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13125,10 +13116,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503542</v>
+        <v>503633</v>
       </c>
       <c r="R118" t="n">
-        <v>7134610</v>
+        <v>7134566</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13187,10 +13178,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120076646</v>
+        <v>120076670</v>
       </c>
       <c r="B119" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13199,25 +13190,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13218,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503675</v>
+        <v>503626</v>
       </c>
       <c r="R119" t="n">
-        <v>7134737</v>
+        <v>7134549</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13289,10 +13280,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120064794</v>
+        <v>120076632</v>
       </c>
       <c r="B120" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13301,41 +13292,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503729</v>
+        <v>503434</v>
       </c>
       <c r="R120" t="n">
-        <v>7134606</v>
+        <v>7134673</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13391,10 +13382,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076686</v>
+        <v>120076651</v>
       </c>
       <c r="B121" t="n">
-        <v>79658</v>
+        <v>90730</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,25 +13394,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13431,10 +13422,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503428</v>
+        <v>503516</v>
       </c>
       <c r="R121" t="n">
-        <v>7134677</v>
+        <v>7134622</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13493,10 +13484,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076634</v>
+        <v>120076616</v>
       </c>
       <c r="B122" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13509,21 +13500,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13524,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503432</v>
+        <v>503430</v>
       </c>
       <c r="R122" t="n">
-        <v>7134696</v>
+        <v>7134700</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13595,10 +13586,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120076619</v>
+        <v>120076685</v>
       </c>
       <c r="B123" t="n">
-        <v>91850</v>
+        <v>79658</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13607,25 +13598,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13635,10 +13626,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503460</v>
+        <v>503819</v>
       </c>
       <c r="R123" t="n">
-        <v>7134749</v>
+        <v>7134668</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13697,10 +13688,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120076612</v>
+        <v>120076625</v>
       </c>
       <c r="B124" t="n">
-        <v>79624</v>
+        <v>78279</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13713,21 +13704,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13737,10 +13728,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503818</v>
+        <v>503539</v>
       </c>
       <c r="R124" t="n">
-        <v>7134671</v>
+        <v>7134558</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13799,10 +13790,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120076611</v>
+        <v>120076599</v>
       </c>
       <c r="B125" t="n">
-        <v>79624</v>
+        <v>90545</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13811,25 +13802,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13839,10 +13830,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503691</v>
+        <v>503657</v>
       </c>
       <c r="R125" t="n">
-        <v>7134749</v>
+        <v>7134513</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13901,10 +13892,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120076651</v>
+        <v>120076640</v>
       </c>
       <c r="B126" t="n">
-        <v>90730</v>
+        <v>78278</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13913,25 +13904,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13941,10 +13932,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503516</v>
+        <v>503654</v>
       </c>
       <c r="R126" t="n">
-        <v>7134622</v>
+        <v>7134725</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14003,10 +13994,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120076645</v>
+        <v>120076686</v>
       </c>
       <c r="B127" t="n">
-        <v>97930</v>
+        <v>79658</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14015,25 +14006,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14043,10 +14034,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503601</v>
+        <v>503428</v>
       </c>
       <c r="R127" t="n">
-        <v>7134773</v>
+        <v>7134677</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14105,7 +14096,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120076664</v>
+        <v>120076660</v>
       </c>
       <c r="B128" t="n">
         <v>78187</v>
@@ -14145,10 +14136,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>503543</v>
+        <v>503616</v>
       </c>
       <c r="R128" t="n">
-        <v>7134608</v>
+        <v>7134591</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14207,10 +14198,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120076606</v>
+        <v>120076675</v>
       </c>
       <c r="B129" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14223,21 +14214,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14247,10 +14238,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>503427</v>
+        <v>503542</v>
       </c>
       <c r="R129" t="n">
-        <v>7134680</v>
+        <v>7134610</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14309,10 +14300,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120076670</v>
+        <v>120076687</v>
       </c>
       <c r="B130" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14321,25 +14312,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14349,10 +14340,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503626</v>
+        <v>503491</v>
       </c>
       <c r="R130" t="n">
-        <v>7134549</v>
+        <v>7134636</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14411,10 +14402,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120076674</v>
+        <v>120076638</v>
       </c>
       <c r="B131" t="n">
-        <v>91858</v>
+        <v>79659</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14427,21 +14418,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14451,10 +14442,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503558</v>
+        <v>503819</v>
       </c>
       <c r="R131" t="n">
-        <v>7134614</v>
+        <v>7134668</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14513,10 +14504,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120076624</v>
+        <v>120076630</v>
       </c>
       <c r="B132" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14529,21 +14520,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14553,10 +14544,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503630</v>
+        <v>503592</v>
       </c>
       <c r="R132" t="n">
-        <v>7134529</v>
+        <v>7134781</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14615,10 +14606,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120076654</v>
+        <v>120076627</v>
       </c>
       <c r="B133" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14631,21 +14622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14655,10 +14646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503821</v>
+        <v>503531</v>
       </c>
       <c r="R133" t="n">
-        <v>7134659</v>
+        <v>7134812</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14717,10 +14708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120076648</v>
+        <v>120076606</v>
       </c>
       <c r="B134" t="n">
-        <v>89247</v>
+        <v>79652</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14729,25 +14720,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1596</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14757,10 +14748,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503495</v>
+        <v>503427</v>
       </c>
       <c r="R134" t="n">
-        <v>7134638</v>
+        <v>7134680</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14819,10 +14810,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120076605</v>
+        <v>120076674</v>
       </c>
       <c r="B135" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14835,21 +14826,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14859,10 +14850,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503568</v>
+        <v>503558</v>
       </c>
       <c r="R135" t="n">
-        <v>7134774</v>
+        <v>7134614</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14921,10 +14912,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120076629</v>
+        <v>120076676</v>
       </c>
       <c r="B136" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,25 +14924,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14961,10 +14952,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503568</v>
+        <v>503536</v>
       </c>
       <c r="R136" t="n">
-        <v>7134773</v>
+        <v>7134619</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15023,10 +15014,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120076636</v>
+        <v>120065097</v>
       </c>
       <c r="B137" t="n">
-        <v>79659</v>
+        <v>91904</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15035,41 +15026,44 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>232140</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503530</v>
+        <v>503748</v>
       </c>
       <c r="R137" t="n">
-        <v>7134813</v>
+        <v>7134611</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15101,12 +15095,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -8175,10 +8175,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120076645</v>
+        <v>120076626</v>
       </c>
       <c r="B70" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503601</v>
+        <v>503534</v>
       </c>
       <c r="R70" t="n">
-        <v>7134773</v>
+        <v>7134804</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120076624</v>
+        <v>120076645</v>
       </c>
       <c r="B72" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503630</v>
+        <v>503601</v>
       </c>
       <c r="R72" t="n">
-        <v>7134529</v>
+        <v>7134773</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120076626</v>
+        <v>120076624</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8497,21 +8497,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503534</v>
+        <v>503630</v>
       </c>
       <c r="R73" t="n">
-        <v>7134804</v>
+        <v>7134529</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9297,10 +9297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120076671</v>
+        <v>120076602</v>
       </c>
       <c r="B81" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9309,25 +9309,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503546</v>
+        <v>503489</v>
       </c>
       <c r="R81" t="n">
-        <v>7134587</v>
+        <v>7134637</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9399,7 +9399,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120076672</v>
+        <v>120076671</v>
       </c>
       <c r="B82" t="n">
         <v>91858</v>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503543</v>
+        <v>503546</v>
       </c>
       <c r="R82" t="n">
-        <v>7134573</v>
+        <v>7134587</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120076602</v>
+        <v>120076672</v>
       </c>
       <c r="B83" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9513,25 +9513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503489</v>
+        <v>503543</v>
       </c>
       <c r="R83" t="n">
-        <v>7134637</v>
+        <v>7134573</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10628,10 +10628,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120076609</v>
+        <v>120076634</v>
       </c>
       <c r="B94" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10644,21 +10644,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>503567</v>
+        <v>503432</v>
       </c>
       <c r="R94" t="n">
-        <v>7134773</v>
+        <v>7134696</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10730,10 +10730,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120076611</v>
+        <v>120076636</v>
       </c>
       <c r="B95" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10742,25 +10742,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10770,10 +10770,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>503691</v>
+        <v>503530</v>
       </c>
       <c r="R95" t="n">
-        <v>7134749</v>
+        <v>7134813</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120076634</v>
+        <v>120076631</v>
       </c>
       <c r="B96" t="n">
         <v>79623</v>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>503432</v>
+        <v>503624</v>
       </c>
       <c r="R96" t="n">
-        <v>7134696</v>
+        <v>7134757</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10934,10 +10934,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120076636</v>
+        <v>120076609</v>
       </c>
       <c r="B97" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10946,25 +10946,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>503530</v>
+        <v>503567</v>
       </c>
       <c r="R97" t="n">
-        <v>7134813</v>
+        <v>7134773</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11036,10 +11036,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120076631</v>
+        <v>120076611</v>
       </c>
       <c r="B98" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11052,21 +11052,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11076,10 +11076,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>503624</v>
+        <v>503691</v>
       </c>
       <c r="R98" t="n">
-        <v>7134757</v>
+        <v>7134749</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11750,10 +11750,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120076648</v>
+        <v>120076628</v>
       </c>
       <c r="B105" t="n">
-        <v>89247</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11762,25 +11762,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503495</v>
+        <v>503570</v>
       </c>
       <c r="R105" t="n">
-        <v>7134638</v>
+        <v>7134765</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11852,10 +11852,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120076608</v>
+        <v>120076635</v>
       </c>
       <c r="B106" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11868,21 +11868,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>503530</v>
+        <v>503426</v>
       </c>
       <c r="R106" t="n">
-        <v>7134813</v>
+        <v>7134704</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11954,10 +11954,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120076612</v>
+        <v>120076639</v>
       </c>
       <c r="B107" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11966,25 +11966,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503818</v>
+        <v>503430</v>
       </c>
       <c r="R107" t="n">
-        <v>7134671</v>
+        <v>7134677</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120076628</v>
+        <v>120076648</v>
       </c>
       <c r="B108" t="n">
-        <v>79623</v>
+        <v>89247</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12068,25 +12068,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>1596</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12096,10 +12096,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503570</v>
+        <v>503495</v>
       </c>
       <c r="R108" t="n">
-        <v>7134765</v>
+        <v>7134638</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12158,10 +12158,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120076635</v>
+        <v>120076608</v>
       </c>
       <c r="B109" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12174,21 +12174,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12198,10 +12198,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503426</v>
+        <v>503530</v>
       </c>
       <c r="R109" t="n">
-        <v>7134704</v>
+        <v>7134813</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,10 +12260,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120076639</v>
+        <v>120076612</v>
       </c>
       <c r="B110" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12272,25 +12272,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12300,10 +12300,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503430</v>
+        <v>503818</v>
       </c>
       <c r="R110" t="n">
-        <v>7134677</v>
+        <v>7134671</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12362,10 +12362,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120064794</v>
+        <v>120076664</v>
       </c>
       <c r="B111" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12374,41 +12374,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503729</v>
+        <v>503543</v>
       </c>
       <c r="R111" t="n">
-        <v>7134606</v>
+        <v>7134608</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12464,10 +12464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120076664</v>
+        <v>120064794</v>
       </c>
       <c r="B112" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12476,41 +12476,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503543</v>
+        <v>503729</v>
       </c>
       <c r="R112" t="n">
-        <v>7134608</v>
+        <v>7134606</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13280,10 +13280,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120076632</v>
+        <v>120076651</v>
       </c>
       <c r="B120" t="n">
-        <v>79623</v>
+        <v>90730</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13292,25 +13292,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13320,10 +13320,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503434</v>
+        <v>503516</v>
       </c>
       <c r="R120" t="n">
-        <v>7134673</v>
+        <v>7134622</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13382,10 +13382,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120076651</v>
+        <v>120076616</v>
       </c>
       <c r="B121" t="n">
-        <v>90730</v>
+        <v>79624</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13394,25 +13394,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503516</v>
+        <v>503430</v>
       </c>
       <c r="R121" t="n">
-        <v>7134622</v>
+        <v>7134700</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13484,10 +13484,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120076616</v>
+        <v>120076632</v>
       </c>
       <c r="B122" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13500,21 +13500,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13524,10 +13524,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503430</v>
+        <v>503434</v>
       </c>
       <c r="R122" t="n">
-        <v>7134700</v>
+        <v>7134673</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>

--- a/artfynd/A 31839-2020 artfynd.xlsx
+++ b/artfynd/A 31839-2020 artfynd.xlsx
@@ -15128,7 +15128,7 @@
         <v>122753581</v>
       </c>
       <c r="B138" t="n">
-        <v>74733</v>
+        <v>74736</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
